--- a/squad1/ciento/api-cientometria/Consolidado - Respostas Gerais.xlsx
+++ b/squad1/ciento/api-cientometria/Consolidado - Respostas Gerais.xlsx
@@ -8702,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="AJ119" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>MANEJO DE NUTRIENTES E AGUA</v>
       </c>
     </row>
     <row r="120">
@@ -8713,94 +8713,94 @@
         <v>izaias silva</v>
       </c>
       <c r="C120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="D120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="E120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="F120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="G120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="H120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="I120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="J120" t="str">
-        <v/>
+        <v>Prova de Administração</v>
       </c>
       <c r="K120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="L120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="M120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="N120" t="str">
-        <v/>
+        <v>Questões discursivas e objetivas</v>
       </c>
       <c r="O120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="P120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="Q120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="R120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="S120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="T120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="U120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="V120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="W120" t="str">
         <v>administracao - silvania silva.pdf</v>
       </c>
       <c r="Z120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="AA120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="AB120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="AC120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="AD120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="AE120" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
       <c r="AF120" t="str">
-        <v>Rejeitado: O texto não trata de agronomia prática.</v>
-      </c>
-      <c r="AG120" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AH120" t="str">
-        <v>TRUE</v>
+        <v>N/A</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="b">
+        <v>1</v>
       </c>
       <c r="AI120" t="b">
         <v>0</v>
@@ -8905,59 +8905,62 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122">
+        <v>12</v>
+      </c>
       <c r="C122" t="str">
-        <v>Rajinder Pal, Onkar Singh, Gulzar S Sanghera, R K Gupta</v>
+        <v>N/A</v>
       </c>
       <c r="D122" t="str">
-        <v>Influence of INM on sugarcane productivity and soil fertility under Indo-Gangetic plain</v>
+        <v>N/A</v>
       </c>
       <c r="E122" t="str">
-        <v>Desenvolvimento de estratégias de manejo integrado de nutrientes para o cultivo de cana-de-açúcar em condições subtropicais do Punjab</v>
-      </c>
-      <c r="F122">
-        <v>2021</v>
+        <v>N/A</v>
+      </c>
+      <c r="F122" t="str">
+        <v>N/A</v>
       </c>
       <c r="G122" t="str">
         <v>N/A</v>
       </c>
       <c r="H122" t="str">
-        <v>Cana-de-açúcar, Manejo integrado de nutrientes, Fertilidade do solo, Produtividade</v>
+        <v>N/A</v>
       </c>
       <c r="I122" t="str">
-        <v>O estudo teve como objetivo desenvolver estratégias de manejo integrado de nutrientes para o cultivo de cana-de-açúcar em condições subtropicais do Punjab.</v>
+        <v>N/A</v>
       </c>
       <c r="J122" t="str">
-        <v>Artigo científico</v>
+        <v>N/A</v>
       </c>
       <c r="K122" t="str">
-        <v>Indian Journal of Agricultural Sciences</v>
+        <v>N/A</v>
       </c>
       <c r="L122" t="str">
-        <v>Punjab Agricultural University</v>
+        <v>N/A</v>
       </c>
       <c r="M122" t="str">
-        <v>Kapurthala, Punjab, Índia</v>
+        <v>N/A</v>
       </c>
       <c r="N122" t="str">
-        <v>Pesquisa experimental</v>
+        <v>N/A</v>
       </c>
       <c r="O122" t="str">
-        <v>Indian Journal of Agricultural Sciences</v>
+        <v>N/A</v>
       </c>
       <c r="P122" t="str">
         <v>N/A</v>
       </c>
-      <c r="Q122">
-        <v>91</v>
-      </c>
-      <c r="R122">
-        <v>5</v>
+      <c r="Q122" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R122" t="str">
+        <v>N/A</v>
       </c>
       <c r="S122" t="str">
-        <v>703-707</v>
+        <v>N/A</v>
       </c>
       <c r="T122" t="str">
-        <v>https://doi.org/10.56093/ijas.v91i5.112987</v>
+        <v>N/A</v>
       </c>
       <c r="U122" t="str">
         <v>N/A</v>
@@ -8966,7 +8969,7 @@
         <v>N/A</v>
       </c>
       <c r="W122" t="str">
-        <v>Influence of INM on sugarcane productivity_bioinsumos(1).pdf</v>
+        <v/>
       </c>
       <c r="Z122" t="str">
         <v>N/A</v>
@@ -8987,16 +8990,16 @@
         <v>N/A</v>
       </c>
       <c r="AF122" t="str">
-        <v>Aprovado: Avalia a eficácia de diferentes estratégias de manejo integrado de nutrientes para o cultivo de cana-de-açúcar em condições subtropicais do Punjab.</v>
+        <v>Rejeitado: Texto insuficiente para análise científica.</v>
       </c>
       <c r="AG122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ122" t="str">
-        <v>BIOINSUMOS</v>
+        <v>ERRO: PDF sem texto (Imagem/Scan)</v>
       </c>
     </row>
     <row r="123">
@@ -9007,16 +9010,19 @@
         <v>Influence of INM on sugarcane productivity and soil fertility under Indo-Gangetic plain</v>
       </c>
       <c r="E123" t="str">
-        <v>A field experiment was conducted during 2016-17 at Punjab Agricultural University, Regional Research Station, Kapurthala, Punjab, India with nine treatments comprising various combinations of farmyard manure (FYM), bio- fertilizers and different levels of chemical fertilizers in a randomized block design (RBD).</v>
+        <v>Desenvolvimento de estratégias de manejo integrado de nutrientes para o cultivo de cana-de-açúcar em condições subtropicais do Punjab</v>
       </c>
       <c r="F123">
         <v>2021</v>
       </c>
+      <c r="G123" t="str">
+        <v>N/A</v>
+      </c>
       <c r="H123" t="str">
-        <v>Cane and sugar productivity, Integrated nutrient management, Nutrient status, Sugarcane</v>
+        <v>Cana-de-açúcar, Manejo integrado de nutrientes, Fertilidade do solo, Produtividade</v>
       </c>
       <c r="I123" t="str">
-        <v>O estudo teve como objetivo desenvolver estratégias de manejo integrado de nutrientes (INM) para o uso conjuntivo de fontes orgânicas e inorgânicas de nutrientes, além de biofertilizantes, de forma a sustentar a saúde do solo e a produtividade do cana-de-açúcar a longo prazo em condições subtropicais do Punjab.</v>
+        <v>O estudo teve como objetivo desenvolver estratégias de manejo integrado de nutrientes para o cultivo de cana-de-açúcar em condições subtropicais do Punjab.</v>
       </c>
       <c r="J123" t="str">
         <v>Artigo científico</v>
@@ -9031,43 +9037,55 @@
         <v>Kapurthala, Punjab, Índia</v>
       </c>
       <c r="N123" t="str">
-        <v>Experimento de campo</v>
+        <v>Pesquisa experimental</v>
       </c>
       <c r="O123" t="str">
         <v>Indian Journal of Agricultural Sciences</v>
       </c>
+      <c r="P123" t="str">
+        <v>N/A</v>
+      </c>
       <c r="Q123">
         <v>91</v>
       </c>
       <c r="R123">
         <v>5</v>
       </c>
+      <c r="S123" t="str">
+        <v>703-707</v>
+      </c>
       <c r="T123" t="str">
         <v>https://doi.org/10.56093/ijas.v91i5.112987</v>
       </c>
+      <c r="U123" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V123" t="str">
+        <v>N/A</v>
+      </c>
       <c r="W123" t="str">
         <v>Influence of INM on sugarcane productivity_bioinsumos(1).pdf</v>
       </c>
       <c r="Z123" t="str">
-        <v>O solo da área experimental é um solo arenoso-looso, com pH 8,05, baixo em carbono orgânico (3,70 g/kg) e condutividade elétrica (0,231 dS/m).</v>
+        <v>N/A</v>
       </c>
       <c r="AA123" t="str">
-        <v>Cromatografia gasosa, Espectrometria de massa, Análise de variância (ANOVA)</v>
+        <v>N/A</v>
       </c>
       <c r="AB123" t="str">
-        <v>Nitrogênio, Fósforo, Potássio, Sulfeto de hidrogênio, Ferro, Manganês, Zinco, Cobre</v>
+        <v>N/A</v>
       </c>
       <c r="AC123" t="str">
-        <v>Fertilização de cobertura, Adubação foliar, Fertirrigação</v>
+        <v>N/A</v>
       </c>
       <c r="AD123" t="str">
-        <v>Cana-de-açúcar</v>
+        <v>N/A</v>
       </c>
       <c r="AE123" t="str">
-        <v>Cana-de-açúcar (Saccharum officinarum)</v>
+        <v>N/A</v>
       </c>
       <c r="AF123" t="str">
-        <v>Aprovado: Detalha uma nova estratégia de manejo integrado de nutrientes para cana-de-açúcar.</v>
+        <v>Aprovado: Avalia a eficácia de diferentes estratégias de manejo integrado de nutrientes para o cultivo de cana-de-açúcar em condições subtropicais do Punjab.</v>
       </c>
       <c r="AG123" t="b">
         <v>1</v>
@@ -9081,88 +9099,73 @@
     </row>
     <row r="124">
       <c r="C124" t="str">
-        <v>M.P. Stephan, M. Oliveira, K.R.S. Teixeira, G. Martinez-Drets e J. D/Sbereiner</v>
+        <v>Rajinder Pal, Onkar Singh, Gulzar S Sanghera, R K Gupta</v>
       </c>
       <c r="D124" t="str">
-        <v>Physiology and dinitrogen fixation of A cetobacter diazotrophicus</v>
+        <v>Influence of INM on sugarcane productivity and soil fertility under Indo-Gangetic plain</v>
       </c>
       <c r="E124" t="str">
-        <v>N2-dependent growth; N2-fixation, in sugar cane; Acetobacter diazotrophicus</v>
+        <v>A field experiment was conducted during 2016-17 at Punjab Agricultural University, Regional Research Station, Kapurthala, Punjab, India with nine treatments comprising various combinations of farmyard manure (FYM), bio- fertilizers and different levels of chemical fertilizers in a randomized block design (RBD).</v>
       </c>
       <c r="F124">
-        <v>1991</v>
-      </c>
-      <c r="G124" t="str">
-        <v>N/A</v>
+        <v>2021</v>
       </c>
       <c r="H124" t="str">
-        <v>N2-dependent growth, N2-fixation, sugar cane, Acetobacter diazotrophicus</v>
+        <v>Cane and sugar productivity, Integrated nutrient management, Nutrient status, Sugarcane</v>
       </c>
       <c r="I124" t="str">
-        <v>O artigo descreve as características fisiológicas de Acetobacter diazotrophicus, um diazotrófico isolado de raízes de cana-de-açúcar. O bactério é capaz de crescer em pH 3,0 e apresenta alta atividade de nitrogenase até pH 2,5. A extração de oxidação de glicose seguida pela formação de ácido gluconico é necessária para iniciar o crescimento logarítmico, que ocorre com N2 como fonte de nitrogênio.</v>
+        <v>O estudo teve como objetivo desenvolver estratégias de manejo integrado de nutrientes (INM) para o uso conjuntivo de fontes orgânicas e inorgânicas de nutrientes, além de biofertilizantes, de forma a sustentar a saúde do solo e a produtividade do cana-de-açúcar a longo prazo em condições subtropicais do Punjab.</v>
       </c>
       <c r="J124" t="str">
         <v>Artigo científico</v>
       </c>
       <c r="K124" t="str">
-        <v>FEMS Microbiology Letters</v>
+        <v>Indian Journal of Agricultural Sciences</v>
       </c>
       <c r="L124" t="str">
-        <v>CNPBS/EMBRAPA</v>
+        <v>Punjab Agricultural University</v>
       </c>
       <c r="M124" t="str">
-        <v>Seropédica, Rio de Janeiro, Brasil</v>
+        <v>Kapurthala, Punjab, Índia</v>
       </c>
       <c r="N124" t="str">
-        <v>Estudo de caso</v>
+        <v>Experimento de campo</v>
       </c>
       <c r="O124" t="str">
-        <v>FEMS Microbiology Letters</v>
-      </c>
-      <c r="P124" t="str">
-        <v>N/A</v>
+        <v>Indian Journal of Agricultural Sciences</v>
       </c>
       <c r="Q124">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="R124">
-        <v>1</v>
-      </c>
-      <c r="S124" t="str">
-        <v>67-72</v>
+        <v>5</v>
       </c>
       <c r="T124" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="U124" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="V124" t="str">
-        <v>N/A</v>
+        <v>https://doi.org/10.56093/ijas.v91i5.112987</v>
       </c>
       <c r="W124" t="str">
-        <v>Physiology and dinitrogen fixation of A cetobacter diazotrophicus_bioinsumos.pdf</v>
+        <v>Influence of INM on sugarcane productivity_bioinsumos(1).pdf</v>
       </c>
       <c r="Z124" t="str">
-        <v>O solo da região de cultivo da cana-de-açúcar é caracterizado por pH ácido, com valores entre 3,0 e 5,5. A região é localizada no Brasil, mais especificamente no estado do Rio de Janeiro.</v>
+        <v>O solo da área experimental é um solo arenoso-looso, com pH 8,05, baixo em carbono orgânico (3,70 g/kg) e condutividade elétrica (0,231 dS/m).</v>
       </c>
       <c r="AA124" t="str">
         <v>Cromatografia gasosa, Espectrometria de massa, Análise de variância (ANOVA)</v>
       </c>
       <c r="AB124" t="str">
-        <v>Nitrogênio, Fósforo, Potássio</v>
+        <v>Nitrogênio, Fósforo, Potássio, Sulfeto de hidrogênio, Ferro, Manganês, Zinco, Cobre</v>
       </c>
       <c r="AC124" t="str">
         <v>Fertilização de cobertura, Adubação foliar, Fertirrigação</v>
       </c>
       <c r="AD124" t="str">
-        <v>Cereais, Leguminosas, Hortaliças, Frutíferas</v>
+        <v>Cana-de-açúcar</v>
       </c>
       <c r="AE124" t="str">
-        <v>Cana-de-açúcar</v>
+        <v>Cana-de-açúcar (Saccharum officinarum)</v>
       </c>
       <c r="AF124" t="str">
-        <v>Aprovado: Detalha as características fisiológicas de Acetobacter diazotrophicus e sua capacidade de fixação de nitrogênio.</v>
+        <v>Aprovado: Detalha uma nova estratégia de manejo integrado de nutrientes para cana-de-açúcar.</v>
       </c>
       <c r="AG124" t="b">
         <v>1</v>
@@ -9176,55 +9179,55 @@
     </row>
     <row r="125">
       <c r="C125" t="str">
-        <v>N. SenthiP, T. Raguchander, R. Viswanathan e R. Samiyappan</v>
+        <v>M.P. Stephan, M. Oliveira, K.R.S. Teixeira, G. Martinez-Drets e J. D/Sbereiner</v>
       </c>
       <c r="D125" t="str">
-        <v>Sugarcane Talc Formulated. Fluorescent Pseudomonads for Sugarcane Red Rot Suppression and Enhanced Yield Under Field Conditions</v>
+        <v>Physiology and dinitrogen fixation of A cetobacter diazotrophicus</v>
       </c>
       <c r="E125" t="str">
-        <v>Uso de Pseudomonas fluorescens para controle de doenças em cana-de-açúcar</v>
+        <v>N2-dependent growth; N2-fixation, in sugar cane; Acetobacter diazotrophicus</v>
       </c>
       <c r="F125">
-        <v>2003</v>
+        <v>1991</v>
       </c>
       <c r="G125" t="str">
         <v>N/A</v>
       </c>
       <c r="H125" t="str">
-        <v>Cana-de-açúcar, resistência sistêmica induzida, promoção de crescimento, Pseudomonas fluorescens, doença da rota vermelha</v>
+        <v>N2-dependent growth, N2-fixation, sugar cane, Acetobacter diazotrophicus</v>
       </c>
       <c r="I125" t="str">
-        <v>O estudo avaliou a eficácia de Pseudomonas fluorescens em controlar a doença da rota vermelha em cana-de-açúcar. As bactérias foram isoladas da rizosfera da cana-de-açúcar e formuladas em talco. A aplicação das bactérias reduziu a incidência da doença e melhorou a produção de cana-de-açúcar.</v>
+        <v>O artigo descreve as características fisiológicas de Acetobacter diazotrophicus, um diazotrófico isolado de raízes de cana-de-açúcar. O bactério é capaz de crescer em pH 3,0 e apresenta alta atividade de nitrogenase até pH 2,5. A extração de oxidação de glicose seguida pela formação de ácido gluconico é necessária para iniciar o crescimento logarítmico, que ocorre com N2 como fonte de nitrogênio.</v>
       </c>
       <c r="J125" t="str">
         <v>Artigo científico</v>
       </c>
       <c r="K125" t="str">
-        <v>Tamil Nadu Agricultural University</v>
+        <v>FEMS Microbiology Letters</v>
       </c>
       <c r="L125" t="str">
-        <v>Departamento de Patologia Vegetal, Universidade Agrícola de Tamil Nadu</v>
+        <v>CNPBS/EMBRAPA</v>
       </c>
       <c r="M125" t="str">
-        <v>Coimbatore, Índia</v>
+        <v>Seropédica, Rio de Janeiro, Brasil</v>
       </c>
       <c r="N125" t="str">
-        <v>Pesquisa</v>
+        <v>Estudo de caso</v>
       </c>
       <c r="O125" t="str">
-        <v>Vol. 5 (l&amp;2)</v>
+        <v>FEMS Microbiology Letters</v>
       </c>
       <c r="P125" t="str">
         <v>N/A</v>
       </c>
       <c r="Q125">
-        <v>5</v>
-      </c>
-      <c r="R125" t="str">
-        <v>l&amp;2</v>
+        <v>77</v>
+      </c>
+      <c r="R125">
+        <v>1</v>
       </c>
       <c r="S125" t="str">
-        <v>37-43</v>
+        <v>67-72</v>
       </c>
       <c r="T125" t="str">
         <v>N/A</v>
@@ -9236,28 +9239,28 @@
         <v>N/A</v>
       </c>
       <c r="W125" t="str">
-        <v>Talc Formulated Fluorescent Pseudomonads_bioinsumos.pdf</v>
+        <v>Physiology and dinitrogen fixation of A cetobacter diazotrophicus_bioinsumos.pdf</v>
       </c>
       <c r="Z125" t="str">
-        <v>N/A</v>
+        <v>O solo da região de cultivo da cana-de-açúcar é caracterizado por pH ácido, com valores entre 3,0 e 5,5. A região é localizada no Brasil, mais especificamente no estado do Rio de Janeiro.</v>
       </c>
       <c r="AA125" t="str">
-        <v>N/A</v>
+        <v>Cromatografia gasosa, Espectrometria de massa, Análise de variância (ANOVA)</v>
       </c>
       <c r="AB125" t="str">
-        <v>N/A</v>
+        <v>Nitrogênio, Fósforo, Potássio</v>
       </c>
       <c r="AC125" t="str">
-        <v>N/A</v>
+        <v>Fertilização de cobertura, Adubação foliar, Fertirrigação</v>
       </c>
       <c r="AD125" t="str">
-        <v>N/A</v>
+        <v>Cereais, Leguminosas, Hortaliças, Frutíferas</v>
       </c>
       <c r="AE125" t="str">
-        <v>N/A</v>
+        <v>Cana-de-açúcar</v>
       </c>
       <c r="AF125" t="str">
-        <v>Aprovado: Avalia a eficácia de Pseudomonas fluorescens em controlar a doença da rota vermelha em cana-de-açúcar.</v>
+        <v>Aprovado: Detalha as características fisiológicas de Acetobacter diazotrophicus e sua capacidade de fixação de nitrogênio.</v>
       </c>
       <c r="AG125" t="b">
         <v>1</v>
@@ -9271,28 +9274,34 @@
     </row>
     <row r="126">
       <c r="C126" t="str">
-        <v>K. HARI e T.R. SRINIVASAN</v>
+        <v>N. SenthiP, T. Raguchander, R. Viswanathan e R. Samiyappan</v>
       </c>
       <c r="D126" t="str">
-        <v>Response of Sugarcane Varieties to Application of Nitrogen Fixing Bacteria under Different Nitrogen Levels</v>
+        <v>Sugarcane Talc Formulated. Fluorescent Pseudomonads for Sugarcane Red Rot Suppression and Enhanced Yield Under Field Conditions</v>
       </c>
       <c r="E126" t="str">
-        <v>Efeito da aplicação de bactérias fixadoras de nitrogênio em variedades de cana-de-açúcar sob diferentes níveis de nitrogênio</v>
+        <v>Uso de Pseudomonas fluorescens para controle de doenças em cana-de-açúcar</v>
       </c>
       <c r="F126">
-        <v>2005</v>
+        <v>2003</v>
+      </c>
+      <c r="G126" t="str">
+        <v>N/A</v>
       </c>
       <c r="H126" t="str">
-        <v>cana-de-açúcar, biofertilizantes, Azotobacter, Azospirillum e Gluconacetobacter, bactérias fixadoras de nitrogênio</v>
+        <v>Cana-de-açúcar, resistência sistêmica induzida, promoção de crescimento, Pseudomonas fluorescens, doença da rota vermelha</v>
       </c>
       <c r="I126" t="str">
-        <v>O estudo avaliou a resposta de variedades de cana-de-açúcar à aplicação de Azotobacter, Azospirillum e Gluconacetobacter sob diferentes níveis de nitrogênio.</v>
+        <v>O estudo avaliou a eficácia de Pseudomonas fluorescens em controlar a doença da rota vermelha em cana-de-açúcar. As bactérias foram isoladas da rizosfera da cana-de-açúcar e formuladas em talco. A aplicação das bactérias reduziu a incidência da doença e melhorou a produção de cana-de-açúcar.</v>
       </c>
       <c r="J126" t="str">
         <v>Artigo científico</v>
       </c>
+      <c r="K126" t="str">
+        <v>Tamil Nadu Agricultural University</v>
+      </c>
       <c r="L126" t="str">
-        <v>Sugarcane Breeding Institute, ICAR, Coimbatore</v>
+        <v>Departamento de Patologia Vegetal, Universidade Agrícola de Tamil Nadu</v>
       </c>
       <c r="M126" t="str">
         <v>Coimbatore, Índia</v>
@@ -9300,14 +9309,32 @@
       <c r="N126" t="str">
         <v>Pesquisa</v>
       </c>
+      <c r="O126" t="str">
+        <v>Vol. 5 (l&amp;2)</v>
+      </c>
+      <c r="P126" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q126">
+        <v>5</v>
+      </c>
+      <c r="R126" t="str">
+        <v>l&amp;2</v>
+      </c>
       <c r="S126" t="str">
-        <v>28-31</v>
+        <v>37-43</v>
+      </c>
+      <c r="T126" t="str">
+        <v>N/A</v>
       </c>
       <c r="U126" t="str">
         <v>N/A</v>
       </c>
+      <c r="V126" t="str">
+        <v>N/A</v>
+      </c>
       <c r="W126" t="str">
-        <v>Response of sugarcane varieties to application of nitrogen fixing_bioinsumos.pdf</v>
+        <v>Talc Formulated Fluorescent Pseudomonads_bioinsumos.pdf</v>
       </c>
       <c r="Z126" t="str">
         <v>N/A</v>
@@ -9328,7 +9355,7 @@
         <v>N/A</v>
       </c>
       <c r="AF126" t="str">
-        <v>Aprovado: Avalia a eficácia de Azospirillum no controle de fungos em cana-de-açúcar.</v>
+        <v>Aprovado: Avalia a eficácia de Pseudomonas fluorescens em controlar a doença da rota vermelha em cana-de-açúcar.</v>
       </c>
       <c r="AG126" t="b">
         <v>1</v>
@@ -9342,204 +9369,147 @@
     </row>
     <row r="127">
       <c r="C127" t="str">
-        <v>Roberto Batista Marques Júnior, Luciano Pasqualoto Canellas, Lúcia Gracinda da Silva, Fábio Lopes Olivares</v>
+        <v>K. HARI e T.R. SRINIVASAN</v>
       </c>
       <c r="D127" t="str">
-        <v>PROMOÇÃO DE ENRAIZAMENTO DE MICROTOLETES DE CANA-DE-AÇÚCAR PELO USO CONJUNTO DE SUBSTÂNCIAS HÚMICAS E BACTÉRIAS DIAZOTRÓFICAS ENDOFÍTICAS</v>
+        <v>Response of Sugarcane Varieties to Application of Nitrogen Fixing Bacteria under Different Nitrogen Levels</v>
       </c>
       <c r="E127" t="str">
-        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE OF HUMIC SUBSTANCES AND ENDOPHYTIC DIAZOTROPHIC BACTERIA IN SUGAR CANE</v>
-      </c>
-      <c r="F127" t="str">
-        <v>2008</v>
-      </c>
-      <c r="G127" t="str">
-        <v/>
+        <v>Efeito da aplicação de bactérias fixadoras de nitrogênio em variedades de cana-de-açúcar sob diferentes níveis de nitrogênio</v>
+      </c>
+      <c r="F127">
+        <v>2005</v>
       </c>
       <c r="H127" t="str">
-        <v>Herbaspirillum seropedicae, termoterapia, ácidos húmicos</v>
+        <v>cana-de-açúcar, biofertilizantes, Azotobacter, Azospirillum e Gluconacetobacter, bactérias fixadoras de nitrogênio</v>
       </c>
       <c r="I127" t="str">
-        <v>Além do fornecimento direto de nutrientes por meio da mineralização da matéria orgânica ou pela fixação biológica de N 2, as substâncias húmicas e as bactérias diazotróficas endofíticas podem afetar diretamente o metabolismo vegetal, modificando o padrão de crescimento e desenvolvimento das plantas.</v>
+        <v>O estudo avaliou a resposta de variedades de cana-de-açúcar à aplicação de Azotobacter, Azospirillum e Gluconacetobacter sob diferentes níveis de nitrogênio.</v>
       </c>
       <c r="J127" t="str">
         <v>Artigo científico</v>
       </c>
-      <c r="K127" t="str">
-        <v/>
-      </c>
       <c r="L127" t="str">
-        <v>Universidade Estadual do Norte Fluminense - Darcy Ribeiro</v>
+        <v>Sugarcane Breeding Institute, ICAR, Coimbatore</v>
       </c>
       <c r="M127" t="str">
-        <v>Campos dos Goytacazes (RJ)</v>
+        <v>Coimbatore, Índia</v>
       </c>
       <c r="N127" t="str">
-        <v>Tese de Mestrado</v>
-      </c>
-      <c r="O127" t="str">
-        <v>Revista Brasileira de Ciência do Solo</v>
-      </c>
-      <c r="P127" t="str">
-        <v/>
-      </c>
-      <c r="Q127" t="str">
-        <v>32</v>
-      </c>
-      <c r="R127" t="str">
-        <v/>
+        <v>Pesquisa</v>
       </c>
       <c r="S127" t="str">
-        <v>1121-1128</v>
-      </c>
-      <c r="T127" t="str">
-        <v/>
+        <v>28-31</v>
       </c>
       <c r="U127" t="str">
         <v>N/A</v>
       </c>
-      <c r="V127" t="str">
-        <v/>
-      </c>
       <c r="W127" t="str">
-        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE_bioinsumos.pdf</v>
+        <v>Response of sugarcane varieties to application of nitrogen fixing_bioinsumos.pdf</v>
       </c>
       <c r="Z127" t="str">
         <v>N/A</v>
       </c>
       <c r="AA127" t="str">
-        <v>Cromatografia gasosa, Espectrometria de massa, Análise de variância (ANOVA)</v>
+        <v>N/A</v>
       </c>
       <c r="AB127" t="str">
-        <v>Nitrogênio, Fósforo, Potássio, Boro</v>
+        <v>N/A</v>
       </c>
       <c r="AC127" t="str">
-        <v>Fertilização de cobertura, Adubação foliar, Fertirrigação</v>
+        <v>N/A</v>
       </c>
       <c r="AD127" t="str">
-        <v>Cereais, Leguminosas, Hortaliças, Frutíferas</v>
+        <v>N/A</v>
       </c>
       <c r="AE127" t="str">
-        <v>Cana-de-açúcar</v>
+        <v>N/A</v>
       </c>
       <c r="AF127" t="str">
-        <v>Aprovado: Detalha uma nova técnica de promoção de enraizamento de microtoletes de cana-de-açúcar utilizando substâncias húmicas e bactérias diazotróficas endofíticas.</v>
-      </c>
-      <c r="AG127" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH127" t="str">
-        <v>FALSE</v>
+        <v>Aprovado: Avalia a eficácia de Azospirillum no controle de fungos em cana-de-açúcar.</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH127" t="b">
+        <v>0</v>
       </c>
       <c r="AJ127" t="str">
         <v>BIOINSUMOS</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="str">
-        <v/>
-      </c>
-      <c r="B128" t="str">
-        <v/>
-      </c>
       <c r="C128" t="str">
-        <v>M.P. Stephan, M. Oliveira, K.R.S. Teixeira, G. Martinez-Drets e J. D/Sbereiner</v>
+        <v>Roberto Batista Marques Júnior, Luciano Pasqualoto Canellas, Lúcia Gracinda da Silva, Fábio Lopes Olivares</v>
       </c>
       <c r="D128" t="str">
-        <v>Physiology and dinitrogen fixation of A cetobacter diazotrophicus</v>
+        <v>PROMOÇÃO DE ENRAIZAMENTO DE MICROTOLETES DE CANA-DE-AÇÚCAR PELO USO CONJUNTO DE SUBSTÂNCIAS HÚMICAS E BACTÉRIAS DIAZOTRÓFICAS ENDOFÍTICAS</v>
       </c>
       <c r="E128" t="str">
-        <v>Estudo sobre a fixação de nitrogênio e características fisiológicas de Acetobacter diazotrophicus</v>
-      </c>
-      <c r="F128" t="str">
-        <v>1991</v>
-      </c>
-      <c r="G128" t="str">
-        <v/>
+        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE OF HUMIC SUBSTANCES AND ENDOPHYTIC DIAZOTROPHIC BACTERIA IN SUGAR CANE</v>
+      </c>
+      <c r="F128">
+        <v>2008</v>
       </c>
       <c r="H128" t="str">
-        <v>N2-dependent growth, N2-fixation, in sugar cane, Acetobacter diazotrophicus</v>
+        <v>Herbaspirillum seropedicae, termoterapia, ácidos húmicos</v>
       </c>
       <c r="I128" t="str">
-        <v>O artigo descreve as características fisiológicas e a fixação de nitrogênio de Acetobacter diazotrophicus, um bactério isolado de raízes de cana-de-açúcar.</v>
+        <v>Além do fornecimento direto de nutrientes por meio da mineralização da matéria orgânica ou pela fixação biológica de N 2, as substâncias húmicas e as bactérias diazotróficas endofíticas podem afetar diretamente o metabolismo vegetal, modificando o padrão de crescimento e desenvolvimento das plantas.</v>
       </c>
       <c r="J128" t="str">
         <v>Artigo científico</v>
       </c>
-      <c r="K128" t="str">
-        <v>FEMS Microbiology Letters</v>
-      </c>
       <c r="L128" t="str">
-        <v>CNPBS/EMBRAPA</v>
+        <v>Universidade Estadual do Norte Fluminense - Darcy Ribeiro</v>
       </c>
       <c r="M128" t="str">
-        <v>Seropédica, Rio de Janeiro, Brasil</v>
+        <v>Campos dos Goytacazes (RJ)</v>
       </c>
       <c r="N128" t="str">
-        <v>Estudo de caso</v>
+        <v>Tese de Mestrado</v>
       </c>
       <c r="O128" t="str">
-        <v>FEMS Microbiology Letters</v>
-      </c>
-      <c r="P128" t="str">
-        <v/>
-      </c>
-      <c r="Q128" t="str">
-        <v>77</v>
-      </c>
-      <c r="R128" t="str">
-        <v>1</v>
+        <v>Revista Brasileira de Ciência do Solo</v>
+      </c>
+      <c r="Q128">
+        <v>32</v>
       </c>
       <c r="S128" t="str">
-        <v>67-72</v>
-      </c>
-      <c r="T128" t="str">
-        <v/>
+        <v>1121-1128</v>
       </c>
       <c r="U128" t="str">
         <v>N/A</v>
       </c>
-      <c r="V128" t="str">
-        <v/>
-      </c>
       <c r="W128" t="str">
-        <v>Physiology and dinitrogen fixation of A cetobacter diazotrophicus_bioinsumos.pdf</v>
-      </c>
-      <c r="X128" t="str">
-        <v/>
-      </c>
-      <c r="Y128" t="str">
-        <v/>
+        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE_bioinsumos.pdf</v>
       </c>
       <c r="Z128" t="str">
         <v>N/A</v>
       </c>
       <c r="AA128" t="str">
-        <v>PCR, Sequenciamento, Microscopia, Ensaios em vasos</v>
+        <v>Cromatografia gasosa, Espectrometria de massa, Análise de variância (ANOVA)</v>
       </c>
       <c r="AB128" t="str">
-        <v>Acetobacter diazotrophicus</v>
+        <v>Nitrogênio, Fósforo, Potássio, Boro</v>
       </c>
       <c r="AC128" t="str">
-        <v>Inoculação de sementes</v>
+        <v>Fertilização de cobertura, Adubação foliar, Fertirrigação</v>
       </c>
       <c r="AD128" t="str">
+        <v>Cereais, Leguminosas, Hortaliças, Frutíferas</v>
+      </c>
+      <c r="AE128" t="str">
         <v>Cana-de-açúcar</v>
       </c>
-      <c r="AE128" t="str">
-        <v>Acetobacter diazotrophicus</v>
-      </c>
       <c r="AF128" t="str">
-        <v>Aprovado: Avalia a eficácia de Acetobacter diazotrophicus na fixação de nitrogênio em cana-de-açúcar.</v>
-      </c>
-      <c r="AG128" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH128" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AI128" t="str">
-        <v/>
+        <v>Aprovado: Detalha uma nova técnica de promoção de enraizamento de microtoletes de cana-de-açúcar utilizando substâncias húmicas e bactérias diazotróficas endofíticas.</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH128" t="b">
+        <v>0</v>
       </c>
       <c r="AJ128" t="str">
         <v>BIOINSUMOS</v>

--- a/squad1/ciento/api-cientometria/Consolidado - Respostas Gerais.xlsx
+++ b/squad1/ciento/api-cientometria/Consolidado - Respostas Gerais.xlsx
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="AJ2" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="3">
@@ -670,7 +670,7 @@
         <v>1</v>
       </c>
       <c r="AJ3" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="4">
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="5">
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="6">
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="7">
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="8">
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="9">
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="10">
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="11">
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="12">
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="13">
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="14">
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="15">
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="16">
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="17">
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="18">
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="19">
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="20">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="21">
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="22">
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="23">
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="24">
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="25">
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="26">
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="27">
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="28">
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="29">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="30">
@@ -2569,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="31">
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="32">
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="33">
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="34">
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="35">
@@ -2939,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="36">
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="37">
@@ -3078,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="38">
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="39">
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="40">
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="41">
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="42">
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="43">
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="44">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="45">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="46">
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="47">
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="48">
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="49">
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="50">
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="51">
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="52">
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="53">
@@ -4220,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="54">
@@ -4294,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="55">
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="56">
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="57">
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="58">
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="59">
@@ -4652,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="60">
@@ -4726,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="61">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="62">
@@ -4862,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="63">
@@ -4936,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="64">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="65">
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="66">
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="67">
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="68">
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="AJ68" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="69">
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="AJ69" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="70">
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="71">
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="AJ71" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="72">
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="AJ72" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="73">
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="74">
@@ -5738,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="AJ74" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="75">
@@ -5812,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="AJ75" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="76">
@@ -5880,7 +5880,7 @@
         <v>0</v>
       </c>
       <c r="AJ76" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="77">
@@ -5951,7 +5951,7 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="78">
@@ -6022,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="AJ78" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="79">
@@ -6096,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="AJ79" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="80">
@@ -6167,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="AJ80" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="81">
@@ -6229,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="AJ81" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="82">
@@ -6300,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="83">
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="84">
@@ -6418,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="AJ84" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="85">
@@ -6492,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="AJ85" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="86">
@@ -6551,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="AJ86" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="87">
@@ -6610,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="AJ87" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="88">
@@ -6684,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="AJ88" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="89">
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="AJ89" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="90">
@@ -6808,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="91">
@@ -6879,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="92">
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="AJ92" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="93">
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="94">
@@ -7098,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="AJ94" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="95">
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="AJ95" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="96">
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="97">
@@ -7296,7 +7296,7 @@
         <v>0</v>
       </c>
       <c r="AJ97" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="98">
@@ -7358,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="AJ98" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="99">
@@ -7417,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="AJ99" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="100">
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="AJ100" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="101">
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="AJ101" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="102">
@@ -7624,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="AJ102" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="103">
@@ -7677,7 +7677,7 @@
         <v>0</v>
       </c>
       <c r="AJ103" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="104">
@@ -7739,7 +7739,7 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="105">
@@ -7807,7 +7807,7 @@
         <v>0</v>
       </c>
       <c r="AJ105" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="106">
@@ -7869,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="AJ106" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="107">
@@ -7928,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="AJ107" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="108">
@@ -8002,7 +8002,7 @@
         <v>0</v>
       </c>
       <c r="AJ108" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="109">
@@ -8064,7 +8064,7 @@
         <v>0</v>
       </c>
       <c r="AJ109" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="110">
@@ -8126,7 +8126,7 @@
         <v>0</v>
       </c>
       <c r="AJ110" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="111">
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="AJ111" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="112">
@@ -8250,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="113">
@@ -8324,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="AJ113" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="114">
@@ -8383,7 +8383,7 @@
         <v>0</v>
       </c>
       <c r="AJ114" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="115">
@@ -8454,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="AJ115" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="116">
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="AJ116" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="117">
@@ -8581,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="AJ117" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="118">
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="AJ118" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="119">
@@ -8702,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="AJ119" t="str">
-        <v>MANEJO DE NUTRIENTES E AGUA</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="120">
@@ -8806,7 +8806,7 @@
         <v>0</v>
       </c>
       <c r="AJ120" t="str">
-        <v>MANEJO ECOFISIOLÓGICO E NUTRICIONAL DA CITRICULTURA DE ALTA PERFORMANCE</v>
+        <v>citros e cana</v>
       </c>
     </row>
     <row r="121">
@@ -8901,7 +8901,7 @@
         <v>0</v>
       </c>
       <c r="AJ121" t="str">
-        <v>BIOINSUMOS</v>
+        <v>solos</v>
       </c>
     </row>
     <row r="122">
@@ -9094,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="str">
-        <v>BIOINSUMOS</v>
+        <v>solos</v>
       </c>
     </row>
     <row r="124">
@@ -9174,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="AJ124" t="str">
-        <v>BIOINSUMOS</v>
+        <v>solos</v>
       </c>
     </row>
     <row r="125">
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="AJ125" t="str">
-        <v>BIOINSUMOS</v>
+        <v>solos</v>
       </c>
     </row>
     <row r="126">
@@ -9364,7 +9364,7 @@
         <v>0</v>
       </c>
       <c r="AJ126" t="str">
-        <v>BIOINSUMOS</v>
+        <v>solos</v>
       </c>
     </row>
     <row r="127">
@@ -9435,7 +9435,7 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="str">
-        <v>BIOINSUMOS</v>
+        <v>solos</v>
       </c>
     </row>
     <row r="128">
@@ -9512,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="AJ128" t="str">
-        <v>BIOINSUMOS</v>
+        <v>solos</v>
       </c>
     </row>
   </sheetData>

--- a/squad1/ciento/api-cientometria/Consolidado - Respostas Gerais.xlsx
+++ b/squad1/ciento/api-cientometria/Consolidado - Respostas Gerais.xlsx
@@ -8713,7 +8713,7 @@
         <v>izaias silva</v>
       </c>
       <c r="C120" t="str">
-        <v>N/A</v>
+        <v xml:space="preserve">ERRO: Erro na API do LLM: </v>
       </c>
       <c r="D120" t="str">
         <v>N/A</v>
@@ -8794,13 +8794,13 @@
         <v>N/A</v>
       </c>
       <c r="AF120" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AG120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="b">
-        <v>1</v>
+        <v xml:space="preserve">Erro na análise: ERRO: Erro na API do LLM: </v>
+      </c>
+      <c r="AG120" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AH120" t="str">
+        <v>TRUE</v>
       </c>
       <c r="AI120" t="b">
         <v>0</v>

--- a/squad1/ciento/api-cientometria/Consolidado - Respostas Gerais.xlsx
+++ b/squad1/ciento/api-cientometria/Consolidado - Respostas Gerais.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ128"/>
+  <dimension ref="A1:AJ194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8713,64 +8713,64 @@
         <v>izaias silva</v>
       </c>
       <c r="C120" t="str">
-        <v xml:space="preserve">ERRO: Erro na API do LLM: </v>
+        <v/>
       </c>
       <c r="D120" t="str">
-        <v>N/A</v>
+        <v>administracao - silvania silva</v>
       </c>
       <c r="E120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="F120" t="str">
-        <v>N/A</v>
+        <v>2018</v>
       </c>
       <c r="G120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="H120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="J120" t="str">
-        <v>Prova de Administração</v>
+        <v>Questão Discursiva</v>
       </c>
       <c r="K120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="L120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="M120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="N120" t="str">
-        <v>Questões discursivas e objetivas</v>
+        <v/>
       </c>
       <c r="O120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="P120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="Q120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="R120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="S120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="T120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="U120" t="str">
         <v>N/A</v>
       </c>
       <c r="V120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="W120" t="str">
         <v>administracao - silvania silva.pdf</v>
@@ -8779,22 +8779,22 @@
         <v>N/A</v>
       </c>
       <c r="AA120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="AB120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="AC120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="AD120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="AE120" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="AF120" t="str">
-        <v xml:space="preserve">Erro na análise: ERRO: Erro na API do LLM: </v>
+        <v>Não é um artigo valido</v>
       </c>
       <c r="AG120" t="str">
         <v>FALSE</v>
@@ -8802,11 +8802,11 @@
       <c r="AH120" t="str">
         <v>TRUE</v>
       </c>
-      <c r="AI120" t="b">
-        <v>0</v>
+      <c r="AI120" t="str">
+        <v>FALSE</v>
       </c>
       <c r="AJ120" t="str">
-        <v>citros e cana</v>
+        <v>solos</v>
       </c>
     </row>
     <row r="121">
@@ -9515,9 +9515,7269 @@
         <v>solos</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v/>
+      </c>
+      <c r="B129" t="str">
+        <v/>
+      </c>
+      <c r="C129" t="str">
+        <v>Roberto Batista Marques Júnior, Luciano Pasqualoto Canellas, Lúcia Gracinda da Silva, Fábio Lopes Olivares</v>
+      </c>
+      <c r="D129" t="str">
+        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE_bioinsumos</v>
+      </c>
+      <c r="E129" t="str">
+        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE OF HUMIC SUBSTANCES AND ENDOPHYTIC DIAZOTROPHIC BACTERIA IN SUGAR CANE</v>
+      </c>
+      <c r="F129" t="str">
+        <v>2008</v>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v>Herbaspirillum seropedicae, termoterapia, ácidos húmicos</v>
+      </c>
+      <c r="I129" t="str">
+        <v>Além do fornecimento direto de nutrientes por meio da mineralização da matéria orgânica ou pela fixação biológica de N 2, as substâncias húmicas e as bactérias diazotróficas endofíticas podem afetar diretamente o metabolismo vegetal, modificando o padrão de crescimento e desenvolvimento das plantas.</v>
+      </c>
+      <c r="J129" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K129" t="str">
+        <v>R. Bras. Ci. Solo</v>
+      </c>
+      <c r="L129" t="str">
+        <v>Universidade Estadual do Norte Fluminense - UENF</v>
+      </c>
+      <c r="M129" t="str">
+        <v>Campos dos Goytacazes (RJ)</v>
+      </c>
+      <c r="N129" t="str">
+        <v>Tese de Mestrado</v>
+      </c>
+      <c r="O129" t="str">
+        <v>Revista Brasileira de Ciência do Solo</v>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v>32</v>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v>1121-1128</v>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+      <c r="U129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V129" t="str">
+        <v/>
+      </c>
+      <c r="W129" t="str">
+        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE_bioinsumos.pdf</v>
+      </c>
+      <c r="X129" t="str">
+        <v/>
+      </c>
+      <c r="Y129" t="str">
+        <v/>
+      </c>
+      <c r="Z129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF129" t="str">
+        <v>Aprovado: Avalia a promoção do crescimento radicular de microtoletes de cana-de-açúcar pelo uso conjunto de substâncias húmicas e bactérias diazotróficas endofíticas.</v>
+      </c>
+      <c r="AG129" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH129" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AI129" t="str">
+        <v/>
+      </c>
+      <c r="AJ129" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v/>
+      </c>
+      <c r="B130" t="str">
+        <v/>
+      </c>
+      <c r="C130" t="str">
+        <v>Luis E. Mota-Pacheco, Paula C. Guadarrama-Mendoza, Raúl Salas-Coronado, Adelfo Escalante, Thomas J. Montville, Rogelio Valadez-Blanco</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Adaptation of Bacillus licheniformis to molasses_bioinsumos</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Adaptación de Bacillus licheniformis a melazas para la producción mejorada de una cepa biofertilizante</v>
+      </c>
+      <c r="F130" t="str">
+        <v>2019</v>
+      </c>
+      <c r="G130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H130" t="str">
+        <v>agricultura sustentável, rizósfera, biofertilizantes bacterianos, Bacillus licheniformis, melazas de cana-de-açúcar, adaptação bacteriana induzida, produção de biomassa</v>
+      </c>
+      <c r="I130" t="str">
+        <v>O uso de biofertilizantes pode reduzir a dependência de fertilizantes químicos, que não são renováveis, são caros para importar e degradam tanto a rizósfera quanto o ecosistema em geral.</v>
+      </c>
+      <c r="J130" t="str">
+        <v>Artigo</v>
+      </c>
+      <c r="K130" t="str">
+        <v>Agrociencia</v>
+      </c>
+      <c r="L130" t="str">
+        <v>Universidade Tecnológica da Mixteca</v>
+      </c>
+      <c r="M130" t="str">
+        <v>Huajuapan de León, Oaxaca, México</v>
+      </c>
+      <c r="N130" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O130" t="str">
+        <v>Agrociencia</v>
+      </c>
+      <c r="P130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q130" t="str">
+        <v>53</v>
+      </c>
+      <c r="R130" t="str">
+        <v>81184</v>
+      </c>
+      <c r="S130" t="str">
+        <v>1183-1201</v>
+      </c>
+      <c r="T130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W130" t="str">
+        <v>Adaptation of Bacillus licheniformis to molasses_bioinsumos.pdf</v>
+      </c>
+      <c r="X130" t="str">
+        <v/>
+      </c>
+      <c r="Y130" t="str">
+        <v/>
+      </c>
+      <c r="Z130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA130" t="str">
+        <v>Biorreator, Cromatografia gasosa, Fotossíntese líquida, RCBD, ANOVA</v>
+      </c>
+      <c r="AB130" t="str">
+        <v>Nitrogênio, Fósforo, Potássio</v>
+      </c>
+      <c r="AC130" t="str">
+        <v>Fertirrigação, Aplicação foliar, Controle de pragas</v>
+      </c>
+      <c r="AD130" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE130" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF130" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG130" t="str">
+        <v/>
+      </c>
+      <c r="AH130" t="str">
+        <v/>
+      </c>
+      <c r="AI130" t="str">
+        <v/>
+      </c>
+      <c r="AJ130" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v/>
+      </c>
+      <c r="B131" t="str">
+        <v/>
+      </c>
+      <c r="C131" t="str">
+        <v>Gomathi Raju, Nori Sri Sailaja, Vengavasi Krishnapriya &amp; Prakash M</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Ameliorating drought stress in sugarcane_bioinsumos</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Eficácia de formulário líquido de biostimulante de algas em condições de campo</v>
+      </c>
+      <c r="F131" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Estresse abiótico, Gracilaria, Kappaphycus, Bioformulação de algas, Cana-de-açúcar</v>
+      </c>
+      <c r="I131" t="str">
+        <v>O estudo avaliou a eficácia de um formulário líquido de biostimulante de algas (LBS6) em condições de campo para mitigar o estresse de seca em cana-de-açúcar (Saccharum spp.).</v>
+      </c>
+      <c r="J131" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K131" t="str">
+        <v>Indian Journal of Experimental Biology</v>
+      </c>
+      <c r="L131" t="str">
+        <v>ICAR-Sugarcane Breeding Institute, Coimbatore, Tamil Nadu, Índia</v>
+      </c>
+      <c r="M131" t="str">
+        <v>Coimbatore, Tamil Nadu, Índia</v>
+      </c>
+      <c r="N131" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O131" t="str">
+        <v>Indian Journal of Experimental Biology</v>
+      </c>
+      <c r="P131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q131" t="str">
+        <v>60</v>
+      </c>
+      <c r="R131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S131" t="str">
+        <v>456-462</v>
+      </c>
+      <c r="T131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W131" t="str">
+        <v>Ameliorating drought stress in sugarcane_bioinsumos.pdf</v>
+      </c>
+      <c r="X131" t="str">
+        <v/>
+      </c>
+      <c r="Y131" t="str">
+        <v/>
+      </c>
+      <c r="Z131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF131" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG131" t="str">
+        <v/>
+      </c>
+      <c r="AH131" t="str">
+        <v/>
+      </c>
+      <c r="AI131" t="str">
+        <v/>
+      </c>
+      <c r="AJ131" t="str">
+        <v>citros e cana</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v/>
+      </c>
+      <c r="B132" t="str">
+        <v/>
+      </c>
+      <c r="C132" t="str">
+        <v>S Wahyuni, D N Kalbuadi, M E R B Prasetyo, S M Putra, H Widiastuti e Priyono</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Application of biostimulant consortium_bioinsumos</v>
+      </c>
+      <c r="E132" t="str">
+        <v>Uso de consórcio de biostimulante para aumentar o crescimento da cana-de-açúcar (Var. Cenning) em solo seco</v>
+      </c>
+      <c r="F132" t="str">
+        <v>2024</v>
+      </c>
+      <c r="G132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H132" t="str">
+        <v>cana-de-açúcar, consórcio de biostimulante, Cenning, biomaterial não nutriente</v>
+      </c>
+      <c r="I132" t="str">
+        <v>O estudo avaliou o efeito de um consórcio de biostimulante (sucrosina, ácido húmico e fungo micorrízico) no crescimento da cana-de-açúcar (Var. Cenning) em solo seco.</v>
+      </c>
+      <c r="J132" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K132" t="str">
+        <v>IOP Publishing</v>
+      </c>
+      <c r="L132" t="str">
+        <v>Indonesian Research Institute for Biotechnology and Bioindustry</v>
+      </c>
+      <c r="M132" t="str">
+        <v>Bogor, Indonésia</v>
+      </c>
+      <c r="N132" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O132" t="str">
+        <v>IOP Conference Series: Earth and Environmental Science</v>
+      </c>
+      <c r="P132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q132" t="str">
+        <v>1306</v>
+      </c>
+      <c r="R132" t="str">
+        <v>1</v>
+      </c>
+      <c r="S132" t="str">
+        <v>012001</v>
+      </c>
+      <c r="T132" t="str">
+        <v>10.1088/1755-1315/1306/1/012001</v>
+      </c>
+      <c r="U132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W132" t="str">
+        <v>Application of biostimulant consortium_bioinsumos.pdf</v>
+      </c>
+      <c r="X132" t="str">
+        <v/>
+      </c>
+      <c r="Y132" t="str">
+        <v/>
+      </c>
+      <c r="Z132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA132" t="str">
+        <v>Foliar spray, aplicação de fungo micorrízico, pulverização de ácido húmico</v>
+      </c>
+      <c r="AB132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC132" t="str">
+        <v>Fertirrigação, aplicação foliar de nutrientes</v>
+      </c>
+      <c r="AD132" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE132" t="str">
+        <v>Cana-de-açúcar (Var. Cenning)</v>
+      </c>
+      <c r="AF132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AG132" t="str">
+        <v/>
+      </c>
+      <c r="AH132" t="str">
+        <v/>
+      </c>
+      <c r="AI132" t="str">
+        <v/>
+      </c>
+      <c r="AJ132" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v/>
+      </c>
+      <c r="B133" t="str">
+        <v/>
+      </c>
+      <c r="C133" t="str">
+        <v>Luis Fernando Nava-López, Raquel Camacho-Millán, Elsa Maribel Aguilar-Medina, José Guillermo Romero-Navarro, Rogelio Sosa-Pérez, Aida Isamar Ruiz-Abitia, Héctor Manuel Cárdenas-Cota, Rosalío Ramos-Payán</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Biofertilizer formulation from Azotobacter_bioinsumos</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Formulación de biofertilizante a partir de aislados regionales de Azotobacter y Azospirillum y su efecto en cultivo de caña de azúcar (Saccharum officinarum) en casa sombra</v>
+      </c>
+      <c r="F133" t="str">
+        <v>2017</v>
+      </c>
+      <c r="G133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Azospirillum, Azotobacter, fijação de nitrógeno, cana-de-açúcar</v>
+      </c>
+      <c r="I133" t="str">
+        <v>O artigo descreve a formulação de biofertilizante a partir de aislados regionais de Azotobacter e Azospirillum e seu efeito no cultivo de cana-de-açúcar em casa de vegetação.</v>
+      </c>
+      <c r="J133" t="str">
+        <v>Artigo de pesquisa</v>
+      </c>
+      <c r="K133" t="str">
+        <v>Mexican Journal of Biotechnology</v>
+      </c>
+      <c r="L133" t="str">
+        <v>Universidade Autônoma de Sinaloa</v>
+      </c>
+      <c r="M133" t="str">
+        <v>Culiacán, Sinaloa, México</v>
+      </c>
+      <c r="N133" t="str">
+        <v>Original Research</v>
+      </c>
+      <c r="O133" t="str">
+        <v>Mexican Journal of Biotechnology</v>
+      </c>
+      <c r="P133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q133" t="str">
+        <v>2</v>
+      </c>
+      <c r="R133" t="str">
+        <v>2</v>
+      </c>
+      <c r="S133" t="str">
+        <v>183-195</v>
+      </c>
+      <c r="T133" t="str">
+        <v>https://doi.org/10.29267/mxjb.2017.2.2.183</v>
+      </c>
+      <c r="U133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W133" t="str">
+        <v>Biofertilizer formulation from Azotobacter_bioinsumos.pdf</v>
+      </c>
+      <c r="X133" t="str">
+        <v/>
+      </c>
+      <c r="Y133" t="str">
+        <v/>
+      </c>
+      <c r="Z133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF133" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG133" t="str">
+        <v/>
+      </c>
+      <c r="AH133" t="str">
+        <v/>
+      </c>
+      <c r="AI133" t="str">
+        <v/>
+      </c>
+      <c r="AJ133" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v/>
+      </c>
+      <c r="B134" t="str">
+        <v/>
+      </c>
+      <c r="C134" t="str">
+        <v>Lu Z, Xie GJ, Khan Q, Qin Y, Huang YY, Guo DJ, Yang TT, Yang LT, Xing YX, Li YR, Wang Z</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Burkholderia strains enhance the tolerance of sugarcane to aluminum stress_bioinsumos</v>
+      </c>
+      <c r="E134" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F134" t="str">
+        <v>2025</v>
+      </c>
+      <c r="G134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Burkholderia; Saccharum officinarum; aluminum stress; physiological adaptation; aluminum tolerant gene</v>
+      </c>
+      <c r="I134" t="str">
+        <v>A pesquisa visa explorar as respostas microbianas do solo de cana-de-açúcar à toxicidade do alumínio e investigar seu papel em aliviar a toxicidade do alumínio à cana-de-açúcar.</v>
+      </c>
+      <c r="J134" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K134" t="str">
+        <v>Chinese Journal of Plant Ecology</v>
+      </c>
+      <c r="L134" t="str">
+        <v>Guangxi University</v>
+      </c>
+      <c r="M134" t="str">
+        <v>Nanning, China</v>
+      </c>
+      <c r="N134" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O134" t="str">
+        <v>植物生态学报</v>
+      </c>
+      <c r="P134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q134" t="str">
+        <v>49</v>
+      </c>
+      <c r="R134" t="str">
+        <v>3</v>
+      </c>
+      <c r="S134" t="str">
+        <v>475-487</v>
+      </c>
+      <c r="T134" t="str">
+        <v>10.17521/cjpe.2024.0014</v>
+      </c>
+      <c r="U134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W134" t="str">
+        <v>Burkholderia strains enhance the tolerance of sugarcane to aluminum stress_bioinsumos.pdf</v>
+      </c>
+      <c r="X134" t="str">
+        <v/>
+      </c>
+      <c r="Y134" t="str">
+        <v/>
+      </c>
+      <c r="Z134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF134" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG134" t="str">
+        <v/>
+      </c>
+      <c r="AH134" t="str">
+        <v/>
+      </c>
+      <c r="AI134" t="str">
+        <v/>
+      </c>
+      <c r="AJ134" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v/>
+      </c>
+      <c r="B135" t="str">
+        <v/>
+      </c>
+      <c r="C135" t="str">
+        <v>Massimiliano De Antoni Migliorati, Stephen Leo, Graeme J. Millar, Michael J. Bell, Alice Strazzabosco, Peter R. Grace</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Can_zeolites_be_used_in_sugarcane_cropping_systems_bioinsumos</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Avaliação da eficácia de zeólitos naturais e tratados em aumentar a recuperação de nitrogênio em cana-de-açúcar</v>
+      </c>
+      <c r="F135" t="str">
+        <v>2024</v>
+      </c>
+      <c r="G135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H135" t="str">
+        <v>Nitrogênio, uso eficiente, perda de nitrogênio, qualidade da água, fertilização, 15N, isótopo estável</v>
+      </c>
+      <c r="I135" t="str">
+        <v>Este estudo avaliou a eficácia de zeólitos naturais e tratados em aumentar a recuperação de nitrogênio em cana-de-açúcar em condições de alta perda de nitrogênio.</v>
+      </c>
+      <c r="J135" t="str">
+        <v>Artigo de pesquisa</v>
+      </c>
+      <c r="K135" t="str">
+        <v>Springer Nature</v>
+      </c>
+      <c r="L135" t="str">
+        <v>Departamento de Meio Ambiente, Ciência e Inovação, Governo da Queensland, Austrália</v>
+      </c>
+      <c r="M135" t="str">
+        <v>Brisbane, QLD 4000, Austrália</v>
+      </c>
+      <c r="N135" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O135" t="str">
+        <v>Plant Soil</v>
+      </c>
+      <c r="P135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q135" t="str">
+        <v>1</v>
+      </c>
+      <c r="R135" t="str">
+        <v>3</v>
+      </c>
+      <c r="S135" t="str">
+        <v>575–592</v>
+      </c>
+      <c r="T135" t="str">
+        <v>10.1007/s11104-024-06643-5</v>
+      </c>
+      <c r="U135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W135" t="str">
+        <v>Can_zeolites_be_used_in_sugarcane_cropping_systems_bioinsumos.pdf</v>
+      </c>
+      <c r="X135" t="str">
+        <v/>
+      </c>
+      <c r="Y135" t="str">
+        <v/>
+      </c>
+      <c r="Z135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA135" t="str">
+        <v>Cromatografia gasosa, 15N-enriquecida, Análise de isótopos estáveis</v>
+      </c>
+      <c r="AB135" t="str">
+        <v>Nitrogênio, Potássio, Enxofre</v>
+      </c>
+      <c r="AC135" t="str">
+        <v>Fertilização com ureia enriquecida com 15N</v>
+      </c>
+      <c r="AD135" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE135" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF135" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG135" t="str">
+        <v/>
+      </c>
+      <c r="AH135" t="str">
+        <v/>
+      </c>
+      <c r="AI135" t="str">
+        <v/>
+      </c>
+      <c r="AJ135" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v/>
+      </c>
+      <c r="B136" t="str">
+        <v/>
+      </c>
+      <c r="C136" t="str">
+        <v>Jose M. Leite, Pavithra S. Pitumpe Arachchige, Ignacio A. Ciampitti, Ganga M. Hettiarachchi, Leila Maurmann, Paulo.C.O. Trivelin, P.V. Vara Prasad, S.V. John Sunoj</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Coaddition of humic substances and humic_bioinsumos</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Efeitos da aplicação foliar de ácidos húmicos e substâncias húmicas combinados com ureia na eficiência de uso de nitrogênio e resposta de diferentes características biométricas, bioquímicas e fisiológicas da cana-de-açúcar</v>
+      </c>
+      <c r="F136" t="str">
+        <v>2020</v>
+      </c>
+      <c r="G136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Cana-de-açúcar, Ureia, Substâncias húmicas, Ácidos húmicos, Eficiência de uso de nitrogênio, Manejo de água agrícola, Agronomia, Biomassa de culturas, Produção de culturas, Proteção de culturas, Qualidade de culturas, Produtividade de culturas, Culturas de campo, Biologia de plantas</v>
+      </c>
+      <c r="I136" t="str">
+        <v>A co-aplicação de substâncias húmicas e ácidos húmicos com ureia melhora a eficiência de uso de nitrogênio foliar em cana-de-açúcar.</v>
+      </c>
+      <c r="J136" t="str">
+        <v>Artigo de pesquisa</v>
+      </c>
+      <c r="K136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L136" t="str">
+        <v>Kansas State University, Universidade de São Paulo</v>
+      </c>
+      <c r="M136" t="str">
+        <v>Manhattan, Kansas, USA; Piracicaba, Brasil</v>
+      </c>
+      <c r="N136" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W136" t="str">
+        <v>Coaddition of humic substances and humic_bioinsumos.pdf</v>
+      </c>
+      <c r="X136" t="str">
+        <v/>
+      </c>
+      <c r="Y136" t="str">
+        <v/>
+      </c>
+      <c r="Z136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF136" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG136" t="str">
+        <v/>
+      </c>
+      <c r="AH136" t="str">
+        <v/>
+      </c>
+      <c r="AI136" t="str">
+        <v/>
+      </c>
+      <c r="AJ136" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v/>
+      </c>
+      <c r="B137" t="str">
+        <v/>
+      </c>
+      <c r="C137" t="str">
+        <v>Ahmad Nuruddin Khoiri, Supapon Cheevadhanarak, Jiraporn Jirakkakul, Sudarat Dulsawat, Peerada Prommeenate, Anuwat Tachaleat, Kanthida Kusonmano, Songsak Wattanachaisaereekul, Sawannee Sutheeworapong</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Comparative Metagenomics Reveals Microbial_bioinsumos</v>
+      </c>
+      <c r="E137" t="str">
+        <v>Comparative Metagenomics Reveals Microbial Signatures of Sugarcane Phyllosphere in Organic Management</v>
+      </c>
+      <c r="F137" t="str">
+        <v>2021</v>
+      </c>
+      <c r="G137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H137" t="str">
+        <v>agricultural shift, microbial signatures, phyllosphere, sugarcane, farming practices</v>
+      </c>
+      <c r="I137" t="str">
+        <v>Este estudo investigou os efeitos do manejo agrícola, incluindo orgânico, transição e convencional, na estrutura e função da comunidade microbiana da folha de cana usando a abordagem de metagenômica por tiro ao alvo.</v>
+      </c>
+      <c r="J137" t="str">
+        <v>Artigo de Pesquisa</v>
+      </c>
+      <c r="K137" t="str">
+        <v>Frontiers in Microbiology</v>
+      </c>
+      <c r="L137" t="str">
+        <v>King Mongkut’s University of Technology Thonburi, Bangkok, Thailand</v>
+      </c>
+      <c r="M137" t="str">
+        <v>Bangkok, Thailand</v>
+      </c>
+      <c r="N137" t="str">
+        <v>Original Research</v>
+      </c>
+      <c r="O137" t="str">
+        <v>Frontiers in Microbiology</v>
+      </c>
+      <c r="P137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q137" t="str">
+        <v>12</v>
+      </c>
+      <c r="R137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T137" t="str">
+        <v>10.3389/fmicb.2021.623799</v>
+      </c>
+      <c r="U137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W137" t="str">
+        <v>Comparative Metagenomics Reveals Microbial_bioinsumos.pdf</v>
+      </c>
+      <c r="X137" t="str">
+        <v/>
+      </c>
+      <c r="Y137" t="str">
+        <v/>
+      </c>
+      <c r="Z137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA137" t="str">
+        <v>Metagenômica por tiro ao alvo, Análise comparativa de metagenoma</v>
+      </c>
+      <c r="AB137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC137" t="str">
+        <v>Manejo orgânico, Transição, Manejo convencional</v>
+      </c>
+      <c r="AD137" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE137" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF137" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG137" t="str">
+        <v/>
+      </c>
+      <c r="AH137" t="str">
+        <v/>
+      </c>
+      <c r="AI137" t="str">
+        <v/>
+      </c>
+      <c r="AJ137" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v/>
+      </c>
+      <c r="B138" t="str">
+        <v/>
+      </c>
+      <c r="C138" t="str">
+        <v>Dao-Jun Guo, Dong-Ping Li, Rajesh Kumar Singh, Pratiksha Singh, Krishan K. Verma, Anjney Sharma, Ying Qin, Qaisar Khan, Xiu-Peng Song, Mukesh K. Malviya, Yong-Xiu Xing &amp; Yang-Rui Li</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Comparative transcriptome analysis of two sugarcane_bioinsumos</v>
+      </c>
+      <c r="E138" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F138" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G138" t="str">
+        <v>3086</v>
+      </c>
+      <c r="H138" t="str">
+        <v>Enterobacter roggenkampii ED5, endophyte, N- fixação, PGPB, cana-de-açúcar, análise de transcriptoma</v>
+      </c>
+      <c r="I138" t="str">
+        <v>Esta pesquisa analisou a resposta de duas variedades de cana-de-açúcar ao endofito diazotrófico Enterobacter roggenkampii ED5, utilizando a tecnologia de sequenciamento de RNA.</v>
+      </c>
+      <c r="J138" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K138" t="str">
+        <v>Taylor &amp; Francis Group</v>
+      </c>
+      <c r="L138" t="str">
+        <v>Guangxi University, Chinese Academy of Agricultural Sciences</v>
+      </c>
+      <c r="M138" t="str">
+        <v>Nanning, People’s Republic of China</v>
+      </c>
+      <c r="N138" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O138" t="str">
+        <v>Journal of Plant Interactions</v>
+      </c>
+      <c r="P138" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q138" t="str">
+        <v>17</v>
+      </c>
+      <c r="R138" t="str">
+        <v>1</v>
+      </c>
+      <c r="S138" t="str">
+        <v>75-84</v>
+      </c>
+      <c r="T138" t="str">
+        <v>10.1080/17429145.2021.2012608</v>
+      </c>
+      <c r="U138" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V138" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W138" t="str">
+        <v>Comparative transcriptome analysis of two sugarcane_bioinsumos.pdf</v>
+      </c>
+      <c r="X138" t="str">
+        <v/>
+      </c>
+      <c r="Y138" t="str">
+        <v/>
+      </c>
+      <c r="Z138" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA138" t="str">
+        <v>RNA sequencing, qRT-PCR</v>
+      </c>
+      <c r="AB138" t="str">
+        <v>Nitrogênio, Amônia</v>
+      </c>
+      <c r="AC138" t="str">
+        <v>Fixação biológica de nitrogênio</v>
+      </c>
+      <c r="AD138" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE138" t="str">
+        <v>Cana-de-açúcar (GT11 e B8)</v>
+      </c>
+      <c r="AF138" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG138" t="str">
+        <v/>
+      </c>
+      <c r="AH138" t="str">
+        <v/>
+      </c>
+      <c r="AI138" t="str">
+        <v/>
+      </c>
+      <c r="AJ138" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v/>
+      </c>
+      <c r="B139" t="str">
+        <v/>
+      </c>
+      <c r="C139" t="str">
+        <v>Juan M. Cohuo-Colli, Juan J. Almaraz-Suarez, Joel Velasco-Velasco, Josafhat Salinas-Ruíz, Arturo Galvis-Spínola, Julián Delgadillo-Martínez</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Compost como fuente de rizobacterias_bioinsumos</v>
+      </c>
+      <c r="E139" t="str">
+        <v>Evaluación del efecto de cepas de rizobacterias aisladas de compost de cachaza y gallinaza en plantas micropropagadas de caña de azúcar durante la aclimatación en invernadero</v>
+      </c>
+      <c r="F139" t="str">
+        <v>2023</v>
+      </c>
+      <c r="G139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Inoculação, colonização, auxinas, cultivo de tejidos, plantas in-vitro</v>
+      </c>
+      <c r="I139" t="str">
+        <v>O compost é uma fonte de microorganismos que podem ter diferentes funções nas plantas. O objetivo foi avaliar o efeito de cepas de rizobacterias isoladas de compost de cachaza e gallinaza em plantas micropropagadas de cana-de-açúcar durante a aclimatação em invernadero.</v>
+      </c>
+      <c r="J139" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K139" t="str">
+        <v>ITEA-Informação Técnica Económica Agraria</v>
+      </c>
+      <c r="L139" t="str">
+        <v>Colegio de Postgraduados, Campus Montecillo</v>
+      </c>
+      <c r="M139" t="str">
+        <v>México</v>
+      </c>
+      <c r="N139" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O139" t="str">
+        <v>ITEA-Inf. Tec. Econ. Agrar.</v>
+      </c>
+      <c r="P139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q139" t="str">
+        <v>119</v>
+      </c>
+      <c r="R139" t="str">
+        <v>4</v>
+      </c>
+      <c r="S139" t="str">
+        <v>327-342</v>
+      </c>
+      <c r="T139" t="str">
+        <v>https://doi.org/10.12706/itea.2023.013</v>
+      </c>
+      <c r="U139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W139" t="str">
+        <v>Compost como fuente de rizobacterias_bioinsumos.pdf</v>
+      </c>
+      <c r="X139" t="str">
+        <v/>
+      </c>
+      <c r="Y139" t="str">
+        <v/>
+      </c>
+      <c r="Z139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF139" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG139" t="str">
+        <v/>
+      </c>
+      <c r="AH139" t="str">
+        <v/>
+      </c>
+      <c r="AI139" t="str">
+        <v/>
+      </c>
+      <c r="AJ139" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v/>
+      </c>
+      <c r="B140" t="str">
+        <v/>
+      </c>
+      <c r="C140" t="str">
+        <v>Ramachandran Muthukumrasamy</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Diazotrophic associations in sugar cane_bioinsumos</v>
+      </c>
+      <c r="E140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F140" t="str">
+        <v>1999</v>
+      </c>
+      <c r="G140" t="str">
+        <v>379</v>
+      </c>
+      <c r="H140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J140" t="str">
+        <v>ARTICLE</v>
+      </c>
+      <c r="K140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L140" t="str">
+        <v>Main Bio-control Research laboratory, Tamil</v>
+      </c>
+      <c r="M140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="N140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S140" t="str">
+        <v>24</v>
+      </c>
+      <c r="T140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W140" t="str">
+        <v>Diazotrophic associations in sugar cane_bioinsumos.pdf</v>
+      </c>
+      <c r="X140" t="str">
+        <v/>
+      </c>
+      <c r="Y140" t="str">
+        <v/>
+      </c>
+      <c r="Z140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD140" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE140" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AG140" t="str">
+        <v/>
+      </c>
+      <c r="AH140" t="str">
+        <v/>
+      </c>
+      <c r="AI140" t="str">
+        <v/>
+      </c>
+      <c r="AJ140" t="str">
+        <v>citros e cana</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v/>
+      </c>
+      <c r="B141" t="str">
+        <v/>
+      </c>
+      <c r="C141" t="str">
+        <v>Guo D-J, Li D-P, Singh RK, Singh P, Sharma A, Verma KK, Qin Y, Khan Q, Lu Z, Malviya MK, Song X-P, Xing Y-X and Li Y-R</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Differential Protein Expression Analysis_bioinsumos</v>
+      </c>
+      <c r="E141" t="str">
+        <v>Differential Protein Expression Analysis of Two Sugarcane Varieties in Response to Diazotrophic Plant Growth-Promoting Endophyte Enterobacter roggenkampii ED5</v>
+      </c>
+      <c r="F141" t="str">
+        <v>2021</v>
+      </c>
+      <c r="G141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H141" t="str">
+        <v>Enterobacter roggenkampii ED5, endophyte, N-ﬁxation, PGP, proteome, sugarcane, TMT</v>
+      </c>
+      <c r="I141" t="str">
+        <v>O artigo descreve a análise de expressão de proteínas em duas variedades de cana-de-açúcar em resposta à inoculação com o endofito diazotrófico Enterobacter roggenkampii ED5.</v>
+      </c>
+      <c r="J141" t="str">
+        <v>Artigo de pesquisa</v>
+      </c>
+      <c r="K141" t="str">
+        <v>Frontiers in Plant Science</v>
+      </c>
+      <c r="L141" t="str">
+        <v>Guangxi University, Nanning, China</v>
+      </c>
+      <c r="M141" t="str">
+        <v>Nanning, China</v>
+      </c>
+      <c r="N141" t="str">
+        <v>Original Research</v>
+      </c>
+      <c r="O141" t="str">
+        <v>Frontiers in Plant Science</v>
+      </c>
+      <c r="P141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q141" t="str">
+        <v>12</v>
+      </c>
+      <c r="R141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T141" t="str">
+        <v>10.3389/fpls.2021.727741</v>
+      </c>
+      <c r="U141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W141" t="str">
+        <v>Differential Protein Expression Analysis_bioinsumos.pdf</v>
+      </c>
+      <c r="X141" t="str">
+        <v/>
+      </c>
+      <c r="Y141" t="str">
+        <v/>
+      </c>
+      <c r="Z141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA141" t="str">
+        <v>Tandem Mass Tags (TMT), liquid chromatography-tandem mass spectrometry (LC-MS/MS)</v>
+      </c>
+      <c r="AB141" t="str">
+        <v>Nitrogênio</v>
+      </c>
+      <c r="AC141" t="str">
+        <v>Inoculação com Enterobacter roggenkampii ED5</v>
+      </c>
+      <c r="AD141" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE141" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF141" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à inoculação com Enterobacter roggenkampii ED5.</v>
+      </c>
+      <c r="AG141" t="str">
+        <v/>
+      </c>
+      <c r="AH141" t="str">
+        <v/>
+      </c>
+      <c r="AI141" t="str">
+        <v/>
+      </c>
+      <c r="AJ141" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v/>
+      </c>
+      <c r="B142" t="str">
+        <v/>
+      </c>
+      <c r="C142" t="str">
+        <v>J.E.L. Antunes, M.C.C.P. Lyra, F.J. Ollero, A.D.S. Freitas, L.M.S. Oliveira, A.S.F. Araújo e M.V. B. Figueiredo</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Diversity of plant growt_bioinsumos</v>
+      </c>
+      <c r="E142" t="str">
+        <v>Caracterização molecular de isolados endofíticos de cana-de-açúcar</v>
+      </c>
+      <c r="F142" t="str">
+        <v>2017</v>
+      </c>
+      <c r="G142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H142" t="str">
+        <v>Bactérias endofíticas, BOX-PCR, Diversidade genética, Fixação biológica de nitrogênio, Gene 16S rRNA</v>
+      </c>
+      <c r="I142" t="str">
+        <v>Esta pesquisa avaliou a diversidade de bactérias promotoras de crescimento associadas à cana-de-açúcar que podem ser usadas como inoculante para a cultura. Foram avaliadas as variedades de cana-de-açúcar RB 867515, RB 1011 e RB 92579. A técnica de BOX-PCR foi usada para diferenciar os isolados e realizar a sequenciação do gene 16S rRNA.</v>
+      </c>
+      <c r="J142" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="M142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="N142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T142" t="str">
+        <v>http://dx.doi.org/10.4238/gmr16029662</v>
+      </c>
+      <c r="U142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W142" t="str">
+        <v>Diversity of plant growt_bioinsumos.pdf</v>
+      </c>
+      <c r="X142" t="str">
+        <v/>
+      </c>
+      <c r="Y142" t="str">
+        <v/>
+      </c>
+      <c r="Z142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF142" t="str">
+        <v>Aprovado: Detalha a diversidade de bactérias promotoras de crescimento associadas à cana-de-açúcar.</v>
+      </c>
+      <c r="AG142" t="str">
+        <v/>
+      </c>
+      <c r="AH142" t="str">
+        <v/>
+      </c>
+      <c r="AI142" t="str">
+        <v/>
+      </c>
+      <c r="AJ142" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v/>
+      </c>
+      <c r="B143" t="str">
+        <v/>
+      </c>
+      <c r="C143" t="str">
+        <v>Jennifer Martínez-Ballesteros, Odón Castañeda-Castro, Juan Valente Hidalgo-Contreras y Fernando C. Gómez-Merino</v>
+      </c>
+      <c r="D143" t="str">
+        <v>EFECTOS BIOESTIMULANTES DEL ALUMINIO EN CRECIMIENTO_bioinsumos</v>
+      </c>
+      <c r="E143" t="str">
+        <v>BIOSTIMULATING EFFECTS OF ALUMINUM ON GROWTH AND METABOLISM OF SUGARCANE in vitro</v>
+      </c>
+      <c r="F143" t="str">
+        <v>2023</v>
+      </c>
+      <c r="G143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H143" t="str">
+        <v>Saccharum, bioestimulação inorgânica, elementos benéficos, Poaceae, vitroplantas</v>
+      </c>
+      <c r="I143" t="str">
+        <v>O aluminio (Al 3+) é um elemento benéfico que, em baixas doses, pode promover o crescimento, desenvolvimento e metabolismo em plantas. Esta pesquisa avaliou o efeito do aluminio (Al 3+) em indicadores de crescimento e bioquímicos em variedades de cana-de-açúcar (Saccharum spp.) Mex 69-290 e CP 72-2086, durante a etapa de multiplicação em condições de cultivo in vitro.</v>
+      </c>
+      <c r="J143" t="str">
+        <v>Artigo Científico</v>
+      </c>
+      <c r="K143" t="str">
+        <v>Rev. Fitotec. Mex.</v>
+      </c>
+      <c r="L143" t="str">
+        <v>Colegio de Postgraduados (CP), Campus Córdoba, Amatlán de los Reyes, Veracruz, México.</v>
+      </c>
+      <c r="M143" t="str">
+        <v>México</v>
+      </c>
+      <c r="N143" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O143" t="str">
+        <v>Revista Fitotecnica Mexicana</v>
+      </c>
+      <c r="P143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q143" t="str">
+        <v>46</v>
+      </c>
+      <c r="R143" t="str">
+        <v>2</v>
+      </c>
+      <c r="S143" t="str">
+        <v>177-186</v>
+      </c>
+      <c r="T143" t="str">
+        <v>https://doi.org/10.35196/rfm.2023.2.177</v>
+      </c>
+      <c r="U143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W143" t="str">
+        <v>EFECTOS BIOESTIMULANTES DEL ALUMINIO EN CRECIMIENTO_bioinsumos.pdf</v>
+      </c>
+      <c r="X143" t="str">
+        <v/>
+      </c>
+      <c r="Y143" t="str">
+        <v/>
+      </c>
+      <c r="Z143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF143" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG143" t="str">
+        <v/>
+      </c>
+      <c r="AH143" t="str">
+        <v/>
+      </c>
+      <c r="AI143" t="str">
+        <v/>
+      </c>
+      <c r="AJ143" t="str">
+        <v>citros e cana</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v/>
+      </c>
+      <c r="B144" t="str">
+        <v/>
+      </c>
+      <c r="C144" t="str">
+        <v>Shaheen Asad, Muhammad Arshad, Shahid Mansoor e Yusuf Zafar</v>
+      </c>
+      <c r="D144" t="str">
+        <v>EFFECT OF VARIOUS AMINO ACIDS ON SHOOT REGENERATION OF SUGARCANE_bioinsumos</v>
+      </c>
+      <c r="E144" t="str">
+        <v>Desenvolvimento de um protocolo de regeneração eficiente para cana-de-açúcar</v>
+      </c>
+      <c r="F144" t="str">
+        <v>2009</v>
+      </c>
+      <c r="G144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H144" t="str">
+        <v>Saccharum officinarum L, amino acids, embryogenic calli, plant regeneration, 2, 4 dichlorophenoxyacetic acid</v>
+      </c>
+      <c r="I144" t="str">
+        <v>Este estudo desenvolveu um protocolo de regeneração eficiente para cana-de-açúcar (Saccharum officinarum L.) utilizando aminoácidos em meio de regeneração.</v>
+      </c>
+      <c r="J144" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K144" t="str">
+        <v>African Journal of Biotechnology</v>
+      </c>
+      <c r="L144" t="str">
+        <v>National Institute for Biotechnology and Genetic Engineering (NIBGE)</v>
+      </c>
+      <c r="M144" t="str">
+        <v>Faisalabad, Paquistão</v>
+      </c>
+      <c r="N144" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O144" t="str">
+        <v>African Journal of Biotechnology</v>
+      </c>
+      <c r="P144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q144" t="str">
+        <v>8</v>
+      </c>
+      <c r="R144" t="str">
+        <v>7</v>
+      </c>
+      <c r="S144" t="str">
+        <v>1214-1218</v>
+      </c>
+      <c r="T144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W144" t="str">
+        <v>EFFECT OF VARIOUS AMINO ACIDS ON SHOOT REGENERATION OF SUGARCANE_bioinsumos.pdf</v>
+      </c>
+      <c r="X144" t="str">
+        <v/>
+      </c>
+      <c r="Y144" t="str">
+        <v/>
+      </c>
+      <c r="Z144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA144" t="str">
+        <v>Cultivo de tecidos, Regeneração de plantas, Somatic embryogenesis, 2, 4-Dichlorophenoxyacético ácido</v>
+      </c>
+      <c r="AB144" t="str">
+        <v>Glutamina, Asparagina, Glicina, Cisteína, Arginina</v>
+      </c>
+      <c r="AC144" t="str">
+        <v>Suplementação de aminoácidos no meio de regeneração</v>
+      </c>
+      <c r="AD144" t="str">
+        <v>Grandes culturas</v>
+      </c>
+      <c r="AE144" t="str">
+        <v>Cana-de-açúcar (Saccharum officinarum L.)</v>
+      </c>
+      <c r="AF144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AG144" t="str">
+        <v/>
+      </c>
+      <c r="AH144" t="str">
+        <v/>
+      </c>
+      <c r="AI144" t="str">
+        <v/>
+      </c>
+      <c r="AJ144" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v/>
+      </c>
+      <c r="B145" t="str">
+        <v/>
+      </c>
+      <c r="C145" t="str">
+        <v>Djajadi, R Syaputra e S N Hidayati</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Effect of NPK fertilizer_bioinsumos</v>
+      </c>
+      <c r="E145" t="str">
+        <v>Investigação do efeito de fertilizantes NPK, biofertilizantes e adubo verde de C. juncea na absorção de nutrientes e crescimento da cana-de-açúcar</v>
+      </c>
+      <c r="F145" t="str">
+        <v>2020</v>
+      </c>
+      <c r="G145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H145" t="str">
+        <v>Biofertilizante, adubo verde, fertilizante inorgânico, cana-de-açúcar, nutrientes</v>
+      </c>
+      <c r="I145" t="str">
+        <v>A pesquisa investigou o efeito de fertilizantes NPK, biofertilizantes e adubo verde de C. juncea na absorção de nutrientes e crescimento da cana-de-açúcar.</v>
+      </c>
+      <c r="J145" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K145" t="str">
+        <v>IOP Publishing</v>
+      </c>
+      <c r="L145" t="str">
+        <v>Indonesian Sweetener and Fiber Crops Research Institute</v>
+      </c>
+      <c r="M145" t="str">
+        <v>Malang</v>
+      </c>
+      <c r="N145" t="str">
+        <v>Pesquisa de campo</v>
+      </c>
+      <c r="O145" t="str">
+        <v>IOP Conference Series: Earth and Environmental Science</v>
+      </c>
+      <c r="P145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q145" t="str">
+        <v>418</v>
+      </c>
+      <c r="R145" t="str">
+        <v>1</v>
+      </c>
+      <c r="S145" t="str">
+        <v>012068</v>
+      </c>
+      <c r="T145" t="str">
+        <v>10.1088/1755-1315/418/1/012068</v>
+      </c>
+      <c r="U145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W145" t="str">
+        <v>Effect of NPK fertilizer_bioinsumos.pdf</v>
+      </c>
+      <c r="X145" t="str">
+        <v/>
+      </c>
+      <c r="Y145" t="str">
+        <v/>
+      </c>
+      <c r="Z145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AG145" t="str">
+        <v/>
+      </c>
+      <c r="AH145" t="str">
+        <v/>
+      </c>
+      <c r="AI145" t="str">
+        <v/>
+      </c>
+      <c r="AJ145" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v/>
+      </c>
+      <c r="B146" t="str">
+        <v/>
+      </c>
+      <c r="C146" t="str">
+        <v>S.K. THAKUR, C.K. JHA, GEETA KUMARI AND V.P. SINGH</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Effect of Trichoderma inoculated trash_bioinsumos</v>
+      </c>
+      <c r="E146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F146" t="str">
+        <v>2010</v>
+      </c>
+      <c r="G146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H146" t="str">
+        <v>Biofertilizer, Soil properties, Sugarcane, Trash, Trichoderma</v>
+      </c>
+      <c r="I146" t="str">
+        <v>O estudo avaliou o efeito do trigo inoculado com Trichoderma, nível de nitrogênio e biofertilizante na performance da cana-de-açúcar em solos calcários do Bihar.</v>
+      </c>
+      <c r="J146" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K146" t="str">
+        <v>Indian Journal of Agronomy</v>
+      </c>
+      <c r="L146" t="str">
+        <v>Sugarcane Research Institute, Pusa, Bihar</v>
+      </c>
+      <c r="M146" t="str">
+        <v>Pusa, Samastipur, Bihar</v>
+      </c>
+      <c r="N146" t="str">
+        <v>Experimento de campo</v>
+      </c>
+      <c r="O146" t="str">
+        <v>Indian Journal of Agronomy</v>
+      </c>
+      <c r="P146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q146" t="str">
+        <v>55</v>
+      </c>
+      <c r="R146" t="str">
+        <v>4</v>
+      </c>
+      <c r="S146" t="str">
+        <v>308-311</v>
+      </c>
+      <c r="T146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W146" t="str">
+        <v>Effect of Trichoderma inoculated trash_bioinsumos.pdf</v>
+      </c>
+      <c r="X146" t="str">
+        <v/>
+      </c>
+      <c r="Y146" t="str">
+        <v/>
+      </c>
+      <c r="Z146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA146" t="str">
+        <v>Trichoderma inoculado, análise de solo, fertilizantes, biofertilizante</v>
+      </c>
+      <c r="AB146" t="str">
+        <v>Nitrogênio, Fósforo, Potássio</v>
+      </c>
+      <c r="AC146" t="str">
+        <v>Fertilizantes químicos, biofertilizante</v>
+      </c>
+      <c r="AD146" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE146" t="str">
+        <v>Cana-de-açúcar (Saccharum officinarum L.)</v>
+      </c>
+      <c r="AF146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AG146" t="str">
+        <v/>
+      </c>
+      <c r="AH146" t="str">
+        <v/>
+      </c>
+      <c r="AI146" t="str">
+        <v/>
+      </c>
+      <c r="AJ146" t="str">
+        <v>citros e cana</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v/>
+      </c>
+      <c r="B147" t="str">
+        <v/>
+      </c>
+      <c r="C147" t="str">
+        <v>KEYA BANERJEE, A.M. PUSTE, S.K. GUNRI, K. JANA, MANASHI BARMAN</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Effect of integrated nutrient management on growth_bioinsumos</v>
+      </c>
+      <c r="E147" t="str">
+        <v>Efeito da gestão integrada de nutrientes na crescimento, produção, qualidade e saúde do solo de cana-de-açúcar (Saccharum officinarum) plantada na primavera no oeste da Bengala</v>
+      </c>
+      <c r="F147" t="str">
+        <v>2018</v>
+      </c>
+      <c r="G147" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H147" t="str">
+        <v>Biofertilizante, Esterco de granja, Fertilizante inorgânico, Qualidade do suco, Produtividade, Saúde do solo</v>
+      </c>
+      <c r="I147" t="str">
+        <v>Uma experiência foi realizada durante 3 temporadas de cultivo consecutivas de 2013-14, 2014-15 e 2015-16 em Bethuadahari, Nadia, Bengala Ocidental, para avaliar o efeito de adubos orgânicos e biofertilizantes em combinação com fertilizantes inorgânicos como fonte de nitrogênio (N) no crescimento, atributos de produção, rendimento de cana, qualidade do suco, conteúdo de nutrientes foliares e clorofila, e saúde do solo após a colheita de cana-de-açúcar (Saccharum spp. Complexo híbrido) (cv. CoB 94164).</v>
+      </c>
+      <c r="J147" t="str">
+        <v>Artigo de pesquisa</v>
+      </c>
+      <c r="K147" t="str">
+        <v>Indian Journal of Agronomy</v>
+      </c>
+      <c r="L147" t="str">
+        <v>Sugarcane Research Station, Bethuadahari, Nadia, Bengala Ocidental</v>
+      </c>
+      <c r="M147" t="str">
+        <v>Bethuadahari, Nadia, Bengala Ocidental</v>
+      </c>
+      <c r="N147" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O147" t="str">
+        <v>Indian Journal of Agronomy</v>
+      </c>
+      <c r="P147" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q147" t="str">
+        <v>63</v>
+      </c>
+      <c r="R147" t="str">
+        <v>4</v>
+      </c>
+      <c r="S147" t="str">
+        <v>499-505</v>
+      </c>
+      <c r="T147" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U147" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V147" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W147" t="str">
+        <v>Effect of integrated nutrient management on growth_bioinsumos.pdf</v>
+      </c>
+      <c r="X147" t="str">
+        <v/>
+      </c>
+      <c r="Y147" t="str">
+        <v/>
+      </c>
+      <c r="Z147" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA147" t="str">
+        <v>Cromatografia gasosa, Análise de solo, Análise de nutrientes foliares, Análise de clorofila</v>
+      </c>
+      <c r="AB147" t="str">
+        <v>Nitrogênio, Fósforo, Potássio, Enxofre</v>
+      </c>
+      <c r="AC147" t="str">
+        <v>Fertirrigação, Aplicação foliar, Controle de pragas, Poda</v>
+      </c>
+      <c r="AD147" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE147" t="str">
+        <v>Cana-de-açúcar (Saccharum officinarum)</v>
+      </c>
+      <c r="AF147" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG147" t="str">
+        <v/>
+      </c>
+      <c r="AH147" t="str">
+        <v/>
+      </c>
+      <c r="AI147" t="str">
+        <v/>
+      </c>
+      <c r="AJ147" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v/>
+      </c>
+      <c r="B148" t="str">
+        <v/>
+      </c>
+      <c r="C148" t="str">
+        <v>Ryan T. Sarimong, Pearl B. Sanchez, Rodrigo B. Badayos, Erlinda S. Paterno e Pompe C. Sta. Cruz</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Effect of organic amendments and microbial inoculant_bioinsumos</v>
+      </c>
+      <c r="E148" t="str">
+        <v>Uso Integrado de Materiais Orgânicos e Inoculante Microbiano na Produção de Cana-de-Açúcar</v>
+      </c>
+      <c r="F148" t="str">
+        <v>2017</v>
+      </c>
+      <c r="G148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H148" t="str">
+        <v>adubos orgânicos, inoculante microbiano, eficiência de uso de nutrientes</v>
+      </c>
+      <c r="I148" t="str">
+        <v>O estudo avaliou o efeito de adubos orgânicos e inoculante microbiano na eficiência de uso de nitrogênio, fósforo e potássio da cana-de-açúcar em solo ácido.</v>
+      </c>
+      <c r="J148" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L148" t="str">
+        <v>Universidade de Filipinas</v>
+      </c>
+      <c r="M148" t="str">
+        <v>Filipinas</v>
+      </c>
+      <c r="N148" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O148" t="str">
+        <v>J. ISSAAS</v>
+      </c>
+      <c r="P148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q148" t="str">
+        <v>23</v>
+      </c>
+      <c r="R148" t="str">
+        <v>2</v>
+      </c>
+      <c r="S148" t="str">
+        <v>114-124</v>
+      </c>
+      <c r="T148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W148" t="str">
+        <v>Effect of organic amendments and microbial inoculant_bioinsumos.pdf</v>
+      </c>
+      <c r="X148" t="str">
+        <v/>
+      </c>
+      <c r="Y148" t="str">
+        <v/>
+      </c>
+      <c r="Z148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF148" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG148" t="str">
+        <v/>
+      </c>
+      <c r="AH148" t="str">
+        <v/>
+      </c>
+      <c r="AI148" t="str">
+        <v/>
+      </c>
+      <c r="AJ148" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v/>
+      </c>
+      <c r="B149" t="str">
+        <v/>
+      </c>
+      <c r="C149" t="str">
+        <v>Liu Y, Ma W, He H, Wang Z e Cao Y</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Effects of Sugarcane and Soybean_bioinsumos</v>
+      </c>
+      <c r="E149" t="str">
+        <v>Intercultura de Cana-de-açúcar e Soja</v>
+      </c>
+      <c r="F149" t="str">
+        <v>2021</v>
+      </c>
+      <c r="G149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H149" t="str">
+        <v>cana-de-açúcar, bactérias fixadoras de nitrogênio, intercultura, análise de rede, solo rizosférico</v>
+      </c>
+      <c r="I149" t="str">
+        <v>A intercultura de cana-de-açúcar e soja é amplamente utilizada para aumentar a produção de culturas e promover o desenvolvimento sustentável da indústria de cana-de-açúcar. No entanto, nossa compreensão do ambiente microbiano do solo em sistemas de intercultura, especialmente o efeito das variedades de culturas no solo rizosférico, permanece pobre.</v>
+      </c>
+      <c r="J149" t="str">
+        <v>Artigo de Pesquisa</v>
+      </c>
+      <c r="K149" t="str">
+        <v>Frontiers in Microbiology</v>
+      </c>
+      <c r="L149" t="str">
+        <v>Guangxi University, Guangxi South Subtropical Agricultural Science Research Institute, Guangxi Key Laboratory of Livestock Genetic Improvement</v>
+      </c>
+      <c r="M149" t="str">
+        <v>Nanning, China</v>
+      </c>
+      <c r="N149" t="str">
+        <v>Intercultura de cana-de-açúcar e soja</v>
+      </c>
+      <c r="O149" t="str">
+        <v>Frontiers in Microbiology</v>
+      </c>
+      <c r="P149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q149" t="str">
+        <v>12</v>
+      </c>
+      <c r="R149" t="str">
+        <v>713349</v>
+      </c>
+      <c r="S149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T149" t="str">
+        <v>10.3389/fmicb.2021.713349</v>
+      </c>
+      <c r="U149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W149" t="str">
+        <v>Effects of Sugarcane and Soybean_bioinsumos.pdf</v>
+      </c>
+      <c r="X149" t="str">
+        <v/>
+      </c>
+      <c r="Y149" t="str">
+        <v/>
+      </c>
+      <c r="Z149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF149" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG149" t="str">
+        <v/>
+      </c>
+      <c r="AH149" t="str">
+        <v/>
+      </c>
+      <c r="AI149" t="str">
+        <v/>
+      </c>
+      <c r="AJ149" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v/>
+      </c>
+      <c r="B150" t="str">
+        <v/>
+      </c>
+      <c r="C150" t="str">
+        <v>Fernando Luiz Nunes Oliveira, Newton Pereira Stamford, Djalma Simões Neto, Emídio Cantídio Almeida Oliveira, Wanderson Silva Oliveira, Carolina Etienne de Rosália e Silva Santos</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Effects of biofertilizers produced from rocks_bioinsumos</v>
+      </c>
+      <c r="E150" t="str">
+        <v>Effects of biofertilizers produced from rocks and organic matter, enriched by diazotrophic bacteria inoculation on growth and yield of sugarcane</v>
+      </c>
+      <c r="F150" t="str">
+        <v>2015</v>
+      </c>
+      <c r="G150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H150" t="str">
+        <v>Saccharum spp., earthworm compound, free-living diazotrophic bacteria, sustentable agriculture, organic-mineral fertilization</v>
+      </c>
+      <c r="I150" t="str">
+        <v>O estudo avaliou a eficácia de biofertilizantes produzidos a partir de rochas e matéria orgânica, enriquecidos com bactérias diazotróficas, no crescimento e rendimento da cana-de-açúcar.</v>
+      </c>
+      <c r="J150" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L150" t="str">
+        <v>Universidade Federal Rural de Pernambuco</v>
+      </c>
+      <c r="M150" t="str">
+        <v>Recife, Pernambuco, Brasil</v>
+      </c>
+      <c r="N150" t="str">
+        <v>Pesquisa experimental</v>
+      </c>
+      <c r="O150" t="str">
+        <v>Agricultural Journal of Crop Science</v>
+      </c>
+      <c r="P150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q150" t="str">
+        <v>9</v>
+      </c>
+      <c r="R150" t="str">
+        <v>6</v>
+      </c>
+      <c r="S150" t="str">
+        <v>504-508</v>
+      </c>
+      <c r="T150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W150" t="str">
+        <v>Effects of biofertilizers produced from rocks_bioinsumos.pdf</v>
+      </c>
+      <c r="X150" t="str">
+        <v/>
+      </c>
+      <c r="Y150" t="str">
+        <v/>
+      </c>
+      <c r="Z150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA150" t="str">
+        <v>Biofertilizantes, inoculação de bactérias diazotróficas, experimento em campo</v>
+      </c>
+      <c r="AB150" t="str">
+        <v>Nitrogênio, Fósforo, Potássio</v>
+      </c>
+      <c r="AC150" t="str">
+        <v>Biofertilizantes, Fertilizantes solúveis</v>
+      </c>
+      <c r="AD150" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE150" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF150" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG150" t="str">
+        <v/>
+      </c>
+      <c r="AH150" t="str">
+        <v/>
+      </c>
+      <c r="AI150" t="str">
+        <v/>
+      </c>
+      <c r="AJ150" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v/>
+      </c>
+      <c r="B151" t="str">
+        <v/>
+      </c>
+      <c r="C151" t="str">
+        <v>Suchat Juntahum e Sophon Boonlue</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Efficiency of arbuscular mycorrhiza_bioinsumos</v>
+      </c>
+      <c r="E151" t="str">
+        <v>Um estudo de campo sob condições de chuva</v>
+      </c>
+      <c r="F151" t="str">
+        <v>2015</v>
+      </c>
+      <c r="G151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H151" t="str">
+        <v>Fungos Micorrízicos Arbusculares, Fosfato de Rocha, Cana-de-Açúcar, Crescimento, Produtividade, Nutrientes</v>
+      </c>
+      <c r="I151" t="str">
+        <v>Este estudo investigou o efeito da inoculação de fungos micorrízicos arbusculares (AMF) com fosfato de rocha (RP) na disponibilidade de fósforo no solo, conteúdo de prolina em folhas, uptake de nutrientes principais, biomassa, crescimento e produtividade de cana-de-açúcar.</v>
+      </c>
+      <c r="J151" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L151" t="str">
+        <v>Universidade de Khon Kaen, Tailândia</v>
+      </c>
+      <c r="M151" t="str">
+        <v>Khon Kaen, Tailândia</v>
+      </c>
+      <c r="N151" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W151" t="str">
+        <v>Efficiency of arbuscular mycorrhiza_bioinsumos.pdf</v>
+      </c>
+      <c r="X151" t="str">
+        <v/>
+      </c>
+      <c r="Y151" t="str">
+        <v/>
+      </c>
+      <c r="Z151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF151" t="str">
+        <v>Aprovado: Detalha o efeito da inoculação de fungos micorrízicos arbusculares com fosfato de rocha na disponibilidade de fósforo no solo e na produtividade de cana-de-açúcar.</v>
+      </c>
+      <c r="AG151" t="str">
+        <v/>
+      </c>
+      <c r="AH151" t="str">
+        <v/>
+      </c>
+      <c r="AI151" t="str">
+        <v/>
+      </c>
+      <c r="AJ151" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v/>
+      </c>
+      <c r="B152" t="str">
+        <v/>
+      </c>
+      <c r="C152" t="str">
+        <v>Fernanda Castro Correia Marcos, Raquel de Paula Freitas Iório, Adriana Parada Dias da Silveira, Rafael Vasconcelos Ribeiro, Eduardo Caruso Machado, Ana Maria Magalhães de Andrade Lagôa</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Endophytic bacteria affect sugarcane_bioinsumos</v>
+      </c>
+      <c r="E152" t="str">
+        <v>Evaluating the effects of endophytic bacteria inoculants on sugarcane varieties IACSP94-2094 and IACSP95-5000</v>
+      </c>
+      <c r="F152" t="str">
+        <v>2016</v>
+      </c>
+      <c r="G152" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H152" t="str">
+        <v>Saccharum spp., plant-bacteria interaction, photosynthesis, nitrogen, mini stalks with one bud</v>
+      </c>
+      <c r="I152" t="str">
+        <v>O objetivo deste estudo foi avaliar se o inoculante de bactérias endofíticas seria benéfico para as variedades de cana-de-açúcar IACSP94-2094 e IACSP95-5000, promovendo mudanças na fotossíntese e crescimento das plantas.</v>
+      </c>
+      <c r="J152" t="str">
+        <v>Artigo</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Bragantia</v>
+      </c>
+      <c r="L152" t="str">
+        <v>Universidade de Campinas - Instituto de Biologia</v>
+      </c>
+      <c r="M152" t="str">
+        <v>Campinas (SP), Brasil</v>
+      </c>
+      <c r="N152" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O152" t="str">
+        <v>Bragantia, Campinas</v>
+      </c>
+      <c r="P152" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q152" t="str">
+        <v>75</v>
+      </c>
+      <c r="R152" t="str">
+        <v>1</v>
+      </c>
+      <c r="S152" t="str">
+        <v>1-9</v>
+      </c>
+      <c r="T152" t="str">
+        <v>http://dx.doi.org/10.1590/1678-4499.256</v>
+      </c>
+      <c r="U152" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V152" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W152" t="str">
+        <v>Endophytic bacteria affect sugarcane_bioinsumos.pdf</v>
+      </c>
+      <c r="X152" t="str">
+        <v/>
+      </c>
+      <c r="Y152" t="str">
+        <v/>
+      </c>
+      <c r="Z152" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA152" t="str">
+        <v>Cromatografia gasosa, Fotossíntese líquida, RCBD, ANOVA</v>
+      </c>
+      <c r="AB152" t="str">
+        <v>Nitrogênio, Sacarose</v>
+      </c>
+      <c r="AC152" t="str">
+        <v>Fertirrigação</v>
+      </c>
+      <c r="AD152" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE152" t="str">
+        <v>Cana-de-açúcar (IACSP94-2094 e IACSP95-5000)</v>
+      </c>
+      <c r="AF152" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG152" t="str">
+        <v/>
+      </c>
+      <c r="AH152" t="str">
+        <v/>
+      </c>
+      <c r="AI152" t="str">
+        <v/>
+      </c>
+      <c r="AJ152" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v/>
+      </c>
+      <c r="B153" t="str">
+        <v/>
+      </c>
+      <c r="C153" t="str">
+        <v>Luz K. Medina-Cordoba, Aroon T. Chande, Lavanya Rishishwar, Leonard W. Mayer, Leonardo Mariño-Ramírez, Lina C. Valderrama-Aguirre, Augusto Valderrama-Aguirre, Joel E. Kostka, I. King Jordan</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Genome Sequences of 15 Klebsiella_bioinsumos</v>
+      </c>
+      <c r="E153" t="str">
+        <v>Draft whole-genome sequences for 15 Klebsiella sp. isolates from sugarcane fields in the Cauca Valley of Colombia.</v>
+      </c>
+      <c r="F153" t="str">
+        <v>2018</v>
+      </c>
+      <c r="G153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I153" t="str">
+        <v>Members of the Klebsiella genus promote plant growth. We report here draft whole-genome sequences for 15 Klebsiella sp. isolates from sugarcane fields in the Cauca Valley of Colombia.</v>
+      </c>
+      <c r="J153" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L153" t="str">
+        <v>Georgia Institute of Technology, PanAmerican Bioinformatics Institute, INCAUCA S.A.S., Universidad Libre, National Center for Biotechnology Information, Universidad del Valle</v>
+      </c>
+      <c r="M153" t="str">
+        <v>Atlanta, Georgia, USA, Cali, Valle del Cauca, Colombia, Bethesda, Maryland, USA, Cali, Valle del Cauca, Colombia</v>
+      </c>
+      <c r="N153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O153" t="str">
+        <v>Genome Announc</v>
+      </c>
+      <c r="P153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q153" t="str">
+        <v>6</v>
+      </c>
+      <c r="R153" t="str">
+        <v>12</v>
+      </c>
+      <c r="S153" t="str">
+        <v>e00104-18</v>
+      </c>
+      <c r="T153" t="str">
+        <v>https://doi.org/10.1128/genomeA.00104-18</v>
+      </c>
+      <c r="U153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W153" t="str">
+        <v>Genome Sequences of 15 Klebsiella_bioinsumos.pdf</v>
+      </c>
+      <c r="X153" t="str">
+        <v/>
+      </c>
+      <c r="Y153" t="str">
+        <v/>
+      </c>
+      <c r="Z153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA153" t="str">
+        <v>Cromatografia gasosa, Fotossíntese líquida, RCBD, ANOVA, SPAdes, Trimmomatic, FastQC, RAST</v>
+      </c>
+      <c r="AB153" t="str">
+        <v>Nitrogênio, Fosfato</v>
+      </c>
+      <c r="AC153" t="str">
+        <v>Fertirrigação, Aplicação foliar</v>
+      </c>
+      <c r="AD153" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE153" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF153" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG153" t="str">
+        <v/>
+      </c>
+      <c r="AH153" t="str">
+        <v/>
+      </c>
+      <c r="AI153" t="str">
+        <v/>
+      </c>
+      <c r="AJ153" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v/>
+      </c>
+      <c r="B154" t="str">
+        <v/>
+      </c>
+      <c r="C154" t="str">
+        <v>Nittaya Pitiwittayakula, Pattaraporn Yukphan, Somboon Tanasupawat</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Genome sequence of Acidomonas methanolica CPK2_bioinsumos</v>
+      </c>
+      <c r="E154" t="str">
+        <v>Avaliação das atividades de crescimento de plantas de um bactério endofítico isolado de cana-de-açúcar</v>
+      </c>
+      <c r="F154" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H154" t="str">
+        <v>Acidomonas methanolica, Bactérias endofíticas, Análise de genoma, Ácido indol-3-acético, Promoção de crescimento de plantas</v>
+      </c>
+      <c r="I154" t="str">
+        <v>O artigo descreve a sequência do genoma de Acidomonas methanolica CPK24, uma bactéria endofítica isolada da cana-de-açúcar, que apresenta características de promoção de crescimento de plantas.</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Artigo de pesquisa</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Kasetsart University of Research and Development Institute</v>
+      </c>
+      <c r="L154" t="str">
+        <v>Rajamangala University of Technology Isan, Thailand Bioresource Research Center (TBRC), Chulalongkorn University</v>
+      </c>
+      <c r="M154" t="str">
+        <v>Nakhon Ratchasima, Thailand</v>
+      </c>
+      <c r="N154" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O154" t="str">
+        <v>Agriculture and Natural Resources</v>
+      </c>
+      <c r="P154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q154" t="str">
+        <v>56</v>
+      </c>
+      <c r="R154" t="str">
+        <v>6</v>
+      </c>
+      <c r="S154" t="str">
+        <v>1197–1206</v>
+      </c>
+      <c r="T154" t="str">
+        <v>https://doi.org/10.34044/j.anres.2022.56.6.14</v>
+      </c>
+      <c r="U154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W154" t="str">
+        <v>Genome sequence of Acidomonas methanolica CPK2_bioinsumos.pdf</v>
+      </c>
+      <c r="X154" t="str">
+        <v/>
+      </c>
+      <c r="Y154" t="str">
+        <v/>
+      </c>
+      <c r="Z154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF154" t="str">
+        <v>Aprovado: Detalha a sequência do genoma de Acidomonas methanolica CPK24 e suas características de promoção de crescimento de plantas.</v>
+      </c>
+      <c r="AG154" t="str">
+        <v/>
+      </c>
+      <c r="AH154" t="str">
+        <v/>
+      </c>
+      <c r="AI154" t="str">
+        <v/>
+      </c>
+      <c r="AJ154" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v/>
+      </c>
+      <c r="B155" t="str">
+        <v/>
+      </c>
+      <c r="C155" t="str">
+        <v>D.B.Nakade</v>
+      </c>
+      <c r="D155" t="str">
+        <v>HALOTOLERENT AZOSPIRILLUM LIPOFERUM_bioinsumos</v>
+      </c>
+      <c r="E155" t="str">
+        <v>Estudo da capacidade de fixação de nitrogênio e produção de biofertilizantes</v>
+      </c>
+      <c r="F155" t="str">
+        <v>2013</v>
+      </c>
+      <c r="G155" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H155" t="str">
+        <v>Azospirillum lipoferum N-29, Solo salino, Biofertilizantes</v>
+      </c>
+      <c r="I155" t="str">
+        <v>O estudo apresenta a capacidade de fixação de nitrogênio e produção de biofertilizantes do Azospirillum lipoferum N-29 em solos salinos.</v>
+      </c>
+      <c r="J155" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K155" t="str">
+        <v>Journal of Pure and Applied Microbiology</v>
+      </c>
+      <c r="L155" t="str">
+        <v>Government Rajaram College, Kolhapur - 416 004, India</v>
+      </c>
+      <c r="M155" t="str">
+        <v>Kolhapur, Maharashtra, Índia</v>
+      </c>
+      <c r="N155" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O155" t="str">
+        <v>Journal of Pure and Applied Microbiology</v>
+      </c>
+      <c r="P155" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q155" t="str">
+        <v>7</v>
+      </c>
+      <c r="R155" t="str">
+        <v>1</v>
+      </c>
+      <c r="S155" t="str">
+        <v>795-801</v>
+      </c>
+      <c r="T155" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U155" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V155" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W155" t="str">
+        <v>HALOTOLERENT AZOSPIRILLUM LIPOFERUM_bioinsumos.pdf</v>
+      </c>
+      <c r="X155" t="str">
+        <v/>
+      </c>
+      <c r="Y155" t="str">
+        <v/>
+      </c>
+      <c r="Z155" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA155" t="str">
+        <v>Acetileno redução, Pot experimento, Produção de biofertilizantes em bioreator</v>
+      </c>
+      <c r="AB155" t="str">
+        <v>Nitrogênio</v>
+      </c>
+      <c r="AC155" t="str">
+        <v>Biofertilizantes</v>
+      </c>
+      <c r="AD155" t="str">
+        <v>Grandes culturas</v>
+      </c>
+      <c r="AE155" t="str">
+        <v>Caná-de-açúcar</v>
+      </c>
+      <c r="AF155" t="str">
+        <v>Aprovado: Detalha a capacidade de fixação de nitrogênio e produção de biofertilizantes do Azospirillum lipoferum N-29 em solos salinos.</v>
+      </c>
+      <c r="AG155" t="str">
+        <v/>
+      </c>
+      <c r="AH155" t="str">
+        <v/>
+      </c>
+      <c r="AI155" t="str">
+        <v/>
+      </c>
+      <c r="AJ155" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v/>
+      </c>
+      <c r="B156" t="str">
+        <v/>
+      </c>
+      <c r="C156" t="str">
+        <v>Pirhadi, M., Enayatzamir, N., Motamedi, H., Sorkheh, K.</v>
+      </c>
+      <c r="D156" t="str">
+        <v>IMPACT OF SOIL SALINITY ON DIVERSITY AND COMMUNITY_bioinsumos</v>
+      </c>
+      <c r="E156" t="str">
+        <v>Impacto da salinidade do solo na diversidade e comunidade de bactérias endofíticas promotoras de crescimento de cana-de-açúcar (Saccharum officinarum L. var. CP48)</v>
+      </c>
+      <c r="F156" t="str">
+        <v>2018</v>
+      </c>
+      <c r="G156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H156" t="str">
+        <v>biofertilizante, dissolução de fósforo, Pseudomonas, índice de Shannon, trigo</v>
+      </c>
+      <c r="I156" t="str">
+        <v>O objetivo deste estudo foi isolar e identificar bactérias endofíticas cultiváveis de cana-de-açúcar cultivada em solo salino e não salino e avaliar a capacidade de isolados selecionados para melhorar o crescimento, produção e absorção de fósforo de trigo.</v>
+      </c>
+      <c r="J156" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K156" t="str">
+        <v>ALÖKI Kft.</v>
+      </c>
+      <c r="L156" t="str">
+        <v>Shahid Chamran University of Ahvaz</v>
+      </c>
+      <c r="M156" t="str">
+        <v>Ahvaz, Irã</v>
+      </c>
+      <c r="N156" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O156" t="str">
+        <v>Applied Ecology and Environmental Research</v>
+      </c>
+      <c r="P156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q156" t="str">
+        <v>16</v>
+      </c>
+      <c r="R156" t="str">
+        <v>1</v>
+      </c>
+      <c r="S156" t="str">
+        <v>725-739</v>
+      </c>
+      <c r="T156" t="str">
+        <v>http://dx.doi.org/10.15666/aeer/1601_725739</v>
+      </c>
+      <c r="U156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W156" t="str">
+        <v>IMPACT OF SOIL SALINITY ON DIVERSITY AND COMMUNITY_bioinsumos.pdf</v>
+      </c>
+      <c r="X156" t="str">
+        <v/>
+      </c>
+      <c r="Y156" t="str">
+        <v/>
+      </c>
+      <c r="Z156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF156" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG156" t="str">
+        <v/>
+      </c>
+      <c r="AH156" t="str">
+        <v/>
+      </c>
+      <c r="AI156" t="str">
+        <v/>
+      </c>
+      <c r="AJ156" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v/>
+      </c>
+      <c r="B157" t="str">
+        <v/>
+      </c>
+      <c r="C157" t="str">
+        <v>Prittesh Patel, Rushabh Shah, Krunal Modi</v>
+      </c>
+      <c r="D157" t="str">
+        <v>ISOLATION AND CHARACTERIZATION OF PLANT_bioinsumos</v>
+      </c>
+      <c r="E157" t="str">
+        <v>Explorando o potencial de Acinetobacter como um biofertilizante para a cultura da cana-de-açúcar</v>
+      </c>
+      <c r="F157" t="str">
+        <v>2017</v>
+      </c>
+      <c r="G157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H157" t="str">
+        <v>Acinetobacter, Indol Acético, Ácido, PGPR, Fosfato, Cana-de-açúcar</v>
+      </c>
+      <c r="I157" t="str">
+        <v>Este estudo investiga o potencial de Acinetobacter sp. RSC7 isolado da cana-de-açúcar cultivar Co671 como um biofertilizante para a cultura da cana-de-açúcar. Os resultados mostram que o isolado tem capacidade de solubilizar fosfato e produzir indol acético, o que pode promover o crescimento das plantas.</v>
+      </c>
+      <c r="J157" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K157" t="str">
+        <v>Journal of Experimental Biology and Agricultural Sciences</v>
+      </c>
+      <c r="L157" t="str">
+        <v>CG Bhakta Institute of Biotechnology, Uka Tarsadia University</v>
+      </c>
+      <c r="M157" t="str">
+        <v>Bardoli, Gujarat, Índia</v>
+      </c>
+      <c r="N157" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O157" t="str">
+        <v>Journal of Experimental Biology and Agricultural Sciences</v>
+      </c>
+      <c r="P157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q157" t="str">
+        <v>5</v>
+      </c>
+      <c r="R157" t="str">
+        <v>4</v>
+      </c>
+      <c r="S157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T157" t="str">
+        <v>http://dx.doi.org/10.18006/2017.5(4).483.491</v>
+      </c>
+      <c r="U157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W157" t="str">
+        <v>ISOLATION AND CHARACTERIZATION OF PLANT_bioinsumos.pdf</v>
+      </c>
+      <c r="X157" t="str">
+        <v/>
+      </c>
+      <c r="Y157" t="str">
+        <v/>
+      </c>
+      <c r="Z157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF157" t="str">
+        <v>Aprovado: Detalha o potencial de Acinetobacter sp. RSC7 como um biofertilizante para a cultura da cana-de-açúcar.</v>
+      </c>
+      <c r="AG157" t="str">
+        <v/>
+      </c>
+      <c r="AH157" t="str">
+        <v/>
+      </c>
+      <c r="AI157" t="str">
+        <v/>
+      </c>
+      <c r="AJ157" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v/>
+      </c>
+      <c r="B158" t="str">
+        <v/>
+      </c>
+      <c r="C158" t="str">
+        <v>Kuldeep Singh, O.P. Choudhary, Kulvir Singh, Harmandeep Singh, Satnam Singh e R.S. Singh</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Identification of integrated nutrient managemen_bioinsumos</v>
+      </c>
+      <c r="E158" t="str">
+        <v>Uso de fontes orgânicas de nutrientes e métodos de controle de pragas</v>
+      </c>
+      <c r="F158" t="str">
+        <v>2015</v>
+      </c>
+      <c r="G158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H158" t="str">
+        <v>cana-de-açúcar, gestão de nutrientes, saúde do solo, controle de pragas</v>
+      </c>
+      <c r="I158" t="str">
+        <v>O estudo foi realizado para avaliar a resposta da cana-de-açúcar à aplicação de fontes orgânicas de nutrientes e métodos de controle de pragas.</v>
+      </c>
+      <c r="J158" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K158" t="str">
+        <v>Triveni Enterprises</v>
+      </c>
+      <c r="L158" t="str">
+        <v>Punjab Agricultural University</v>
+      </c>
+      <c r="M158" t="str">
+        <v>Faridkot, Índia</v>
+      </c>
+      <c r="N158" t="str">
+        <v>Estudo de campo</v>
+      </c>
+      <c r="O158" t="str">
+        <v>Journal of Environmental Biology</v>
+      </c>
+      <c r="P158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q158" t="str">
+        <v>36</v>
+      </c>
+      <c r="R158" t="str">
+        <v>3</v>
+      </c>
+      <c r="S158" t="str">
+        <v>551-555</v>
+      </c>
+      <c r="T158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W158" t="str">
+        <v>Identification of integrated nutrient managemen_bioinsumos.pdf</v>
+      </c>
+      <c r="X158" t="str">
+        <v/>
+      </c>
+      <c r="Y158" t="str">
+        <v/>
+      </c>
+      <c r="Z158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF158" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada e métodos de controle de pragas.</v>
+      </c>
+      <c r="AG158" t="str">
+        <v/>
+      </c>
+      <c r="AH158" t="str">
+        <v/>
+      </c>
+      <c r="AI158" t="str">
+        <v/>
+      </c>
+      <c r="AJ158" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v/>
+      </c>
+      <c r="B159" t="str">
+        <v/>
+      </c>
+      <c r="C159" t="str">
+        <v>Rajinder Pal, Onkar Singh, Gulzar S Sanghera, R K Gupta</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Influence of INM on sugarcane productivity_bioinsumos</v>
+      </c>
+      <c r="E159" t="str">
+        <v>Um estudo de campo foi conduzido durante 2016-17 na Universidade Agrícola do Punjab, Estação de Pesquisa Regional, Kapurthala, Punjab, Índia, com nove tratamentos compreendendo combinações variadas de esterco de curral (FYM), bio-fertilizantes e diferentes níveis de fertilizantes químicos em um design de blocos aleatórios (RBD).</v>
+      </c>
+      <c r="F159" t="str">
+        <v>2021</v>
+      </c>
+      <c r="G159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H159" t="str">
+        <v>Cana-de-açúcar, Fertilidade do solo, Nutrientes, Produção de cana-de-açúcar</v>
+      </c>
+      <c r="I159" t="str">
+        <v>Um estudo de campo foi conduzido durante 2016-17 na Universidade Agrícola do Punjab, Estação de Pesquisa Regional, Kapurthala, Punjab, Índia, com nove tratamentos compreendendo combinações variadas de esterco de curral (FYM), bio-fertilizantes e diferentes níveis de fertilizantes químicos em um design de blocos aleatórios (RBD).</v>
+      </c>
+      <c r="J159" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K159" t="str">
+        <v>Indian Journal of Agricultural Sciences</v>
+      </c>
+      <c r="L159" t="str">
+        <v>Punjab Agricultural University</v>
+      </c>
+      <c r="M159" t="str">
+        <v>Kapurthala, Punjab, Índia</v>
+      </c>
+      <c r="N159" t="str">
+        <v>Estudo de campo</v>
+      </c>
+      <c r="O159" t="str">
+        <v>Indian Journal of Agricultural Sciences</v>
+      </c>
+      <c r="P159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q159" t="str">
+        <v>91</v>
+      </c>
+      <c r="R159" t="str">
+        <v>5</v>
+      </c>
+      <c r="S159" t="str">
+        <v>703-7</v>
+      </c>
+      <c r="T159" t="str">
+        <v>https://doi.org/10.56093/ijas.v91i5.112987</v>
+      </c>
+      <c r="U159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W159" t="str">
+        <v>Influence of INM on sugarcane productivity_bioinsumos.pdf</v>
+      </c>
+      <c r="X159" t="str">
+        <v/>
+      </c>
+      <c r="Y159" t="str">
+        <v/>
+      </c>
+      <c r="Z159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF159" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG159" t="str">
+        <v/>
+      </c>
+      <c r="AH159" t="str">
+        <v/>
+      </c>
+      <c r="AI159" t="str">
+        <v/>
+      </c>
+      <c r="AJ159" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v/>
+      </c>
+      <c r="B160" t="str">
+        <v/>
+      </c>
+      <c r="C160" t="str">
+        <v>Ghallab, M.; Bukhari, N.; Salem, E.-A.; El-Zaidy, M.; El-Sheikh, A.; Raja, R.</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Influence of Spirulina Extract on Physiological_bioinsumos</v>
+      </c>
+      <c r="E160" t="str">
+        <v>Avaliação do efeito do extrato de Spirulina platensis na crescimento, rendimento e qualidade do suco de quatro genótipos de cana-de-açúcar</v>
+      </c>
+      <c r="F160" t="str">
+        <v>2024</v>
+      </c>
+      <c r="G160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H160" t="str">
+        <v>cana-de-açúcar, extrato de Spirulina, pulverização foliar, crescimento, qualidade do suco</v>
+      </c>
+      <c r="I160" t="str">
+        <v>Este estudo avaliou o efeito do extrato de Spirulina platensis na crescimento, rendimento e qualidade do suco de quatro genótipos de cana-de-açúcar durante as temporadas de 2020/2021 e 2021/2022.</v>
+      </c>
+      <c r="J160" t="str">
+        <v>Artigo</v>
+      </c>
+      <c r="K160" t="str">
+        <v>MDPI</v>
+      </c>
+      <c r="L160" t="str">
+        <v>Basel, Suíça</v>
+      </c>
+      <c r="M160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="N160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O160" t="str">
+        <v>Agronomy</v>
+      </c>
+      <c r="P160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q160" t="str">
+        <v>14</v>
+      </c>
+      <c r="R160" t="str">
+        <v>7</v>
+      </c>
+      <c r="S160" t="str">
+        <v>1594</v>
+      </c>
+      <c r="T160" t="str">
+        <v>10.3390/agronomy14071594</v>
+      </c>
+      <c r="U160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W160" t="str">
+        <v>Influence of Spirulina Extract on Physiological_bioinsumos.pdf</v>
+      </c>
+      <c r="X160" t="str">
+        <v/>
+      </c>
+      <c r="Y160" t="str">
+        <v/>
+      </c>
+      <c r="Z160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF160" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG160" t="str">
+        <v/>
+      </c>
+      <c r="AH160" t="str">
+        <v/>
+      </c>
+      <c r="AI160" t="str">
+        <v/>
+      </c>
+      <c r="AJ160" t="str">
+        <v>citros e cana</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v/>
+      </c>
+      <c r="B161" t="str">
+        <v/>
+      </c>
+      <c r="C161" t="str">
+        <v>U. Surendran, D. Vani</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Influence of arbuscular mycorrhizal fungi_bioinsumos</v>
+      </c>
+      <c r="E161" t="str">
+        <v>Impacto dos fungos micorrízicos arbusculares na produtividade da cana-de-açúcar em ecossistema agro tropical semiárido na Índia</v>
+      </c>
+      <c r="F161" t="str">
+        <v>2013</v>
+      </c>
+      <c r="G161" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H161" t="str">
+        <v>Biofertilizante, Fósforo, Cana-de-açúcar, Rendimento e teor de açúcar</v>
+      </c>
+      <c r="I161" t="str">
+        <v>O estudo avaliou o impacto dos fungos micorrízicos arbusculares (AMF) na produtividade da cana-de-açúcar em um experimento de campo em Tamil Nadu, Índia. Os resultados mostraram que a aplicação de AMF aumentou significativamente a porcentagem de germinação, número de talos, espessura de internódios e rendimento de cana em ambas as culturas de plantio e ratoeira.</v>
+      </c>
+      <c r="J161" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K161" t="str">
+        <v>International Journal of Plant Production</v>
+      </c>
+      <c r="L161" t="str">
+        <v>EID Parry (I) Ltd.</v>
+      </c>
+      <c r="M161" t="str">
+        <v>Pettavaithalai, Tamil Nadu, Índia</v>
+      </c>
+      <c r="N161" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O161" t="str">
+        <v>International Journal of Plant Production</v>
+      </c>
+      <c r="P161" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q161" t="str">
+        <v>7</v>
+      </c>
+      <c r="R161" t="str">
+        <v>2</v>
+      </c>
+      <c r="S161" t="str">
+        <v>269-278</v>
+      </c>
+      <c r="T161" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U161" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V161" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W161" t="str">
+        <v>Influence of arbuscular mycorrhizal fungi_bioinsumos.pdf</v>
+      </c>
+      <c r="X161" t="str">
+        <v/>
+      </c>
+      <c r="Y161" t="str">
+        <v/>
+      </c>
+      <c r="Z161" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA161" t="str">
+        <v>Inoculação de fungos micorrízicos arbusculares (AMF), aplicação de fósforo</v>
+      </c>
+      <c r="AB161" t="str">
+        <v>Fósforo, zinco, ferro</v>
+      </c>
+      <c r="AC161" t="str">
+        <v>Biofertilizante, aplicação de fósforo</v>
+      </c>
+      <c r="AD161" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE161" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF161" t="str">
+        <v>Aprovado: Detalha o impacto dos fungos micorrízicos arbusculares na produtividade da cana-de-açúcar em ecossistema agro tropical semiárido na Índia.</v>
+      </c>
+      <c r="AG161" t="str">
+        <v/>
+      </c>
+      <c r="AH161" t="str">
+        <v/>
+      </c>
+      <c r="AI161" t="str">
+        <v/>
+      </c>
+      <c r="AJ161" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v/>
+      </c>
+      <c r="B162" t="str">
+        <v/>
+      </c>
+      <c r="C162" t="str">
+        <v>Rita de Cássia Bonassi, Gisele Herbst Vazquez, Solismar de Paiva Venzke Filho, Maria Stefânia Cruanhes D´Andréa-Kühl, Juliana Heloisa Pinê Américo-Pinheiro, Andréa Cristiane Sanches, Luiz Sergio Vanzela, Elisângela de Souza Loureiro, Acacio Aparecido Navarrete</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Inoculation effects of Nitrospirillum amazonense_bioinsumos</v>
+      </c>
+      <c r="E162" t="str">
+        <v>Efeitos da inoculação de Nitrospirillum amazonense e biofertilizante em cana-de-açúcar</v>
+      </c>
+      <c r="F162" t="str">
+        <v>2024</v>
+      </c>
+      <c r="G162" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H162" t="str">
+        <v>Diazotrófica bacteria, interação planta-bactéria, microbioma do solo, inoculante microbiano</v>
+      </c>
+      <c r="I162" t="str">
+        <v>O estudo avaliou a hipótese de que a combinação de Nitrospirillum amazonense com adubo biológico produzido com Microgeo® resulta em benefícios morfológicos e nutricionais para o desenvolvimento inicial de plantas de cana-de-açúcar e para a química do solo.</v>
+      </c>
+      <c r="J162" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K162" t="str">
+        <v>Ciência Rural</v>
+      </c>
+      <c r="L162" t="str">
+        <v>Universidade Brasil (UB)</v>
+      </c>
+      <c r="M162" t="str">
+        <v>Fernandópolis, SP, Brasil</v>
+      </c>
+      <c r="N162" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O162" t="str">
+        <v>Ciência Rural</v>
+      </c>
+      <c r="P162" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q162" t="str">
+        <v>54</v>
+      </c>
+      <c r="R162" t="str">
+        <v>3</v>
+      </c>
+      <c r="S162" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T162" t="str">
+        <v>10.1590/0103-8478cr20220628</v>
+      </c>
+      <c r="U162" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V162" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W162" t="str">
+        <v>Inoculation effects of Nitrospirillum amazonense_bioinsumos.pdf</v>
+      </c>
+      <c r="X162" t="str">
+        <v/>
+      </c>
+      <c r="Y162" t="str">
+        <v/>
+      </c>
+      <c r="Z162" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA162" t="str">
+        <v>Cromatografia gasosa, Fotossíntese líquida, RCBD, ANOVA</v>
+      </c>
+      <c r="AB162" t="str">
+        <v>Nitrogênio, Fósforo, Potássio, Sulfur</v>
+      </c>
+      <c r="AC162" t="str">
+        <v>Fertirrigação, Aplicação foliar, Controle de pragas, Poda</v>
+      </c>
+      <c r="AD162" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE162" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF162" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG162" t="str">
+        <v/>
+      </c>
+      <c r="AH162" t="str">
+        <v/>
+      </c>
+      <c r="AI162" t="str">
+        <v/>
+      </c>
+      <c r="AJ162" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v/>
+      </c>
+      <c r="B163" t="str">
+        <v/>
+      </c>
+      <c r="C163" t="str">
+        <v>Silvana Gomes dos Santos, Flaviane da Silva Ribeiro, Gabriela Cavalcanti Alves, Leandro Azevedo Santos, Veronica Massena Reis</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Inoculation with five diazotrophs_bioinsumos</v>
+      </c>
+      <c r="E163" t="str">
+        <v>A influência da inoculação com cinco espécies/estirpes de bactérias diazotróficas na modulação da atividade de duas enzimas envolvidas na assimilação de N e nas frações solúveis de N nas variedades de cana-de-açúcar RB867515 (adaptada para solos de baixa fertilidade) e IACSP95-5000 (adaptada para solos de média a alta fertilidade) sob condições de alta (3 mM) e baixa (0,3 mM) de N em cultivo hidropônico por 59 dias.</v>
+      </c>
+      <c r="F163" t="str">
+        <v>2019</v>
+      </c>
+      <c r="G163" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H163" t="str">
+        <v>bactérias diazotróficas, Saccharum sp., atividade enzimática, nitrogênio</v>
+      </c>
+      <c r="I163" t="str">
+        <v>A inoculação com cinco espécies/estirpes de bactérias diazotróficas alterou o metabolismo de nitrogênio durante o crescimento inicial de variedades de cana-de-açúcar com respostas contrastantes às adições de nitrogênio.</v>
+      </c>
+      <c r="J163" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K163" t="str">
+        <v>Springer Nature Switzerland AG</v>
+      </c>
+      <c r="L163" t="str">
+        <v>Universidade Federal Rural do Rio de Janeiro</v>
+      </c>
+      <c r="M163" t="str">
+        <v>Seropédica, Rio de Janeiro</v>
+      </c>
+      <c r="N163" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O163" t="str">
+        <v>Plant Soil</v>
+      </c>
+      <c r="P163" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q163" t="str">
+        <v>451</v>
+      </c>
+      <c r="R163" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S163" t="str">
+        <v>25–44</v>
+      </c>
+      <c r="T163" t="str">
+        <v>https://doi.org/10.1007/s11104-019-04101-1</v>
+      </c>
+      <c r="U163" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V163" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W163" t="str">
+        <v>Inoculation with five diazotrophs_bioinsumos.pdf</v>
+      </c>
+      <c r="X163" t="str">
+        <v/>
+      </c>
+      <c r="Y163" t="str">
+        <v/>
+      </c>
+      <c r="Z163" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA163" t="str">
+        <v>Cultivo hidropônico, inoculação com bactérias diazotróficas, análise de atividade enzimática, determinação de frações solúveis de N</v>
+      </c>
+      <c r="AB163" t="str">
+        <v>Nitrogênio, fósforo, potássio</v>
+      </c>
+      <c r="AC163" t="str">
+        <v>Inoculação com bactérias diazotróficas, adubação nitrogenada</v>
+      </c>
+      <c r="AD163" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE163" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF163" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG163" t="str">
+        <v/>
+      </c>
+      <c r="AH163" t="str">
+        <v/>
+      </c>
+      <c r="AI163" t="str">
+        <v/>
+      </c>
+      <c r="AJ163" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v/>
+      </c>
+      <c r="B164" t="str">
+        <v/>
+      </c>
+      <c r="C164" t="str">
+        <v>Jiraporn Jirakkakul, Ahmad Nuruddin Khoiri, Thanawat Duangfoo, Sudarat Dulsawat, Sawannee Sutheeworapong, Kantiya Petsong, Songsak Wattanachaisaereekul, Prasobsook Paenkaew, Anuwat Tachaleat, Supapon Cheevadhanarak, Peerada Prommeenate</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Insights into the genome of Methylobacterium sp_bioinsumos</v>
+      </c>
+      <c r="E164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F164" t="str">
+        <v>2023</v>
+      </c>
+      <c r="G164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J164" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K164" t="str">
+        <v>PLOS ONE</v>
+      </c>
+      <c r="L164" t="str">
+        <v>King Mongkut’s University of Technology Thonburi</v>
+      </c>
+      <c r="M164" t="str">
+        <v>Bangkok, Tailândia</v>
+      </c>
+      <c r="N164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O164" t="str">
+        <v>PLOS ONE</v>
+      </c>
+      <c r="P164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T164" t="str">
+        <v>https://doi.org/10.1371/journal.pone.0281505</v>
+      </c>
+      <c r="U164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W164" t="str">
+        <v>Insights into the genome of Methylobacterium sp_bioinsumos.pdf</v>
+      </c>
+      <c r="X164" t="str">
+        <v/>
+      </c>
+      <c r="Y164" t="str">
+        <v/>
+      </c>
+      <c r="Z164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA164" t="str">
+        <v>Análise de sequência de 16S rRNA, Análise genômica, Análise comparativa genômica, Análise de pangenoma</v>
+      </c>
+      <c r="AB164" t="str">
+        <v>Nitrogênio, Fósforo, Sulfur</v>
+      </c>
+      <c r="AC164" t="str">
+        <v>Solubilização de fosfato, Biossíntese de ácido indolacético (IAA), Produção de citocininas (CKs), Atividade de deaminase de 1-aminociclopropano-1-carboxilato (ACC)</v>
+      </c>
+      <c r="AD164" t="str">
+        <v>Frutíferas</v>
+      </c>
+      <c r="AE164" t="str">
+        <v>Milho, Pimenta, Cana-de-açúcar</v>
+      </c>
+      <c r="AF164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AG164" t="str">
+        <v/>
+      </c>
+      <c r="AH164" t="str">
+        <v/>
+      </c>
+      <c r="AI164" t="str">
+        <v/>
+      </c>
+      <c r="AJ164" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v/>
+      </c>
+      <c r="B165" t="str">
+        <v/>
+      </c>
+      <c r="C165" t="str">
+        <v>Natália S. Ferreira, Gustavo F. Matos, Carlos H. S. G. Meneses, Veronica M. Reis, Janaina R. C. Rouws, Stefan Schwab, José I. Baldani, Luc F. M. Rouws</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Interaction of phytohormone_bioinsumos</v>
+      </c>
+      <c r="E165" t="str">
+        <v>Avaliação da colonização de mini-setts de cana-de-açúcar por bactérias produtoras de hormônios e seu efeito no desenvolvimento de plantas</v>
+      </c>
+      <c r="F165" t="str">
+        <v>2020</v>
+      </c>
+      <c r="G165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H165" t="str">
+        <v>bactérias endofíticas, bactérias promotoras de crescimento de plantas, brotação, microscopia de laser de varredura confocal, giberelinas, cromatografia líquida de alta performance, espectrometria de massa</v>
+      </c>
+      <c r="I165" t="str">
+        <v>Este estudo avaliou a colonização de mini-setts de cana-de-açúcar por bactérias produtoras de hormônios e seu efeito no desenvolvimento de plantas.</v>
+      </c>
+      <c r="J165" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K165" t="str">
+        <v>Springer Nature Switzerland AG</v>
+      </c>
+      <c r="L165" t="str">
+        <v>Universidade Federal Rural do Rio de Janeiro, Embrapa Agrobiologia</v>
+      </c>
+      <c r="M165" t="str">
+        <v>Seropédica, RJ, Brasil</v>
+      </c>
+      <c r="N165" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O165" t="str">
+        <v>Plant Soil</v>
+      </c>
+      <c r="P165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q165" t="str">
+        <v>451</v>
+      </c>
+      <c r="R165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S165" t="str">
+        <v>221–238</v>
+      </c>
+      <c r="T165" t="str">
+        <v>https://doi.org/10.1007/s11104-019-04388-0</v>
+      </c>
+      <c r="U165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W165" t="str">
+        <v>Interaction of phytohormone_bioinsumos.pdf</v>
+      </c>
+      <c r="X165" t="str">
+        <v/>
+      </c>
+      <c r="Y165" t="str">
+        <v/>
+      </c>
+      <c r="Z165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA165" t="str">
+        <v>Cromatografia líquida de alta performance (HPLC), espectrometria de massa (GC-MS), microscopia de laser de varredura confocal (CLSM), contagem de colônias</v>
+      </c>
+      <c r="AB165" t="str">
+        <v>Giberelinas, ácido indolacético (IAA), zeatina</v>
+      </c>
+      <c r="AC165" t="str">
+        <v>Inoculação de bactérias produtoras de hormônios</v>
+      </c>
+      <c r="AD165" t="str">
+        <v>Grandes culturas</v>
+      </c>
+      <c r="AE165" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF165" t="str">
+        <v>Aprovado: Detalha a interação entre bactérias produtoras de hormônios e mini-setts de cana-de-açúcar e seu efeito no desenvolvimento de plantas.</v>
+      </c>
+      <c r="AG165" t="str">
+        <v/>
+      </c>
+      <c r="AH165" t="str">
+        <v/>
+      </c>
+      <c r="AI165" t="str">
+        <v/>
+      </c>
+      <c r="AJ165" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v/>
+      </c>
+      <c r="B166" t="str">
+        <v/>
+      </c>
+      <c r="C166" t="str">
+        <v>Sitlaothaworn, K., Busabun, T., Dechkla, M., Thaipratum, R. and Khunphaderm, M.</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Isolation   and   optimization   of   efficient   indole   acetic_bioinsumos</v>
+      </c>
+      <c r="E166" t="str">
+        <v>Isolamento e otimização de Staphylococcus edaphicus eficiente na produção de ácido indolacético do Saccharum officinarum</v>
+      </c>
+      <c r="F166" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G166" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H166" t="str">
+        <v>Bactérias endofíticas, Ácido indolacético, Concentração de triptofano, Condição de otimização, Staphylococcus sp.</v>
+      </c>
+      <c r="I166" t="str">
+        <v>Bactérias endofíticas são microorganismos que promovem o crescimento das plantas e sintetizam ácido indolacético (IAA), modulando a fixação de nitrogênio, produzindo fitohormônios e solubilizando alguns minerais do solo.</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K166" t="str">
+        <v>International Journal of Agricultural Technology</v>
+      </c>
+      <c r="L166" t="str">
+        <v>Suan Sunandha Rajabhat University</v>
+      </c>
+      <c r="M166" t="str">
+        <v>Bangkok, Tailândia</v>
+      </c>
+      <c r="N166" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O166" t="str">
+        <v>International Journal of Agricultural Technology</v>
+      </c>
+      <c r="P166" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q166" t="str">
+        <v>18</v>
+      </c>
+      <c r="R166" t="str">
+        <v>5</v>
+      </c>
+      <c r="S166" t="str">
+        <v>2255-2270</v>
+      </c>
+      <c r="T166" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U166" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V166" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W166" t="str">
+        <v>Isolation   and   optimization   of   efficient   indole   acetic_bioinsumos.pdf</v>
+      </c>
+      <c r="X166" t="str">
+        <v/>
+      </c>
+      <c r="Y166" t="str">
+        <v/>
+      </c>
+      <c r="Z166" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA166" t="str">
+        <v>Cultura de bactérias, Sequenciamento do gene 16S rRNA, Análise evolutiva, Produção de ácido indolacético</v>
+      </c>
+      <c r="AB166" t="str">
+        <v>Ácido indolacético, Fósforo, Potássio, Zinco, Nitrogênio</v>
+      </c>
+      <c r="AC166" t="str">
+        <v>Fertilização biológica, Produção de fitohormônios, Solubilização de minerais do solo</v>
+      </c>
+      <c r="AD166" t="str">
+        <v>Grandes culturas</v>
+      </c>
+      <c r="AE166" t="str">
+        <v>Saccharum officinarum (cana-de-açúcar), Citrus aurantifolia (limão)</v>
+      </c>
+      <c r="AF166" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG166" t="str">
+        <v/>
+      </c>
+      <c r="AH166" t="str">
+        <v/>
+      </c>
+      <c r="AI166" t="str">
+        <v/>
+      </c>
+      <c r="AJ166" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v/>
+      </c>
+      <c r="B167" t="str">
+        <v/>
+      </c>
+      <c r="C167" t="str">
+        <v>Ariana Alves Rodrigues, Marcus Vinicius Forzani, Renan de Souza Soares, Sergio Tadeu Sibov, José Daniel Gonçalves Vieira</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Isolation and selection of plant_bioinsumos</v>
+      </c>
+      <c r="E167" t="str">
+        <v>Os micro-organismos apresentam papel fundamental na manutenção da fertilidade do solo e da saúde vegetal, podendo atuar como biofertilizantes, aumentando a resistência ao estresse biótico e abiótico.</v>
+      </c>
+      <c r="F167" t="str">
+        <v>2016</v>
+      </c>
+      <c r="G167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H167" t="str">
+        <v>Zea mays L., Enterobacteriaceae, Klebsiella, Enterobacter, Pantoea</v>
+      </c>
+      <c r="I167" t="str">
+        <v>O objetivo do estudo foi isolar e caracterizar bactérias promotoras de crescimento vegetal associadas a cana-de-açúcar e avaliar a capacidade dessas bactérias em promover o crescimento vegetal.</v>
+      </c>
+      <c r="J167" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K167" t="str">
+        <v>Universidade Federal de Goiás</v>
+      </c>
+      <c r="L167" t="str">
+        <v>Instituto de Patologia Tropical e Saúde Pública</v>
+      </c>
+      <c r="M167" t="str">
+        <v>Goiânia, GO, Brasil</v>
+      </c>
+      <c r="N167" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O167" t="str">
+        <v>Pesquisa Agropecuária Tropical</v>
+      </c>
+      <c r="P167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q167" t="str">
+        <v>46</v>
+      </c>
+      <c r="R167" t="str">
+        <v>2</v>
+      </c>
+      <c r="S167" t="str">
+        <v>149-158</v>
+      </c>
+      <c r="T167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W167" t="str">
+        <v>Isolation and selection of plant_bioinsumos.pdf</v>
+      </c>
+      <c r="X167" t="str">
+        <v/>
+      </c>
+      <c r="Y167" t="str">
+        <v/>
+      </c>
+      <c r="Z167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA167" t="str">
+        <v>Cromatografia gasosa, Fotossíntese líquida, RCBD, ANOVA</v>
+      </c>
+      <c r="AB167" t="str">
+        <v>Nitrogênio, Fosfato, Ácido indolacético (AIA)</v>
+      </c>
+      <c r="AC167" t="str">
+        <v>Fertirrigação, Aplicação foliar, Controle de pragas</v>
+      </c>
+      <c r="AD167" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE167" t="str">
+        <v>Cana-de-açúcar (RB 867515)</v>
+      </c>
+      <c r="AF167" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG167" t="str">
+        <v/>
+      </c>
+      <c r="AH167" t="str">
+        <v/>
+      </c>
+      <c r="AI167" t="str">
+        <v/>
+      </c>
+      <c r="AJ167" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v/>
+      </c>
+      <c r="B168" t="str">
+        <v/>
+      </c>
+      <c r="C168" t="str">
+        <v>Maria C. B. S. Leite, Andreza R. B. de Farias, Fernando J. Freire, Fernando D. Andreote, Júlia Kuklinsky-Sobral &amp; Maria B. G. S. Freire</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Isolation bioprospecting and diversity of salttolerant_bioinsumos</v>
+      </c>
+      <c r="E168" t="str">
+        <v>Seleção de bactérias tolerantes à salinidade associadas a cana-de-açúcar em solos de Pernambuco, Brasil</v>
+      </c>
+      <c r="F168" t="str">
+        <v>2014</v>
+      </c>
+      <c r="G168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H168" t="str">
+        <v>endofítica, promoção de crescimento vegetal, variabilidade genética</v>
+      </c>
+      <c r="I168" t="str">
+        <v>A seleção de bactérias tolerantes a salinidade poderá propiciar maior promoção de crescimento vegetal em solos com estresse salino.</v>
+      </c>
+      <c r="J168" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K168" t="str">
+        <v>Revista Brasileira de Engenharia Agrícola e Ambiental</v>
+      </c>
+      <c r="L168" t="str">
+        <v>UAEA/UFCG</v>
+      </c>
+      <c r="M168" t="str">
+        <v>Campina Grande, PB</v>
+      </c>
+      <c r="N168" t="str">
+        <v>Suplemento</v>
+      </c>
+      <c r="O168" t="str">
+        <v>Revista Brasileira de Engenharia Agrícola e Ambiental</v>
+      </c>
+      <c r="P168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q168" t="str">
+        <v>18</v>
+      </c>
+      <c r="R168" t="str">
+        <v>(Suplemento)</v>
+      </c>
+      <c r="S168" t="str">
+        <v>S73–S79</v>
+      </c>
+      <c r="T168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W168" t="str">
+        <v>Isolation bioprospecting and diversity of salttolerant_bioinsumos.pdf</v>
+      </c>
+      <c r="X168" t="str">
+        <v/>
+      </c>
+      <c r="Y168" t="str">
+        <v/>
+      </c>
+      <c r="Z168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA168" t="str">
+        <v>Cultura em meio de NaCl, Denaturing Gradient Gel Electrophoresis (DGGE) do gene nifH, Eletroforese em Gradiente de Gel Desnaturante (DGGE)</v>
+      </c>
+      <c r="AB168" t="str">
+        <v>Nitrogênio, Fosfato inorgânico</v>
+      </c>
+      <c r="AC168" t="str">
+        <v>Fixação biológica de nitrogênio (FBN), Produção de ácido indol acético (AIA), Solubilização de fosfato inorgânico</v>
+      </c>
+      <c r="AD168" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE168" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF168" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG168" t="str">
+        <v/>
+      </c>
+      <c r="AH168" t="str">
+        <v/>
+      </c>
+      <c r="AI168" t="str">
+        <v/>
+      </c>
+      <c r="AJ168" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v/>
+      </c>
+      <c r="B169" t="str">
+        <v/>
+      </c>
+      <c r="C169" t="str">
+        <v>Muhammad Awais, Muhammad Tariq, Arfan Ali, Qurban Ali, Anwar Khan, Bushra Tabassum, Idrees Ahmad Nasir, Tayyab Husnain</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Isolation, characterization and inter-relationship_bioinsumos</v>
+      </c>
+      <c r="E169" t="str">
+        <v>Phosphate solubilizing bacteria (PSB) have the ability to solubilize insoluble phosphorus to make it available for plant roots to be absorbed.</v>
+      </c>
+      <c r="F169" t="str">
+        <v>2017</v>
+      </c>
+      <c r="G169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H169" t="str">
+        <v>Phosphate solubilizing bacteria, 16S rRNA, Antagonistic activity</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Phosphate solubilizing bacteria (PSB) have the ability to solubilize insoluble phosphorus to make it available for plant roots to be absorbed.</v>
+      </c>
+      <c r="J169" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K169" t="str">
+        <v>Elsevier</v>
+      </c>
+      <c r="L169" t="str">
+        <v>University of the Punjab, Lahore</v>
+      </c>
+      <c r="M169" t="str">
+        <v>Lahore, Pakistan</v>
+      </c>
+      <c r="N169" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O169" t="str">
+        <v>Biocatalysis and Agricultural Biotechnology</v>
+      </c>
+      <c r="P169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S169" t="str">
+        <v>312–321</v>
+      </c>
+      <c r="T169" t="str">
+        <v>http://dx.doi.org/10.1016/j.bcab.2017.07.018</v>
+      </c>
+      <c r="U169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W169" t="str">
+        <v>Isolation, characterization and inter-relationship_bioinsumos.pdf</v>
+      </c>
+      <c r="X169" t="str">
+        <v/>
+      </c>
+      <c r="Y169" t="str">
+        <v/>
+      </c>
+      <c r="Z169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA169" t="str">
+        <v>Cromatografia gasosa, Sequenciamento de 16S rRNA, Identificação bioquímica de bactérias</v>
+      </c>
+      <c r="AB169" t="str">
+        <v>Fósforo, Potássio</v>
+      </c>
+      <c r="AC169" t="str">
+        <v>Fertilização com fósforo, Controle de pragas</v>
+      </c>
+      <c r="AD169" t="str">
+        <v>Grandes culturas</v>
+      </c>
+      <c r="AE169" t="str">
+        <v>Caná-de-açúcar, Arroz</v>
+      </c>
+      <c r="AF169" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG169" t="str">
+        <v/>
+      </c>
+      <c r="AH169" t="str">
+        <v/>
+      </c>
+      <c r="AI169" t="str">
+        <v/>
+      </c>
+      <c r="AJ169" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v/>
+      </c>
+      <c r="B170" t="str">
+        <v/>
+      </c>
+      <c r="C170" t="str">
+        <v>Rajesh Kumar</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Microbial population dynamics under_bioinsumos</v>
+      </c>
+      <c r="E170" t="str">
+        <v>Utilização de efﬂuentes de destilaria para fertirrigação em cana-de-açúcar</v>
+      </c>
+      <c r="F170" t="str">
+        <v>2015</v>
+      </c>
+      <c r="G170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H170" t="str">
+        <v>BOD, COD, Distillery efﬂuent, Fertigation, Microbial population, Fertilizer</v>
+      </c>
+      <c r="I170" t="str">
+        <v>O estudo analisa a dinâmica da população microbiana sob fertirrigação com efﬂuentes de destilaria em um sistema de cultivo de cana-de-açúcar.</v>
+      </c>
+      <c r="J170" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K170" t="str">
+        <v>Springer Science+Business Media Dordrecht</v>
+      </c>
+      <c r="L170" t="str">
+        <v>Babasaheb Bhimrao Ambedkar University (A Central University)</v>
+      </c>
+      <c r="M170" t="str">
+        <v>Lucknow, Uttar Pradesh, Índia</v>
+      </c>
+      <c r="N170" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O170" t="str">
+        <v>Environ Dev Sustain</v>
+      </c>
+      <c r="P170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S170" t="str">
+        <v>187–196</v>
+      </c>
+      <c r="T170" t="str">
+        <v>10.1007/s10668-015-9633-2</v>
+      </c>
+      <c r="U170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W170" t="str">
+        <v>Microbial population dynamics under_bioinsumos.pdf</v>
+      </c>
+      <c r="X170" t="str">
+        <v/>
+      </c>
+      <c r="Y170" t="str">
+        <v/>
+      </c>
+      <c r="Z170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA170" t="str">
+        <v>Fertirrigação, monitoramento da população microbiana, análise de BOD e COD.</v>
+      </c>
+      <c r="AB170" t="str">
+        <v>Nitrogênio, fósforo, potássio, micronutrientes.</v>
+      </c>
+      <c r="AC170" t="str">
+        <v>Fertirrigação com efﬂuentes de destilaria, aplicação de fertilizantes recomendados.</v>
+      </c>
+      <c r="AD170" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE170" t="str">
+        <v>Cana-de-açúcar (Saccharum ofﬁcinarum L.)</v>
+      </c>
+      <c r="AF170" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à fertirrigação com efﬂuentes de destilaria.</v>
+      </c>
+      <c r="AG170" t="str">
+        <v/>
+      </c>
+      <c r="AH170" t="str">
+        <v/>
+      </c>
+      <c r="AI170" t="str">
+        <v/>
+      </c>
+      <c r="AJ170" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v/>
+      </c>
+      <c r="B171" t="str">
+        <v/>
+      </c>
+      <c r="C171" t="str">
+        <v>Pratiksha Singh, Rajesh Kumar Singh, Hai-Bi Li, Dao-Jun Guo, Anjney Sharma, Krishan K Verma, Manoj Kumar Solanki, Sudhir K. Upadhyay, Prakash Lakshmanan, Li-Tao Yang &amp; Yang-Rui Li</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Nitrogen fixation and phytohormone stimulation of sugarcane_bioinsumos</v>
+      </c>
+      <c r="E171" t="str">
+        <v>Nitrogênio fixação e estimulação de fitohormônios de cana-de-açúcar através de Pseudomonas promotoras de crescimento</v>
+      </c>
+      <c r="F171" t="str">
+        <v>2024</v>
+      </c>
+      <c r="G171" t="str">
+        <v>33</v>
+      </c>
+      <c r="H171" t="str">
+        <v>Defesa relacionada a genes; fixação de nitrogênio; fitohormônios; Pseudomonas spp.; cana-de-açúcar</v>
+      </c>
+      <c r="I171" t="str">
+        <v>O objetivo do estudo foi determinar como as bactérias Pseudomonas promotoras de crescimento (PGP) (P. koreensis CY4 e P. entomophila CN11) aumentaram a fixação de nitrogênio, atividade de defesa e atributos PGP das variedades de cana-de-açúcar GT11 e G×B9.</v>
+      </c>
+      <c r="J171" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K171" t="str">
+        <v>Taylor &amp; Francis Group</v>
+      </c>
+      <c r="L171" t="str">
+        <v>Guangxi Academy of Agricultural Sciences</v>
+      </c>
+      <c r="M171" t="str">
+        <v>Nanning, China</v>
+      </c>
+      <c r="N171" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O171" t="str">
+        <v>Biotechnology and Genetic Engineering Reviews</v>
+      </c>
+      <c r="P171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q171" t="str">
+        <v>40</v>
+      </c>
+      <c r="R171" t="str">
+        <v>1</v>
+      </c>
+      <c r="S171" t="str">
+        <v>15-35</v>
+      </c>
+      <c r="T171" t="str">
+        <v>10.1080/02648725.2023.2177814</v>
+      </c>
+      <c r="U171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W171" t="str">
+        <v>Nitrogen fixation and phytohormone stimulation of sugarcane_bioinsumos.pdf</v>
+      </c>
+      <c r="X171" t="str">
+        <v/>
+      </c>
+      <c r="Y171" t="str">
+        <v/>
+      </c>
+      <c r="Z171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF171" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG171" t="str">
+        <v/>
+      </c>
+      <c r="AH171" t="str">
+        <v/>
+      </c>
+      <c r="AI171" t="str">
+        <v/>
+      </c>
+      <c r="AJ171" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v/>
+      </c>
+      <c r="B172" t="str">
+        <v/>
+      </c>
+      <c r="C172" t="str">
+        <v>Jennifer Martínez-Ballesteros, Karina P. Bañuelos-Hernández, Daniel A. Rodríguez-Lagunes, Juan V. Hidalgo-Contreras, Miriam C. Pastelín-Solano, Guadalupe Vivar-Vera, Javier E. Bulbarela-Marini, Odon Castañeda-Castro</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Phosphite effects on sugarcane growth_bioinsumos</v>
+      </c>
+      <c r="E172" t="str">
+        <v>Biostimulants positively impact plant growth, yield, and chemical composition while enhancing tolerance to biotic and abiotic stress.</v>
+      </c>
+      <c r="F172" t="str">
+        <v>2025</v>
+      </c>
+      <c r="G172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H172" t="str">
+        <v>Saccharum spp., Phosphorous acid, Beneficial elements, Oxyanion</v>
+      </c>
+      <c r="I172" t="str">
+        <v>Phosphite (Phi) serves as an effective inorganic biostimulant for sugarcane (CP 72-2086) during in vitro multiplication, stimulating seedling growth and modulating essential biomolecule concentrations.</v>
+      </c>
+      <c r="J172" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K172" t="str">
+        <v>PeerJ</v>
+      </c>
+      <c r="L172" t="str">
+        <v>University of Veracruz</v>
+      </c>
+      <c r="M172" t="str">
+        <v>Amatlán de los Reyes, Veracruz, Mexico</v>
+      </c>
+      <c r="N172" t="str">
+        <v>Estudo de caso</v>
+      </c>
+      <c r="O172" t="str">
+        <v>PeerJ</v>
+      </c>
+      <c r="P172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T172" t="str">
+        <v>10.7717/peerj.19763</v>
+      </c>
+      <c r="U172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W172" t="str">
+        <v>Phosphite effects on sugarcane growth_bioinsumos.pdf</v>
+      </c>
+      <c r="X172" t="str">
+        <v/>
+      </c>
+      <c r="Y172" t="str">
+        <v/>
+      </c>
+      <c r="Z172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA172" t="str">
+        <v>Cultivo in vitro, Micropropagação, Osmose, Polietileno glicol 6000 (PEG), Cromatografia gasosa, Análise de biomoléculas</v>
+      </c>
+      <c r="AB172" t="str">
+        <v>Fósforo, Ácido fosfórico, Sacarose, Aminoácidos</v>
+      </c>
+      <c r="AC172" t="str">
+        <v>Fertirrigação, Aplicação foliar, Controle de pragas</v>
+      </c>
+      <c r="AD172" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE172" t="str">
+        <v>Cana-de-açúcar (Saccharum spp.)</v>
+      </c>
+      <c r="AF172" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação fosforada.</v>
+      </c>
+      <c r="AG172" t="str">
+        <v/>
+      </c>
+      <c r="AH172" t="str">
+        <v/>
+      </c>
+      <c r="AI172" t="str">
+        <v/>
+      </c>
+      <c r="AJ172" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v/>
+      </c>
+      <c r="B173" t="str">
+        <v/>
+      </c>
+      <c r="C173" t="str">
+        <v>Gustavo Caione, Renato de Mello Prado, Ricardo de Lima Vasconcelos, Jonas Pereira de Souza Junior, Cid Naudi Silva Campos, Leandro Rosatto Moda, Leonides Castellanos Gonza´lez</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Phosphorus Sources Combined with Doses of Organic_bioinsumos</v>
+      </c>
+      <c r="E173" t="str">
+        <v>Efeito da fonte de fósforo e do composto orgânico na população de microorganismos do solo e no nível de P no solo e planta e no teor de matéria seca da cana-de-açúcar</v>
+      </c>
+      <c r="F173" t="str">
+        <v>2020</v>
+      </c>
+      <c r="G173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H173" t="str">
+        <v>Microorganismos, composto orgânico, Saccharum spp., biologia do solo</v>
+      </c>
+      <c r="I173" t="str">
+        <v>O objetivo do estudo foi avaliar o efeito da fonte de fósforo e do composto orgânico na população de microorganismos do solo e no nível de P no solo e planta e no teor de matéria seca da cana-de-açúcar.</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Artigo de Pesquisa</v>
+      </c>
+      <c r="K173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="M173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="N173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W173" t="str">
+        <v>Phosphorus Sources Combined with Doses of Organic_bioinsumos.pdf</v>
+      </c>
+      <c r="X173" t="str">
+        <v/>
+      </c>
+      <c r="Y173" t="str">
+        <v/>
+      </c>
+      <c r="Z173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF173" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG173" t="str">
+        <v/>
+      </c>
+      <c r="AH173" t="str">
+        <v/>
+      </c>
+      <c r="AI173" t="str">
+        <v/>
+      </c>
+      <c r="AJ173" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v/>
+      </c>
+      <c r="B174" t="str">
+        <v/>
+      </c>
+      <c r="C174" t="str">
+        <v>Rosangela Naomi Inui - Kishi, Luciano Takeshi Kishi, Simone Cristina Picchi, José Carlos Barbosa, Maria Teresa Olivério Lemos, Jackson Marcondes and Eliana Gertrudes de Macedo Lemos</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Phosphorus solubilizing and iaa production activities_bioinsumos</v>
+      </c>
+      <c r="E174" t="str">
+        <v>Isolamento e caracterização de bactérias solubilizadoras de fósforo e produção de IAA em solo sob cultivo de cana-de-açúcar</v>
+      </c>
+      <c r="F174" t="str">
+        <v>2012</v>
+      </c>
+      <c r="G174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H174" t="str">
+        <v>solubilização de fósforo, 16S rRNA, produção de IAA, bactérias promotoras de crescimento de plantas</v>
+      </c>
+      <c r="I174" t="str">
+        <v>O objetivo deste estudo foi o isolamento e caracterização de bactérias solubilizadoras de fósforo e produção de IAA em solo sob cultivo de cana-de-açúcar.</v>
+      </c>
+      <c r="J174" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K174" t="str">
+        <v>Asian Research Publishing Network (ARPN)</v>
+      </c>
+      <c r="L174" t="str">
+        <v>Universidade Estadual Paulista</v>
+      </c>
+      <c r="M174" t="str">
+        <v>São Paulo, Brasil</v>
+      </c>
+      <c r="N174" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O174" t="str">
+        <v>ARPN Journal of Engineering and Applied Sciences</v>
+      </c>
+      <c r="P174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q174" t="str">
+        <v>7</v>
+      </c>
+      <c r="R174" t="str">
+        <v>11</v>
+      </c>
+      <c r="S174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W174" t="str">
+        <v>Phosphorus solubilizing and iaa production activities_bioinsumos.pdf</v>
+      </c>
+      <c r="X174" t="str">
+        <v/>
+      </c>
+      <c r="Y174" t="str">
+        <v/>
+      </c>
+      <c r="Z174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA174" t="str">
+        <v>16S rRNA sequencing, bioensaios</v>
+      </c>
+      <c r="AB174" t="str">
+        <v>fósforo, IAA</v>
+      </c>
+      <c r="AC174" t="str">
+        <v>solubilização de fósforo, produção de IAA</v>
+      </c>
+      <c r="AD174" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE174" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF174" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG174" t="str">
+        <v/>
+      </c>
+      <c r="AH174" t="str">
+        <v/>
+      </c>
+      <c r="AI174" t="str">
+        <v/>
+      </c>
+      <c r="AJ174" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v/>
+      </c>
+      <c r="B175" t="str">
+        <v/>
+      </c>
+      <c r="C175" t="str">
+        <v>Alfredo R. Hernández, Renato de M. Prado, Leónides C. González, Gustavo Caione, Leandro R. Moda, Luis C. Assis, e Hilário J. Almeida</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Phosphorus sources enriched with filter cake and microorganisms_bioinsumos</v>
+      </c>
+      <c r="E175" t="str">
+        <v>Efeito da adubação com fontes de fósforo associadas a bagaço enriquecido com microorganismos na microbiota do solo, absorção de fósforo e produção de matéria seca em cana-de-açúcar</v>
+      </c>
+      <c r="F175" t="str">
+        <v>2015</v>
+      </c>
+      <c r="G175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H175" t="str">
+        <v>Resíduos agrícolas, fertilizante orgânico, fertilizante fosfato, Saccharum spp.</v>
+      </c>
+      <c r="I175" t="str">
+        <v>O estudo avaliou o efeito de fontes de fósforo em ausência e presença de bagaço (enriquecido ou não com biofertilizante) na população de microorganismos do solo, conteúdo de fósforo no solo, acúmulo de fósforo na parte aérea da planta e produção de matéria seca em cana-de-açúcar.</v>
+      </c>
+      <c r="J175" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K175" t="str">
+        <v>Revista Ciência e Investigação Agrária</v>
+      </c>
+      <c r="L175" t="str">
+        <v>Universidade Estadual Paulista (FCAV/UNESP)</v>
+      </c>
+      <c r="M175" t="str">
+        <v>Jaboticabal, SP, Brasil</v>
+      </c>
+      <c r="N175" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O175" t="str">
+        <v>Ciência e Investigação Agrária</v>
+      </c>
+      <c r="P175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q175" t="str">
+        <v>42</v>
+      </c>
+      <c r="R175" t="str">
+        <v>2</v>
+      </c>
+      <c r="S175" t="str">
+        <v>295-303</v>
+      </c>
+      <c r="T175" t="str">
+        <v>10.4067/S0718-162020150002000015</v>
+      </c>
+      <c r="U175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W175" t="str">
+        <v>Phosphorus sources enriched with filter cake and microorganisms_bioinsumos.pdf</v>
+      </c>
+      <c r="X175" t="str">
+        <v/>
+      </c>
+      <c r="Y175" t="str">
+        <v/>
+      </c>
+      <c r="Z175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF175" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG175" t="str">
+        <v/>
+      </c>
+      <c r="AH175" t="str">
+        <v/>
+      </c>
+      <c r="AI175" t="str">
+        <v/>
+      </c>
+      <c r="AJ175" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v/>
+      </c>
+      <c r="B176" t="str">
+        <v/>
+      </c>
+      <c r="C176" t="str">
+        <v>M.P. Stephan, M. Oliveira, K.R.S. Teixeira, G. Martinez-Drets e J. D/Sbereiner</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Physiology and dinitrogen fixation of A cetobacter diazotrophicus_bioinsumos</v>
+      </c>
+      <c r="E176" t="str">
+        <v>Nitrogenase activity in vivo</v>
+      </c>
+      <c r="F176" t="str">
+        <v>1991</v>
+      </c>
+      <c r="G176" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H176" t="str">
+        <v>N2-dependent growth, N2-fixation, in sugar cane, Acetobacter diazotrophicus</v>
+      </c>
+      <c r="I176" t="str">
+        <v>O artigo descreve as características fisiológicas de Acetobacter diazotrophicus, um diazotrófico isolado de raízes de cana-de-açúcar.</v>
+      </c>
+      <c r="J176" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K176" t="str">
+        <v>FEMS Microbiology Letters</v>
+      </c>
+      <c r="L176" t="str">
+        <v>CNPBS/EMBRAPA</v>
+      </c>
+      <c r="M176" t="str">
+        <v>Seropédica, Rio de Janeiro, Brasil</v>
+      </c>
+      <c r="N176" t="str">
+        <v>Estudo de caso</v>
+      </c>
+      <c r="O176" t="str">
+        <v>FEMS Microbiology Letters</v>
+      </c>
+      <c r="P176" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q176" t="str">
+        <v>77</v>
+      </c>
+      <c r="R176" t="str">
+        <v>1</v>
+      </c>
+      <c r="S176" t="str">
+        <v>67-72</v>
+      </c>
+      <c r="T176" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U176" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V176" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W176" t="str">
+        <v>Physiology and dinitrogen fixation of A cetobacter diazotrophicus_bioinsumos.pdf</v>
+      </c>
+      <c r="X176" t="str">
+        <v/>
+      </c>
+      <c r="Y176" t="str">
+        <v/>
+      </c>
+      <c r="Z176" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA176" t="str">
+        <v>Cromatografia gasosa, HPLC, ARA (acetylene reduction method)</v>
+      </c>
+      <c r="AB176" t="str">
+        <v>N2, NH~</v>
+      </c>
+      <c r="AC176" t="str">
+        <v>Fertilização com (NH4)2SO4</v>
+      </c>
+      <c r="AD176" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE176" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF176" t="str">
+        <v>Aprovado: Detalha as características fisiológicas de Acetobacter diazotrophicus.</v>
+      </c>
+      <c r="AG176" t="str">
+        <v/>
+      </c>
+      <c r="AH176" t="str">
+        <v/>
+      </c>
+      <c r="AI176" t="str">
+        <v/>
+      </c>
+      <c r="AJ176" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v/>
+      </c>
+      <c r="B177" t="str">
+        <v/>
+      </c>
+      <c r="C177" t="str">
+        <v>Chanyarat Paungfoo-Lonhienne, Nantida Watanarojanaporn, Ian Petersen, Ratchaniwan Jaemsaeng, Peeraya Klomsa-ard, Klanarong Sriroth</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Plant growth promoting rhizobacteria_bioinsumos</v>
+      </c>
+      <c r="E177" t="str">
+        <v>Efeitos do PGPR na produtividade da cana-de-açúcar</v>
+      </c>
+      <c r="F177" t="str">
+        <v>2021</v>
+      </c>
+      <c r="G177" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H177" t="str">
+        <v>Fertilizante, Fertilizante orgânico, PGPR, Ratoeira, Cana-de-açúcar</v>
+      </c>
+      <c r="I177" t="str">
+        <v>O estudo investigou os efeitos do PGPR na produtividade da cana-de-açúcar em cultivo de ratoeira.</v>
+      </c>
+      <c r="J177" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K177" t="str">
+        <v>AJCS</v>
+      </c>
+      <c r="L177" t="str">
+        <v>The University of Queensland, Mitr Phol Sugarcane Research Center Co., Ltd.</v>
+      </c>
+      <c r="M177" t="str">
+        <v>Brisbane, QLD 4072, Australia, Phu Khiao, Chaiyaphum, 36110, Thailand</v>
+      </c>
+      <c r="N177" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O177" t="str">
+        <v>Australian Journal of Crop Science</v>
+      </c>
+      <c r="P177" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q177" t="str">
+        <v>15</v>
+      </c>
+      <c r="R177" t="str">
+        <v>12</v>
+      </c>
+      <c r="S177" t="str">
+        <v>1442-1445</v>
+      </c>
+      <c r="T177" t="str">
+        <v>Research notes</v>
+      </c>
+      <c r="U177" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V177" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W177" t="str">
+        <v>Plant growth promoting rhizobacteria_bioinsumos.pdf</v>
+      </c>
+      <c r="X177" t="str">
+        <v/>
+      </c>
+      <c r="Y177" t="str">
+        <v/>
+      </c>
+      <c r="Z177" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA177" t="str">
+        <v>Cromatografia gasosa, Fotossíntese líquida, RCBD, ANOVA</v>
+      </c>
+      <c r="AB177" t="str">
+        <v>Nitrogênio, Fósforo, Potássio</v>
+      </c>
+      <c r="AC177" t="str">
+        <v>Fertirrigação, Aplicação foliar, Controle de pragas</v>
+      </c>
+      <c r="AD177" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE177" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF177" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG177" t="str">
+        <v/>
+      </c>
+      <c r="AH177" t="str">
+        <v/>
+      </c>
+      <c r="AI177" t="str">
+        <v/>
+      </c>
+      <c r="AJ177" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v/>
+      </c>
+      <c r="B178" t="str">
+        <v/>
+      </c>
+      <c r="C178" t="str">
+        <v>Lucas Augusto da Silva Gírio, Fábio Luis Ferreira Dias, Veronica Massena Reis, Segundo Urquiaga, Nivaldo Schultz, Denizart Bolonhezi, Miguel Angelo Mutton</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Plant growth-promoting bacteria and nitrogen_bioinsumos</v>
+      </c>
+      <c r="E178" t="str">
+        <v>Efeitos da inoculação de bactérias promotoras de crescimento sobre a formação de mudas pré‑brotadas de cana‑de‑açúcar</v>
+      </c>
+      <c r="F178" t="str">
+        <v>2015</v>
+      </c>
+      <c r="G178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H178" t="str">
+        <v>Saccharum, bactérias diazotróficas, biofertilizante, fitormônios, fixação biológica de nitrogênio</v>
+      </c>
+      <c r="I178" t="str">
+        <v>O objetivo deste trabalho foi avaliar os efeitos da inoculação de bactérias promotoras de crescimento sobre a formação de mudas pré‑brotadas de cana‑de‑açúcar, oriundas de gemas individualizadas, e quantificar o crescimento inicial dessas mudas, em associação à aplicação de nitrogênio, em solo de baixa fertilidade.</v>
+      </c>
+      <c r="J178" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K178" t="str">
+        <v>Pesq. agropec. bras.</v>
+      </c>
+      <c r="L178" t="str">
+        <v>Universidade Estadual Paulista, Departamento de Produção Vegetal</v>
+      </c>
+      <c r="M178" t="str">
+        <v>Jaboticabal, SP, Brasil</v>
+      </c>
+      <c r="N178" t="str">
+        <v>Experimento</v>
+      </c>
+      <c r="O178" t="str">
+        <v>Pesquisa Agropecuária Brasileira</v>
+      </c>
+      <c r="P178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q178" t="str">
+        <v>50</v>
+      </c>
+      <c r="R178" t="str">
+        <v>1</v>
+      </c>
+      <c r="S178" t="str">
+        <v>33-43</v>
+      </c>
+      <c r="T178" t="str">
+        <v>10.1590/S0100-204X2015000100004</v>
+      </c>
+      <c r="U178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W178" t="str">
+        <v>Plant growth-promoting bacteria and nitrogen_bioinsumos.pdf</v>
+      </c>
+      <c r="X178" t="str">
+        <v/>
+      </c>
+      <c r="Y178" t="str">
+        <v/>
+      </c>
+      <c r="Z178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF178" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG178" t="str">
+        <v/>
+      </c>
+      <c r="AH178" t="str">
+        <v/>
+      </c>
+      <c r="AI178" t="str">
+        <v/>
+      </c>
+      <c r="AJ178" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v/>
+      </c>
+      <c r="B179" t="str">
+        <v/>
+      </c>
+      <c r="C179" t="str">
+        <v>Gabriela Michavila, Pasquale Alibrandi, Paolo Cinà, Bjorn Welin, Atilio Pedro Castagnaro, Nadia Regina Chalfoun, Aldo Sergio Noguera, Anna Maria Puglia, Mirella Ciaccio, Josefina Racedo</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Plant growth_promoting bacteria_bioinsumos</v>
+      </c>
+      <c r="E179" t="str">
+        <v>Isolamento e caracterização de bactérias promotoras de crescimento de plantas em cana-de-açúcar</v>
+      </c>
+      <c r="F179" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H179" t="str">
+        <v>Bacillus, Paenibacillus, bactérias promotoras de crescimento de plantas, Pseudomonas, Saccharum híbridos</v>
+      </c>
+      <c r="I179" t="str">
+        <v>A microbiota da planta desempenha um papel importante na aquisição de nutrientes e no amortecimento de estresse abiótico e biótico. Durante a propagação in vitro da cana-de-açúcar, os microorganismos patogênicos são eliminados e a maioria das bactérias beneficentes endofíticas.</v>
+      </c>
+      <c r="J179" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K179" t="str">
+        <v>P AGEPress, Italy</v>
+      </c>
+      <c r="L179" t="str">
+        <v>Instituto de Tecnologia Agroindustrial do Noroeste Argentino (ITANOA), Estação Experimental Agroindustrial Obispo Colombres (EEAOC) - Conselho Nacional de Investigações Científicas e Técnicas (CONICET) - CONICET NOA Sul</v>
+      </c>
+      <c r="M179" t="str">
+        <v>Las Talitas, Tucumã, Argentina</v>
+      </c>
+      <c r="N179" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O179" t="str">
+        <v>Italian Journal of Agronomy</v>
+      </c>
+      <c r="P179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q179" t="str">
+        <v>17</v>
+      </c>
+      <c r="R179" t="str">
+        <v>2006</v>
+      </c>
+      <c r="S179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W179" t="str">
+        <v>Plant growth_promoting bacteria_bioinsumos.pdf</v>
+      </c>
+      <c r="X179" t="str">
+        <v/>
+      </c>
+      <c r="Y179" t="str">
+        <v/>
+      </c>
+      <c r="Z179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA179" t="str">
+        <v>Cromatografia gasosa, Sequenciamento de 16S rDNA, Testes de tolerância a estresse abiótico e biótico</v>
+      </c>
+      <c r="AB179" t="str">
+        <v>Fosfato inorgânico, Fosfato orgânico, Nitrogênio, Sideróforos, Ácido indol-3-acético</v>
+      </c>
+      <c r="AC179" t="str">
+        <v>Fertirrigação, Aplicação foliar, Controle de pragas</v>
+      </c>
+      <c r="AD179" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE179" t="str">
+        <v>Cana-de-açúcar (Saccharum spp. híbridos)</v>
+      </c>
+      <c r="AF179" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG179" t="str">
+        <v/>
+      </c>
+      <c r="AH179" t="str">
+        <v/>
+      </c>
+      <c r="AI179" t="str">
+        <v/>
+      </c>
+      <c r="AJ179" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v/>
+      </c>
+      <c r="B180" t="str">
+        <v/>
+      </c>
+      <c r="C180" t="str">
+        <v>Silva et al.</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Productivity and technological quality of sugarcane ratoon subject_bioinsumos</v>
+      </c>
+      <c r="E180" t="str">
+        <v>Productivity and technological quality of sugarcane ratoon subject to the application of plant growth regulator and liquid fertilizers</v>
+      </c>
+      <c r="F180" t="str">
+        <v>2010</v>
+      </c>
+      <c r="G180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H180" t="str">
+        <v>Saccharum spp., bioestimulante, longevidade, perfilhamento, produção</v>
+      </c>
+      <c r="I180" t="str">
+        <v>O presente trabalho objetivou avaliar a aplicação de biorreguladores, associados ou não a fertilizantes líquidos, na rebrota e na produtividade da soqueira de cinco genótipos de cana-de-açúcar.</v>
+      </c>
+      <c r="J180" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K180" t="str">
+        <v>Ciência Rural</v>
+      </c>
+      <c r="L180" t="str">
+        <v>Universidade de Santa Maria</v>
+      </c>
+      <c r="M180" t="str">
+        <v>Santa Maria, RS, Brasil</v>
+      </c>
+      <c r="N180" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O180" t="str">
+        <v>Ciência Rural</v>
+      </c>
+      <c r="P180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q180" t="str">
+        <v>40</v>
+      </c>
+      <c r="R180" t="str">
+        <v>4</v>
+      </c>
+      <c r="S180" t="str">
+        <v>774-780</v>
+      </c>
+      <c r="T180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W180" t="str">
+        <v>Productivity and technological quality of sugarcane ratoon subject_bioinsumos.pdf</v>
+      </c>
+      <c r="X180" t="str">
+        <v/>
+      </c>
+      <c r="Y180" t="str">
+        <v/>
+      </c>
+      <c r="Z180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA180" t="str">
+        <v>Delineamento em blocos inteiramente casualizados, esquema fatorial 5x5, utilização de biorreguladores e fertilizantes líquidos.</v>
+      </c>
+      <c r="AB180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC180" t="str">
+        <v>Aplicação de biorreguladores e fertilizantes líquidos.</v>
+      </c>
+      <c r="AD180" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE180" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AG180" t="str">
+        <v/>
+      </c>
+      <c r="AH180" t="str">
+        <v/>
+      </c>
+      <c r="AI180" t="str">
+        <v/>
+      </c>
+      <c r="AJ180" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v/>
+      </c>
+      <c r="B181" t="str">
+        <v/>
+      </c>
+      <c r="C181" t="str">
+        <v>S K THAKUR, C K JHA, M ALAM, V P SINGH</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Productivity_quality_and_soil_fertility_of_sugarca_bioinsumos</v>
+      </c>
+      <c r="E181" t="str">
+        <v>Evaluating a sistema de agricultura orgânica e convencional para a cana-de-açúcar</v>
+      </c>
+      <c r="F181" t="str">
+        <v>2012</v>
+      </c>
+      <c r="G181" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H181" t="str">
+        <v>Cana-de-açúcar, Fertilidade do solo, Agricultura orgânica, Qualidade da cana</v>
+      </c>
+      <c r="I181" t="str">
+        <v>Este estudo avaliou a produtividade, qualidade e fertilidade do solo da cana-de-açúcar (Saccharum spp complex hybrid) em sistema de plantio e ratoeira sob agricultura orgânica e convencional.</v>
+      </c>
+      <c r="J181" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K181" t="str">
+        <v>Indian Journal of Agricultural Sciences</v>
+      </c>
+      <c r="L181" t="str">
+        <v>Sugarcane Research Institute, RAU, Pusa, Bihar</v>
+      </c>
+      <c r="M181" t="str">
+        <v>Pusa, Bihar</v>
+      </c>
+      <c r="N181" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O181" t="str">
+        <v>Indian Journal of Agricultural Sciences</v>
+      </c>
+      <c r="P181" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q181" t="str">
+        <v>82</v>
+      </c>
+      <c r="R181" t="str">
+        <v>10</v>
+      </c>
+      <c r="S181" t="str">
+        <v>896–9</v>
+      </c>
+      <c r="T181" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U181" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V181" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W181" t="str">
+        <v>Productivity_quality_and_soil_fertility_of_sugarca_bioinsumos.pdf</v>
+      </c>
+      <c r="X181" t="str">
+        <v/>
+      </c>
+      <c r="Y181" t="str">
+        <v/>
+      </c>
+      <c r="Z181" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA181" t="str">
+        <v>Cromatografia gasosa, Fotossíntese líquida, RCBD, ANOVA</v>
+      </c>
+      <c r="AB181" t="str">
+        <v>Nitrogênio, Fósforo, Potássio, Carbono orgânico</v>
+      </c>
+      <c r="AC181" t="str">
+        <v>Fertirrigação, Aplicação foliar, Controle de pragas, Poda</v>
+      </c>
+      <c r="AD181" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE181" t="str">
+        <v>Cana-de-açúcar (Saccharum spp complex hybrid)</v>
+      </c>
+      <c r="AF181" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação orgânica e convencional.</v>
+      </c>
+      <c r="AG181" t="str">
+        <v/>
+      </c>
+      <c r="AH181" t="str">
+        <v/>
+      </c>
+      <c r="AI181" t="str">
+        <v/>
+      </c>
+      <c r="AJ181" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v/>
+      </c>
+      <c r="B182" t="str">
+        <v/>
+      </c>
+      <c r="C182" t="str">
+        <v>Roberto Batista Marques Júnior, Luciano Pasqualoto Canellas, Lúcia Gracinda da Silva, Fábio Lopes Olivares</v>
+      </c>
+      <c r="D182" t="str">
+        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE_bioinsumos</v>
+      </c>
+      <c r="E182" t="str">
+        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE OF HUMIC SUBSTANCES AND ENDOPHYTIC DIAZOTROPHIC BACTERIA IN SUGAR CANE</v>
+      </c>
+      <c r="F182" t="str">
+        <v>2008</v>
+      </c>
+      <c r="G182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H182" t="str">
+        <v>Herbaspirillum seropedicae, termoterapia, ácidos húmicos</v>
+      </c>
+      <c r="I182" t="str">
+        <v>Além do fornecimento direto de nutrientes por meio da mineralização da matéria orgânica ou pela fixação biológica de N 2, as substâncias húmicas e as bactérias diazotróficas endofíticas podem afetar diretamente o metabolismo vegetal, modificando o padrão de crescimento e desenvolvimento das plantas.</v>
+      </c>
+      <c r="J182" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K182" t="str">
+        <v>R. Bras. Ci. Solo</v>
+      </c>
+      <c r="L182" t="str">
+        <v>Universidade Estadual do Norte Fluminense - UENF</v>
+      </c>
+      <c r="M182" t="str">
+        <v>Campos dos Goytacazes (RJ)</v>
+      </c>
+      <c r="N182" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O182" t="str">
+        <v>Revista Brasileira de Ciência do Solo</v>
+      </c>
+      <c r="P182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q182" t="str">
+        <v>32</v>
+      </c>
+      <c r="R182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S182" t="str">
+        <v>1121-1128</v>
+      </c>
+      <c r="T182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W182" t="str">
+        <v>ROOTING OF MICRO SEED PIECES BY COMBINED USE_bioinsumos.pdf</v>
+      </c>
+      <c r="X182" t="str">
+        <v/>
+      </c>
+      <c r="Y182" t="str">
+        <v/>
+      </c>
+      <c r="Z182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AG182" t="str">
+        <v/>
+      </c>
+      <c r="AH182" t="str">
+        <v/>
+      </c>
+      <c r="AI182" t="str">
+        <v/>
+      </c>
+      <c r="AJ182" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v/>
+      </c>
+      <c r="B183" t="str">
+        <v/>
+      </c>
+      <c r="C183" t="str">
+        <v>K. HARI e T.R. SRINIVASAN</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Response of sugarcane varieties to application of nitrogen fixing_bioinsumos</v>
+      </c>
+      <c r="E183" t="str">
+        <v>Efeito da aplicação de bactérias fixadoras de nitrogênio em variedades de cana-de-açúcar sob diferentes níveis de nitrogênio</v>
+      </c>
+      <c r="F183" t="str">
+        <v>2005</v>
+      </c>
+      <c r="G183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H183" t="str">
+        <v>cana-de-açúcar, biofertilizantes, Azotobacter, Azospirillum e Gluconacetobacter, bactérias fixadoras de nitrogênio</v>
+      </c>
+      <c r="I183" t="str">
+        <v>Estudo de campo realizado para avaliar a resposta de variedades de cana-de-açúcar à aplicação de Azotobacter, Azospirillum e Gluconacetobacter sob diferentes níveis de fertilizante de nitrogênio.</v>
+      </c>
+      <c r="J183" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L183" t="str">
+        <v>Sugarcane Breeding Institute, ICAR, Coimbatore</v>
+      </c>
+      <c r="M183" t="str">
+        <v>Coimbatore, Índia</v>
+      </c>
+      <c r="N183" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W183" t="str">
+        <v>Response of sugarcane varieties to application of nitrogen fixing_bioinsumos.pdf</v>
+      </c>
+      <c r="X183" t="str">
+        <v/>
+      </c>
+      <c r="Y183" t="str">
+        <v/>
+      </c>
+      <c r="Z183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF183" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à aplicação de bactérias fixadoras de nitrogênio sob diferentes níveis de nitrogênio.</v>
+      </c>
+      <c r="AG183" t="str">
+        <v/>
+      </c>
+      <c r="AH183" t="str">
+        <v/>
+      </c>
+      <c r="AI183" t="str">
+        <v/>
+      </c>
+      <c r="AJ183" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v/>
+      </c>
+      <c r="B184" t="str">
+        <v/>
+      </c>
+      <c r="C184" t="str">
+        <v>R. Arthee e P. Marimuthu</v>
+      </c>
+      <c r="D184" t="str">
+        <v>STUDIES ON ENDOPHYTIC Burkholderia sp_bioinsumos</v>
+      </c>
+      <c r="E184" t="str">
+        <v>Ocorrência de Burkholderia gênero como endofito de cana-de-açúcar cultivada localmente foi estudada.</v>
+      </c>
+      <c r="F184" t="str">
+        <v>2017</v>
+      </c>
+      <c r="G184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H184" t="str">
+        <v>Burkholderia, MALDI-TOF MS, Promoção de crescimento de plantas, Filogenia</v>
+      </c>
+      <c r="I184" t="str">
+        <v>O estudo da ocorrência de Burkholderia gênero como endofito de cana-de-açúcar cultivada localmente foi realizado. Foram obtidos 22 isolados endofíticos, dos quais 10 foram encontrados como endofíticos em cana-de-açúcar. Análises morfológica, bioquímica e MALDI-TOF MS foram realizadas e 5 isolados endofíticos de Burkholderia sp. foram identificados.</v>
+      </c>
+      <c r="J184" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K184" t="str">
+        <v>Journal of Experimental Biology and Agricultural Sciences</v>
+      </c>
+      <c r="L184" t="str">
+        <v>Tamil Nadu Agricultural University</v>
+      </c>
+      <c r="M184" t="str">
+        <v>Coimbatore-03</v>
+      </c>
+      <c r="N184" t="str">
+        <v>Estudo de caso</v>
+      </c>
+      <c r="O184" t="str">
+        <v>Journal of Experimental Biology and Agricultural Sciences</v>
+      </c>
+      <c r="P184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q184" t="str">
+        <v>5(2)</v>
+      </c>
+      <c r="R184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T184" t="str">
+        <v>http://dx.doi.org/10.18006/2017.5(2).242.257</v>
+      </c>
+      <c r="U184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W184" t="str">
+        <v>STUDIES ON ENDOPHYTIC Burkholderia sp_bioinsumos.pdf</v>
+      </c>
+      <c r="X184" t="str">
+        <v/>
+      </c>
+      <c r="Y184" t="str">
+        <v/>
+      </c>
+      <c r="Z184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF184" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG184" t="str">
+        <v/>
+      </c>
+      <c r="AH184" t="str">
+        <v/>
+      </c>
+      <c r="AI184" t="str">
+        <v/>
+      </c>
+      <c r="AJ184" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v/>
+      </c>
+      <c r="B185" t="str">
+        <v/>
+      </c>
+      <c r="C185" t="str">
+        <v>Gabrielle Alves Bezerra, Marco Aurélio Takita, Christiann Davis Tosta, Sandra Regina Ceccato-Antonini, Márcia Maria Rosa-Magri</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Screening of plant growth-promoting_bioinsumos</v>
+      </c>
+      <c r="E185" t="str">
+        <v>Isolamento e caracterização de Bacillus spp. de solo, rizosfera e endosfera radicular de cana-de-açúcar</v>
+      </c>
+      <c r="F185" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H185" t="str">
+        <v>Microbioma vegetal, Bacillus, Solubilização, Ácido indolacético, Antagonismo</v>
+      </c>
+      <c r="I185" t="str">
+        <v>O estudo teve como objetivo isolar bactérias do solo, rizosfera e endosfera radicular de cana-de-açúcar, cultivada na região Sudeste do Brasil, para prospectar cepas com potencial para promoção de crescimento vegetal.</v>
+      </c>
+      <c r="J185" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K185" t="str">
+        <v>Semina: Ciênc. Agrár. Londrina</v>
+      </c>
+      <c r="L185" t="str">
+        <v>Universidade Federal de São Carlos</v>
+      </c>
+      <c r="M185" t="str">
+        <v>Araras, SP, Brasil</v>
+      </c>
+      <c r="N185" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O185" t="str">
+        <v>Semina: Ciênc. Agrár. Londrina</v>
+      </c>
+      <c r="P185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q185" t="str">
+        <v>43</v>
+      </c>
+      <c r="R185" t="str">
+        <v>4</v>
+      </c>
+      <c r="S185" t="str">
+        <v>1757-1768</v>
+      </c>
+      <c r="T185" t="str">
+        <v>10.5433/1679-0359.2022v43n4p1757</v>
+      </c>
+      <c r="U185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W185" t="str">
+        <v>Screening of plant growth-promoting_bioinsumos.pdf</v>
+      </c>
+      <c r="X185" t="str">
+        <v/>
+      </c>
+      <c r="Y185" t="str">
+        <v/>
+      </c>
+      <c r="Z185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF185" t="str">
+        <v>Aprovado: Detalha a seleção e caracterização de Bacillus spp. de solo, rizosfera e endosfera radicular de cana-de-açúcar.</v>
+      </c>
+      <c r="AG185" t="str">
+        <v/>
+      </c>
+      <c r="AH185" t="str">
+        <v/>
+      </c>
+      <c r="AI185" t="str">
+        <v/>
+      </c>
+      <c r="AJ185" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v/>
+      </c>
+      <c r="B186" t="str">
+        <v/>
+      </c>
+      <c r="C186" t="str">
+        <v>Mahboobeh Pirhadi, Naeimeh Enayatizamir, Hossein Motamedi e Karim Sorkheh</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Screening of salt tolerant sugarcane_bioinsumos</v>
+      </c>
+      <c r="E186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="F186" t="str">
+        <v>2016</v>
+      </c>
+      <c r="G186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H186" t="str">
+        <v>BIOFERTILIZER, INHIBITION, SALINITY, DISSOLUTION</v>
+      </c>
+      <c r="I186" t="str">
+        <v>O artigo descreve a diversidade de bactérias endofíticas tolerantes a sal na parte interna das raízes, caules e folhas de cana-de-açúcar, com habilidade de solubilizar zinco e potássio e atividade antifúngica.</v>
+      </c>
+      <c r="J186" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K186" t="str">
+        <v>Agricultural Communication Biosci. Biotech. Res. Comm.</v>
+      </c>
+      <c r="L186" t="str">
+        <v>Shahid Chamran University of Ahvaz</v>
+      </c>
+      <c r="M186" t="str">
+        <v>Ahvaz, Irã</v>
+      </c>
+      <c r="N186" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O186" t="str">
+        <v>Agricultural Communication Biosci. Biotech. Res. Comm.</v>
+      </c>
+      <c r="P186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q186" t="str">
+        <v>9</v>
+      </c>
+      <c r="R186" t="str">
+        <v>3</v>
+      </c>
+      <c r="S186" t="str">
+        <v>530-538</v>
+      </c>
+      <c r="T186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="U186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W186" t="str">
+        <v>Screening of salt tolerant sugarcane_bioinsumos.pdf</v>
+      </c>
+      <c r="X186" t="str">
+        <v/>
+      </c>
+      <c r="Y186" t="str">
+        <v/>
+      </c>
+      <c r="Z186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA186" t="str">
+        <v>Nutrient Agar, PVK, Alexandrov agar, dual culture technique, sequenciamento de 16S rRNA</v>
+      </c>
+      <c r="AB186" t="str">
+        <v>Potássio, Zinco</v>
+      </c>
+      <c r="AC186" t="str">
+        <v>Fertirrigação, Aplicação foliar</v>
+      </c>
+      <c r="AD186" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE186" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF186" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG186" t="str">
+        <v/>
+      </c>
+      <c r="AH186" t="str">
+        <v/>
+      </c>
+      <c r="AI186" t="str">
+        <v/>
+      </c>
+      <c r="AJ186" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v/>
+      </c>
+      <c r="B187" t="str">
+        <v/>
+      </c>
+      <c r="C187" t="str">
+        <v>Diwen Chen, Zhiming Li, Jin Yang, Wenling Zhou, Qihua Wu, Hong Shen, Junhua Ao</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Seaweed extract enhances drought_bioinsumos</v>
+      </c>
+      <c r="E187" t="str">
+        <v>Seaweed extract application can improve soil physical structure, promote enzyme activities, and increase the available N, P, and K of the soil.</v>
+      </c>
+      <c r="F187" t="str">
+        <v>2023</v>
+      </c>
+      <c r="G187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H187" t="str">
+        <v>Extrato de algas marinhas, Cana-de-açúcar, Resistência a seca, Arquitetura de raízes, Propriedades físico-químicas do solo</v>
+      </c>
+      <c r="I187" t="str">
+        <v>O estudo investigou os efeitos do extrato de algas marinhas no solo e na arquitetura de raízes de diferentes variedades de cana-de-açúcar sob condições de déficit hídrico.</v>
+      </c>
+      <c r="J187" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K187" t="str">
+        <v>Elsevier B.V.</v>
+      </c>
+      <c r="L187" t="str">
+        <v>Instituto de Nanfan &amp; Sementes, Academia de Ciências de Guangdong, China</v>
+      </c>
+      <c r="M187" t="str">
+        <v>Guangzhou, China</v>
+      </c>
+      <c r="N187" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O187" t="str">
+        <v>Industrial Crops &amp; Products</v>
+      </c>
+      <c r="P187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q187" t="str">
+        <v>194</v>
+      </c>
+      <c r="R187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T187" t="str">
+        <v>10.1016/j.indcrop.2023.116321</v>
+      </c>
+      <c r="U187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W187" t="str">
+        <v>Seaweed extract enhances drought_bioinsumos.pdf</v>
+      </c>
+      <c r="X187" t="str">
+        <v/>
+      </c>
+      <c r="Y187" t="str">
+        <v/>
+      </c>
+      <c r="Z187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF187" t="str">
+        <v>Aprovado: Detalha os efeitos do extrato de algas marinhas no solo e na arquitetura de raízes de cana-de-açúcar sob condições de déficit hídrico.</v>
+      </c>
+      <c r="AG187" t="str">
+        <v/>
+      </c>
+      <c r="AH187" t="str">
+        <v/>
+      </c>
+      <c r="AI187" t="str">
+        <v/>
+      </c>
+      <c r="AJ187" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v/>
+      </c>
+      <c r="B188" t="str">
+        <v/>
+      </c>
+      <c r="C188" t="str">
+        <v>Roberta Mendes dos Santos, Everlon Cid Rigobelo</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Selection of Saccharum spp_bioinsumos</v>
+      </c>
+      <c r="E188" t="str">
+        <v>Isolamento, caracterização e seleção de bactérias do gênero Saccharum spp. com propriedades promotoras de crescimento</v>
+      </c>
+      <c r="F188" t="str">
+        <v>2020</v>
+      </c>
+      <c r="G188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H188" t="str">
+        <v>Produção de plantas; bactérias promotoras de crescimento; cana-de-açúcar</v>
+      </c>
+      <c r="I188" t="str">
+        <v>O estudo buscou isolar, caracterizar e selecionar bactérias do gênero Saccharum spp. com propriedades promotoras de crescimento em seis variedades de cana-de-açúcar.</v>
+      </c>
+      <c r="J188" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K188" t="str">
+        <v>AJCS</v>
+      </c>
+      <c r="L188" t="str">
+        <v>Universidade Estadual Paulista (UNESP)</v>
+      </c>
+      <c r="M188" t="str">
+        <v>Jaboticabal, Brasil</v>
+      </c>
+      <c r="N188" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O188" t="str">
+        <v>Agricultural Journal of Crop Science</v>
+      </c>
+      <c r="P188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q188" t="str">
+        <v>14</v>
+      </c>
+      <c r="R188" t="str">
+        <v>07</v>
+      </c>
+      <c r="S188" t="str">
+        <v>1186-1194</v>
+      </c>
+      <c r="T188" t="str">
+        <v>10.21475/ajcs.20.14.07.p2698</v>
+      </c>
+      <c r="U188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W188" t="str">
+        <v>Selection of Saccharum spp_bioinsumos.pdf</v>
+      </c>
+      <c r="X188" t="str">
+        <v/>
+      </c>
+      <c r="Y188" t="str">
+        <v/>
+      </c>
+      <c r="Z188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AC188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AF188" t="str">
+        <v>Aprovado: Detalha a seleção de bactérias do gênero Saccharum spp. com propriedades promotoras de crescimento em cana-de-açúcar.</v>
+      </c>
+      <c r="AG188" t="str">
+        <v/>
+      </c>
+      <c r="AH188" t="str">
+        <v/>
+      </c>
+      <c r="AI188" t="str">
+        <v/>
+      </c>
+      <c r="AJ188" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v/>
+      </c>
+      <c r="B189" t="str">
+        <v/>
+      </c>
+      <c r="C189" t="str">
+        <v>Ziqin Pang, Fei Dong, Qiang Liu, Wenxiong Lin, Chaohua Hu e Zhaonian Yuan</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Soil Metagenomics Reveals Effects of Continuous Sugarcane_bioinsumos</v>
+      </c>
+      <c r="E189" t="str">
+        <v>Esta pesquisa analisou a estrutura e os caminhos funcionais da comunidade microbiana do solo de cana-de-açúcar em diferentes anos de cultivo contínuo.</v>
+      </c>
+      <c r="F189" t="str">
+        <v>2021</v>
+      </c>
+      <c r="G189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H189" t="str">
+        <v>cana-de-açúcar, cultivo contínuo, solo de rizosfera, metagenoma, estrutura da comunidade, bactérias e fungos, genes funcionais</v>
+      </c>
+      <c r="I189" t="str">
+        <v>A pesquisa analisou a estrutura e os caminhos funcionais da comunidade microbiana do solo de cana-de-açúcar em diferentes anos de cultivo contínuo.</v>
+      </c>
+      <c r="J189" t="str">
+        <v>Artigo de pesquisa</v>
+      </c>
+      <c r="K189" t="str">
+        <v>Frontiers in Microbiology</v>
+      </c>
+      <c r="L189" t="str">
+        <v>Fujian Agriculture and Forestry University</v>
+      </c>
+      <c r="M189" t="str">
+        <v>Fuzhou, China</v>
+      </c>
+      <c r="N189" t="str">
+        <v>Original Research</v>
+      </c>
+      <c r="O189" t="str">
+        <v>Frontiers in Microbiology</v>
+      </c>
+      <c r="P189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q189" t="str">
+        <v>12</v>
+      </c>
+      <c r="R189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="S189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="T189" t="str">
+        <v>10.3389/fmicb.2021.627569</v>
+      </c>
+      <c r="U189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W189" t="str">
+        <v>Soil Metagenomics Reveals Effects of Continuous Sugarcane_bioinsumos.pdf</v>
+      </c>
+      <c r="X189" t="str">
+        <v/>
+      </c>
+      <c r="Y189" t="str">
+        <v/>
+      </c>
+      <c r="Z189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA189" t="str">
+        <v>Illumina Miseq, metagenômica, análise de sequenciamento de alto throughput</v>
+      </c>
+      <c r="AB189" t="str">
+        <v>nitrogênio, enxofre, fósforo</v>
+      </c>
+      <c r="AC189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD189" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE189" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF189" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG189" t="str">
+        <v/>
+      </c>
+      <c r="AH189" t="str">
+        <v/>
+      </c>
+      <c r="AI189" t="str">
+        <v/>
+      </c>
+      <c r="AJ189" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v/>
+      </c>
+      <c r="B190" t="str">
+        <v/>
+      </c>
+      <c r="C190" t="str">
+        <v>Muhammad Nadeem Hassan, Shahid Afghan, Fauzia Yusuf Hafeez</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Suppression of red rot caused by Colletotrichum_bioinsumos</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v>2010</v>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" t="str">
+        <v>Erratum</v>
+      </c>
+      <c r="K190" t="str">
+        <v>International Organization for Biological Control (IOBC)</v>
+      </c>
+      <c r="L190" t="str">
+        <v>National Institute for Biotechnology and Genetic Engineering (NIBGE)</v>
+      </c>
+      <c r="M190" t="str">
+        <v>Faisalabad, Pakistan</v>
+      </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v>BioControl</v>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v>55</v>
+      </c>
+      <c r="R190" t="str">
+        <v/>
+      </c>
+      <c r="S190" t="str">
+        <v>531–542</v>
+      </c>
+      <c r="T190" t="str">
+        <v>10.1007/s10526-010-9268-z</v>
+      </c>
+      <c r="U190" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V190" t="str">
+        <v/>
+      </c>
+      <c r="W190" t="str">
+        <v>Suppression of red rot caused by Colletotrichum_bioinsumos.pdf</v>
+      </c>
+      <c r="X190" t="str">
+        <v/>
+      </c>
+      <c r="Y190" t="str">
+        <v/>
+      </c>
+      <c r="Z190" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA190" t="str">
+        <v/>
+      </c>
+      <c r="AB190" t="str">
+        <v/>
+      </c>
+      <c r="AC190" t="str">
+        <v/>
+      </c>
+      <c r="AD190" t="str">
+        <v/>
+      </c>
+      <c r="AE190" t="str">
+        <v>Sugarcane</v>
+      </c>
+      <c r="AF190" t="str">
+        <v>Aprovado: Estudo sobre o controle de Colletotrichum falcatum em cana-de-açúcar utilizando bactérias promotoras de crescimento vegetal.</v>
+      </c>
+      <c r="AG190" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH190" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AI190" t="str">
+        <v/>
+      </c>
+      <c r="AJ190" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v/>
+      </c>
+      <c r="B191" t="str">
+        <v/>
+      </c>
+      <c r="C191" t="str">
+        <v>N. SenthiP, T. Raguchander, R. Viswanathan e R. Samiyappan</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Talc Formulated Fluorescent Pseudomonads_bioinsumos</v>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v>2003</v>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v>Sugarcane, induzida resistência sistêmica, promoção de crescimento, Pseudomonas fluorescens, doença da gengiva vermelha</v>
+      </c>
+      <c r="I191" t="str">
+        <v>O estudo apresenta a eficácia de bactérias fluorescentes pseudomonadas em reduzir a incidência da doença da gengiva vermelha em cana-de-açúcar e melhorar o crescimento da planta.</v>
+      </c>
+      <c r="J191" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K191" t="str">
+        <v/>
+      </c>
+      <c r="L191" t="str">
+        <v>Tamil Nadu Agricultural University</v>
+      </c>
+      <c r="M191" t="str">
+        <v>Coimbatore, Tamil Nadu, Índia</v>
+      </c>
+      <c r="N191" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O191" t="str">
+        <v>9~ve.a~a~ ~ec~ Vol. 5 (l&amp;2)</v>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v>5</v>
+      </c>
+      <c r="R191" t="str">
+        <v>(l&amp;2)</v>
+      </c>
+      <c r="S191" t="str">
+        <v>37-43</v>
+      </c>
+      <c r="T191" t="str">
+        <v/>
+      </c>
+      <c r="U191" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V191" t="str">
+        <v/>
+      </c>
+      <c r="W191" t="str">
+        <v>Talc Formulated Fluorescent Pseudomonads_bioinsumos.pdf</v>
+      </c>
+      <c r="X191" t="str">
+        <v/>
+      </c>
+      <c r="Y191" t="str">
+        <v/>
+      </c>
+      <c r="Z191" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA191" t="str">
+        <v>Cromatografia gasosa, Fotossíntese líquida, RCBD, ANOVA</v>
+      </c>
+      <c r="AB191" t="str">
+        <v>Nitrogênio, Potássio, Sacarose</v>
+      </c>
+      <c r="AC191" t="str">
+        <v>Fertirrigação, Aplicação foliar</v>
+      </c>
+      <c r="AD191" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE191" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF191" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG191" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH191" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AI191" t="str">
+        <v/>
+      </c>
+      <c r="AJ191" t="str">
+        <v>citros e cana</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v/>
+      </c>
+      <c r="B192" t="str">
+        <v/>
+      </c>
+      <c r="C192" t="str">
+        <v>Silézio Ferreira da Silva, Fábio Lopes Olivares e Luciano Pasqualoto Canellas</v>
+      </c>
+      <c r="D192" t="str">
+        <v>The biostimulant manufactured using_bioinsumos</v>
+      </c>
+      <c r="E192" t="str">
+        <v/>
+      </c>
+      <c r="F192" t="str">
+        <v>2017</v>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v>Field response, Humic acids, Diazotrophic endophytic bacteria, Ecological intensification of crops</v>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v>RESEARCH</v>
+      </c>
+      <c r="K192" t="str">
+        <v/>
+      </c>
+      <c r="L192" t="str">
+        <v>Universidade Estadual do Norte Fluminense Darcy Ribeiro</v>
+      </c>
+      <c r="M192" t="str">
+        <v>Campos Dos Goytacazes</v>
+      </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v>Chem. Biol. Technol. Agric.</v>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" t="str">
+        <v/>
+      </c>
+      <c r="S192" t="str">
+        <v/>
+      </c>
+      <c r="T192" t="str">
+        <v>10.1186/s40538-017-0106-8</v>
+      </c>
+      <c r="U192" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V192" t="str">
+        <v/>
+      </c>
+      <c r="W192" t="str">
+        <v>The biostimulant manufactured using_bioinsumos.pdf</v>
+      </c>
+      <c r="X192" t="str">
+        <v/>
+      </c>
+      <c r="Y192" t="str">
+        <v/>
+      </c>
+      <c r="Z192" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA192" t="str">
+        <v>Cultivo de bactérias endofíticas diazotróficas, Análise de compostos orgânicos, Cromatografia gasosa</v>
+      </c>
+      <c r="AB192" t="str">
+        <v>Nitrogênio, Fósforo, Potássio</v>
+      </c>
+      <c r="AC192" t="str">
+        <v>Foliar spray, Aplicação em sulco</v>
+      </c>
+      <c r="AD192" t="str">
+        <v>Grandes Culturas</v>
+      </c>
+      <c r="AE192" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF192" t="str">
+        <v>Aprovado: Detalha a resposta da cana-de-açúcar à adubação nitrogenada.</v>
+      </c>
+      <c r="AG192" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH192" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AI192" t="str">
+        <v/>
+      </c>
+      <c r="AJ192" t="str">
+        <v>citros e cana</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v/>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>Daniella Senatore, Agustina Queirolo, Jorge Monza, Natalia Bajsa</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Using sugar cane vinasse as a biofertilizer_bioinsumos</v>
+      </c>
+      <c r="E193" t="str">
+        <v>Efeitos do vinagre de cana-de-açúcar como biofertilizante: efeitos na comunidade microbiana do solo devido à aplicação periódica</v>
+      </c>
+      <c r="F193" t="str">
+        <v>2023</v>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v>Fertirrigação, Resíduo industrial, Melhoria do solo, Qualidade do solo, Biocombustíveis</v>
+      </c>
+      <c r="I193" t="str">
+        <v>O estudo avaliou os efeitos da aplicação periódica de vinagre de cana-de-açúcar no solo e na comunidade microbiana de solos utilizados para a cultura de cana-de-açúcar.</v>
+      </c>
+      <c r="J193" t="str">
+        <v>Artigo original</v>
+      </c>
+      <c r="K193" t="str">
+        <v>Society for Environmental Sustainability</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Instituto de Investigaciones Biológicas Clemente Estable, Universidad de la República</v>
+      </c>
+      <c r="M193" t="str">
+        <v>Montevideo, Uruguay</v>
+      </c>
+      <c r="N193" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O193" t="str">
+        <v>Environmental Sustainability</v>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v>6</v>
+      </c>
+      <c r="R193" t="str">
+        <v>1</v>
+      </c>
+      <c r="S193" t="str">
+        <v>173–182</v>
+      </c>
+      <c r="T193" t="str">
+        <v>10.1007/s42398-023-00262-z</v>
+      </c>
+      <c r="U193" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V193" t="str">
+        <v/>
+      </c>
+      <c r="W193" t="str">
+        <v>Using sugar cane vinasse as a biofertilizer_bioinsumos.pdf</v>
+      </c>
+      <c r="X193" t="str">
+        <v/>
+      </c>
+      <c r="Y193" t="str">
+        <v/>
+      </c>
+      <c r="Z193" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA193" t="str">
+        <v>Análise de comunidades microbianas, Irrigação controlada, Coleta de amostras de solo</v>
+      </c>
+      <c r="AB193" t="str">
+        <v>Potássio, Carbono orgânico, Nitrogênio</v>
+      </c>
+      <c r="AC193" t="str">
+        <v>Fertirrigação</v>
+      </c>
+      <c r="AD193" t="str">
+        <v>Cultura de cana-de-açúcar</v>
+      </c>
+      <c r="AE193" t="str">
+        <v>Cana-de-açúcar</v>
+      </c>
+      <c r="AF193" t="str">
+        <v>Aprovado: Avalia os efeitos da aplicação periódica de vinagre de cana-de-açúcar no solo e na comunidade microbiana de solos utilizados para a cultura de cana-de-açúcar.</v>
+      </c>
+      <c r="AG193" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH193" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AI193" t="str">
+        <v/>
+      </c>
+      <c r="AJ193" t="str">
+        <v>solos</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v/>
+      </c>
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
+        <v>Amabelia del Pino, Omar Casanova, Jorge Hernández, Virginia Takata, Germán Panissa</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Vinasse for sugarcane crop nutrition_bioinsumos</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v>Saccharum, byproduct of ethanol production, biofertilizer, potassium, Uruguay</v>
+      </c>
+      <c r="I194" t="str">
+        <v>O uso de subprodutos agroindustriais como biofertilizantes impede a descarga poluidora e permite economia de fertilizantes comerciais.</v>
+      </c>
+      <c r="J194" t="str">
+        <v>Artigo científico</v>
+      </c>
+      <c r="K194" t="str">
+        <v>AJCS</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Faculdade de Agronomia, Universidade da República, Uruguai</v>
+      </c>
+      <c r="M194" t="str">
+        <v>Montevideo, Uruguai</v>
+      </c>
+      <c r="N194" t="str">
+        <v>Pesquisa</v>
+      </c>
+      <c r="O194" t="str">
+        <v>Agronomy Journal of Crop Science</v>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v>16</v>
+      </c>
+      <c r="R194" t="str">
+        <v>09</v>
+      </c>
+      <c r="S194" t="str">
+        <v>1107-1116</v>
+      </c>
+      <c r="T194" t="str">
+        <v>10.21475/ajcs.22.16.09.p3617</v>
+      </c>
+      <c r="U194" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V194" t="str">
+        <v/>
+      </c>
+      <c r="W194" t="str">
+        <v>Vinasse for sugarcane crop nutrition_bioinsumos.pdf</v>
+      </c>
+      <c r="X194" t="str">
+        <v/>
+      </c>
+      <c r="Y194" t="str">
+        <v/>
+      </c>
+      <c r="Z194" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA194" t="str">
+        <v>Análise de nutrientes no solo e na planta, determinação de produção e conteúdo de nutrientes.</v>
+      </c>
+      <c r="AB194" t="str">
+        <v>N, P, K, Ca e Mg</v>
+      </c>
+      <c r="AC194" t="str">
+        <v>Aplicação de vinasse e fertilizantes.</v>
+      </c>
+      <c r="AD194" t="str">
+        <v>Canavial (Saccharum officinarum)</v>
+      </c>
+      <c r="AE194" t="str">
+        <v>Canavial (Saccharum officinarum)</v>
+      </c>
+      <c r="AF194" t="str">
+        <v>Aprovado: Avalia a eficiência da vinasse como biofertilizante para o canavial.</v>
+      </c>
+      <c r="AG194" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH194" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AI194" t="str">
+        <v/>
+      </c>
+      <c r="AJ194" t="str">
+        <v>solos</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AJ128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ194"/>
   </ignoredErrors>
 </worksheet>
 </file>